--- a/public/conference_list.xlsx
+++ b/public/conference_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G176"/>
+  <dimension ref="A1:G152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,101 +456,101 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Financial Econometrics Conference</t>
+          <t>Fifth Annual Junior Faculty Business &amp; Financial Law Workshop</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2027-04-21</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2027-04-23</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Lancaster University, England</t>
+          <t>Philadelphia, University of Pennsylvania</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>£30 GBP</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>High-frequency econometrics, Market microstructure, Forecasting, Asset Pricing and investments, Risk neutral density estimation, Fintech &amp; blockchain, Cryptocurrencies, Climate econometrics, Volatility modelling, Artificial intelligence &amp; machine learning, Factor models, Term structure models, Risk modelling, Real time detection of extreme market events, Options &amp; derivatives modelling, Multivariate &amp; high dimensional time series modelling</t>
+          <t>Corporations, securities, finance, accounting, banking, bankruptcy, tax, and general business law</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026 Sydney Banking and Financial Stability Conference</t>
+          <t>SGF Conference 2027</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2027-04-09</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2027-04-09</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>The University of Sydney Business School, Sydney, Australia</t>
+          <t>Zurich, Switzerland</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CHF 60</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Banking, financial stability, Financial Intermediation, Financial Institutions and Markets, Fintech, Cryptocurrency and Central Bank Digital Currency, Financial system stability, Corporate Finance, Asset Pricing, Investment and Funds Management, Macro Finance</t>
+          <t>All topic areas of finance</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IIMB-CCGS International Corporate Governance &amp; Sustainability Conference 2026</t>
+          <t>HEC-HKUST-NUS Workshop on Sustainable Finance</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Indian Institute of Management, Bangalore, India</t>
+          <t>Paris and Hong Kong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -560,71 +560,71 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Corporate governance, sustainability, geo-political and economy risk, supply chain risk, AI and data analytics in governance, management and law, corporate governance and executive leadership, internal and external mechanisms of corporate governance, board diversity, governance for sustainable value creation, governance in startups, family business &amp; SMEs, balance between shareholders and stakeholders, role of auditors and institutional investors, corporate disclosures &amp; reporting practices, environment, social and governance, enterprise risk management, cyber security &amp; governance</t>
+          <t>Sustainable finance</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Conference on CSR, the Economy and Financial Markets</t>
+          <t>22nd International Behavioural Finance Conference (IBFC)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Düsseldorf, Germany</t>
+          <t>University of Chicago, Booth School of Business, Gleacher Center</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>€150 for regular participants, €100 for PhD students</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climate risk and pricing, Role of financial markets, banks, institutional investors in CSR, Effects of CSR on valuation, performance, cost of capital, funding and capital structure, Socio-economic aspects and their implications for companies and financial markets, Corporate governance and CSR, Risk management and CSR, CSR reporting and disclosure, ESG backlash and politicization, Sustainability strategy under new constraints, Measurement: information content and reliability of ESG indices, CSR activities and the economy</t>
+          <t>Behavioural Asset Pricing, Behavioural Corporate, Biases and Heuristics, Cryptocurrencies, Financial Analysts, Personal Financial Behavior, Financial Markets, Investment Decisions, Mergers and Acquisitions, Political Environment, Retail Investors, Sentiment, Climate Finance, CSR and ESG</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>International Conference in Banking and Financial Studies 2026 (ICBFS 2026)</t>
+          <t>European Winter Finance Conference 2027</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2027-01-10</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2027-01-13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Parma, Italy</t>
+          <t>Hotel Armancette, Saint-Gervais-les-Bains (near Megève), France</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -634,34 +634,34 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Banking and finance, Accounting, auditing, and taxation, Asset allocation and valuation, Banking regulation and financial services, Behavioral and experimental finance/economics, Big data in finance, artificial intelligence, and cybersecurity, Climate finance and sustainability, Corporate finance, IPOs, SEOs, M&amp;A, and crowdfunding, Corporate governance, Country funds, sovereign funds, and hedge funds, Debt markets and instruments, Digital finance, cryptocurrencies, and blockchain, Emerging markets finance, Energy finance and environmental issues, Entrepreneurial finance, venture capital, and private equity, Ethical finance, green finance, ESG, and CSR, Financial accounting and regulation, Financial crises, contagion, integration, and global risk interconnections, Financial engineering and derivatives, Foreign exchange markets and currency issues, Global imbalances and sustainability, Household finance, real estate finance, and microfinance, Market efficiency and behavior, Multinational financial management, Portfolio management and optimization, Risk management and compliance, Small business finance</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Colorado Finance Summit 2026</t>
+          <t>International Conference in Venice - Artificial Intelligence, Financial Innovation and Credit Risk</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vail, Colorado</t>
+          <t>Venice, Italy</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,34 +671,34 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>All areas of finance, theoretical and empirical contributions</t>
+          <t>Credit risk, financial innovation, artificial intelligence, financial stability, sustainability, design of credit markets</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>18th Annual Hedge Fund Research Conference</t>
+          <t>Prediction Markets Conference</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Université Paris Dauphine - PSL, Paris</t>
+          <t>Yale School of Management, New Haven, Connecticut</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -708,71 +708,71 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hedge funds, mutual funds, ETFs, private equity funds, institutional investors’ risks and performance, transparency (reporting) and due diligence, financial intermediation activity, macroeconomic issues such as systemic risk and contagion, institutional investors’ incentives and activism, portfolio liquidation and liquidity, financial regulation</t>
+          <t>Theoretical and empirical research on prediction markets</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>15th LaBS International Banking Workshop</t>
+          <t>63rd Annual Eastern Finance Association Meeting</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2027-04-07</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2027-04-10</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>HSE University and online</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>75 USD</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Banking in Emerging Markets: Challenges and Opportunities, theoretical and empirical research in Banking or Household finance</t>
+          <t>All areas of finance</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Private Equity Research Consortium (PERC) Symposium</t>
+          <t>Oklahoma Aerospace and Defense Finance Conference</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2027-03-26</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2027-03-27</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Chapel Hill, NC</t>
+          <t>Norman, Oklahoma</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -782,34 +782,34 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Private equity, buyouts, distressed securities, mezzanine financing, special situations, private credit, venture capital, real estate, real assets</t>
+          <t>Theoretical and empirical papers on any aviation, space, or defense finance research topic, including but not limited to venture capital and private equity financing, fiscal impacts of rearmament, capital structure determinants, sustainability in military aviation, risk management, asset pricing, and more.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IMRC 2026</t>
+          <t>Massey Sustainable Finance Conference</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>IIM Ahmedabad</t>
+          <t>Queenstown, New Zealand</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -819,71 +819,71 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Finance, Accounting, Economics, governance, financial risk &amp; analytics, theoretical and empirical asset pricing, quality of financial reporting and adoption of IFRS, market microstructure and algorithmic trading, insurance/reinsurance/pension funds, business cycles, corporate finance, capital structure and dividend policy, financial policy choice, institutions and regulation, enhancing liquidity in commodity derivatives markets, public economics, asset allocation and investment management, computational finance and financial econometrics, FDI and portfolio capital flows, household finance, international trade and exchange rates, financial crises, systemic risk and macro-finance, financial risk analytics and management, financial analytics, monetary policy and banking, global value chains and firm performance, macroeconomics, applied microeconomics</t>
+          <t>Artificial intelligence and machine learning applications in Sustainable Finance, Alternative data on firms' digital transformation, Behavioral Finance/Economics and its implications to climate transition, Blue economy, Carbon market and carbon credit, Carbon price forecasting techniques, Circular economy, Corporate Social Responsibility, Climate Finance, Climate risks: assessment and management, Climate transition and portfolio management, Cryptocurrency and digital finance interactions with Sustainable Finance, Diversity, equity and inclusion in Finance, Digital finance, Fintech, and sustainability, Environmental, Social and Governance, Financial markets and climate transition, Household Finance and sustainability, Green Finance, Green Finance and energy security, (Renewable) Energy Finance, Renewable Energy and Sustainability, Sustainable Finance and Accounting</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>16th Workshop on Exchange Rates</t>
+          <t>3rd Annual Boca Finance and Real Estate Conference</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Florida Atlantic University, Boca Raton, Florida, USA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$50 USD</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>The drivers of exchange rates and related asset prices from a financial perspective, Exchange rates and the transmission of monetary policy, FX interventions and supply side shocks, Exchange rates and macrofinancial stability frameworks, FX risk premia and their drivers, Global linkages between capital flows, foreign exchange rates and risk appetite, The international use of currencies and its implications for exchange rates, Implications of digital and tokenised assets for FX markets</t>
+          <t>All topics related to finance and real estate</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026 New Zealand Finance Meeting</t>
+          <t>22nd Annual Olin Finance Conference at WashU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Auckland, New Zealand</t>
+          <t>Washington University in St. Louis</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -893,145 +893,145 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>All topics related to the field of finance</t>
+          <t>asset pricing, behavioral finance, corporate finance, financial intermediation, household finance, development finance, labor finance</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6th Conference on Corporate Policies and Asset Prices (COAP)</t>
+          <t>16th Workshop on Exchange Rates</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nice, France</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>€50</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>asset pricing anomalies and their explanations; corporate finance models of asset pricing anomalies; dynamic corporate finance and contracting models, and their asset pricing implications; the asset pricing implications of sustainable finance; feedback effects from asset prices to corporate decisions; structural estimation of dynamic models using asset price data</t>
+          <t>Drivers of exchange rates and related asset prices from a financial perspective; Exchange rates and the transmission of monetary policy; FX interventions and supply side shocks; Exchange rates and macrofinancial stability frameworks; FX risk premia and their drivers; Global linkages between capital flows, foreign exchange rates and risk appetite; The international use of currencies and its implications for exchange rates; Implications of digital and tokenised assets for FX markets</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5th Contemporary Issues in Financial Markets and Banking</t>
+          <t>Southwestern Finance Association 2027 Annual Meeting</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2027-02-10</t>
+          <t>2027-02-17</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2027-02-11</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Online Conference</t>
+          <t>Las Vegas, NV</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USD 175</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Financial resilience; Green, climate and sustainable finance; Decentralised finance and disruptive financial technologies; Theoretical asset pricing; Empirical asset pricing, liquidity and behavioural economics and finance; Risk management; Financial inclusion; Alternative investments; Crowd-funding; Islamic banking; Banking and financial sector stability and regulation; Financial (dis)integration and Brexit; Artificial intelligence, machine and deep learning applications in finance; Corporate finance and sustainable energy financing; Crisis investment and portfolio management; Corporate governance; International financial management and investment; Market microstructure; Household finance; Real estate and property markets; Metaverse and Blockchain technologies in finance; Intersection between finance and economic theory, especially financial applications of game theory, decision theory, and computational financial economics; experimental economics with implications for financial theory and practice.</t>
+          <t>All aspects of finance and financial education</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>International Conference on Trade Wars, Geopolitical Fragmentation and Repercussions for Financial and Monetary Stability</t>
+          <t>34th Annual PBFEAM and 20th NYCU International conferences</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Brunel University of London (UK)</t>
+          <t>National Yang Ming Chiao Tung University, Hsinchu, Taiwan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>USD $250 for On-line Presenter &amp; USD $300 for On-site Presenter</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Art of the (trade) deal and financial costs, Asymmetric impacts on regions, commodity exporters, service-oriented economies and manufacturing centres, Capital flows and sudden stops due to trade wars, Central Banking in the age of trade wars and geopolitical conflicts, Central bank digital currencies (CBDCs), trade wars and geopolitical tensions, Currency weaponisation, competitive devaluation and financial instability, Digitisation, financial decoupling and financial stability during trade conflicts, Emerging markets and international financial flows under trade tensions, Empirical and theoretical analyses of strategic financial policies under trade restrictions, Exorbitant privilege of the US$ in the 21st century and the rise of alternative currencies, European Economic and Monetary Union’s financial integration with the US and the Global South, Financialization in the context of trade wars, Global financial imbalances, causes and financial consequences in the context of trade wars, International financial and monetary architecture and stress management in the age of trade conflict, Inflation targeting, trade wars and geopolitical conflicts, Productivity, innovation and efficiency related to technological spillovers and protectionism, Reallocation of global capital, safe havens and asset price bubbles during trade conflicts, Regional financial and monetary integration and the positive role of regions during trade conflicts, Role of central banks and macroprudential policy during trade conflicts, Sustainable financial development of the Global South and trade wars, Tariffs and non-tariff barriers and their negative financial impact on markets and firms</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labor &amp; Finance Group Fall 2026 Conference</t>
+          <t>Financial Research Association 2026 Annual Conference</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Penn State University – Smeal College of Business, State College, PA</t>
+          <t>Las Vegas, NV, USA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1041,34 +1041,34 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Human capital, compensation, and incentives; Labor market power, monopsony/oligopsony, and wage setting; Unions, collective bargaining, and worker representation; Organizational design, internal labor markets, and corporate governance; Labor mobility, non-compete agreements, and talent flows; Labor-related disclosure, regulation, and policy; Labor and financial markets, asset pricing, and corporate policies; Entrepreneurship and innovation</t>
+          <t>New finance papers of general interest to the profession, early work, research by junior scholars</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CUHK-RAPS-RCFS Conference on Asset Pricing and Corporate Finance</t>
+          <t>Fisher AI in Business Conference</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Ohio State University, Columbus</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1078,56 +1078,56 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Asset Pricing, Corporate Finance</t>
+          <t>AI’s impact on business functions and organizational transformation; multi-agent AI systems and human-AI collaboration; AI-driven customer and employee experiences; AI, sustainability, and ESG; building and scaling AI ventures; AI governance, ethics, and regulation; AI’s influence on strategy and competition; AI’s impact on work and society; measuring AI effectiveness; and AI applications in healthcare, education, and other high-stakes domains.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026 ABFER-JFDS Conference on AI for Finance</t>
+          <t>21st Annual Conference on Asia-Pacific Financial Markets (CAFM)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>International Institute of Finance, Hefei, Anhui, China</t>
+          <t>CONRAD Seoul</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Applications of artificial intelligence, machine learning, natural language processing, large language models, AI agents, high-performance computing in finance; Use of unstructured and alternative data in investment, auditing, and related fields; Social and economic impacts of AI adoption; Ethical, governance, and regulatory considerations of AI in finance; Quantitative investment strategies and portfolio optimization using AI.</t>
+          <t>All areas of finance</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Financial Economic Meeting</t>
+          <t>2026 Derivative Markets Conference</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Auckland, New Zealand</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1152,182 +1152,182 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Financial markets &amp; asset pricing, Banking, credit &amp; financial stability, Macroeconomics &amp; international finance, Sustainable finance &amp; climate risk, Quantitative methods &amp; emerging approaches</t>
+          <t>All topics related to derivative markets</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>39th Australasian Finance and Banking Conference</t>
+          <t>2027 Midwest Finance Association Annual Meeting</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2027-03-18</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2027-03-20</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AGSM and the UNSW Business School, Sydney, Australia</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>75 USD</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Opportunities and Risks of AI Technology in Finance, CBDCs, Fintech, and Digital Finance, Sustainable Investment</t>
+          <t>corporate finance, financial institutions, asset pricing, asset management</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Finance at a Time of Change and Uncertainty</t>
+          <t>2027 Bretton Woods Accounting and Finance Ski Conference</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2027-03-03</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2027-03-06</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Renmin University of China, Beijing, China</t>
+          <t>Bretton Woods, New Hampshire</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>89 USD</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Finance and AI, Finance and politics, Finance and climate change</t>
+          <t>All areas of accounting and finance</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MIT GCFP 13th Annual Conference</t>
+          <t>3rd LSU Finance Mardi Gras Conference</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2027-02-05</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2027-02-06</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cambridge, MA</t>
+          <t>Baton Rouge, LA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>75 USD</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Financial regulation in an era of innovation and disruption, AI's impact on financial markets, labor markets and the economy, investor protection and fair lending, new risks to financial stability, changing market structure for equities, bonds, and derivatives, growth of event contracts and prediction markets, growth of non-bank credit, developments in stablecoins, digital currencies, and payment systems, risks in “safe” assets such as sovereign debt, international coordination and comparisons, innovations in market architecture and infrastructure</t>
+          <t>All topics in finance</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EUROFIDAI-ESSEC Paris December Finance Meeting</t>
+          <t>Financial Econometrics Conference</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2027-04-21</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2027-04-23</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pullman Paris Montparnasse Hotel</t>
+          <t>Lancaster University, England</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>75€</t>
+          <t>30 GBP</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>All areas of finance</t>
+          <t>High-frequency econometrics, Market microstructure, Forecasting, Asset Pricing and investments, Risk neutral density estimation, Fintech &amp; blockchain, Cryptocurrencies, Climate econometrics, Volatility modelling, Artificial intelligence &amp; machine learning, Factor models, Term structure models, Risk modelling, Real time detection of extreme market events, Options &amp; derivatives modelling, Multivariate &amp; high dimensional time series modelling</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Chicago Fed/University of Chicago Conference on Municipal Bond Markets</t>
+          <t>2026 Sydney Banking and Financial Stability Conference</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Chicago</t>
+          <t>The University of Sydney Business School, Sydney, Australia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1337,145 +1337,145 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Unpublished and highly policy-relevant research papers on municipal bond markets, focusing on primary market frictions, secondary market frictions, role of retail investors, government policies affecting bond price formation, and the effect of state and federal policies on government access to external finance.</t>
+          <t>Banking, financial stability, financial intermediation, financial institutions and markets, fintech, cryptocurrency and central bank digital currency, financial system stability, corporate finance, asset pricing, investment and funds management, macro finance</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SFS Cavalcade Asia-Pacific 2026</t>
+          <t>IIMB-CCGS International Corporate Governance &amp; Sustainability Conference 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>City University of Hong Kong</t>
+          <t>Indian Institute of Management, Bangalore, India</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>$75 USD</t>
+          <t>Waived for selected Paper Presenters</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>In-depth participation in finance-related topics including but not limited to asset pricing, corporate finance, and fixed income.</t>
+          <t>Corporate governance and sustainability, Geo-political, economy, supply chain risk and corporate governance, AI, Data Analytics, and Machine Learning: Technology &amp; Governance, Bridging Management and Law for a Responsible Corporation, Corporate Governance and Executive Leadership, Internal &amp; External Mechanisms of Corporate Governance, Corporate Governance in Today’s Business Environment, Board Diversity, Governance for sustainable value creation, Governance in Startups, family business &amp; SMEs, Managing the right balance: Shareholders and Stakeholders, Role of Auditors and Institutional Investors, Corporate Disclosures &amp; Reporting Practices, Environment, Social and Governance, Enterprise Risk Management, Cyber Security &amp; Governance</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sustainable Accounting, Finance and Economics International Conference 2026 (SAFE2026)</t>
+          <t>Conference on CSR, the Economy and Financial Markets</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bandar Sunway, Malaysia</t>
+          <t>Düsseldorf, Germany</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>€ 150 for regular participants and € 100 for PhD students</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sustainability-oriented research in accounting, finance, and economics</t>
+          <t>Climate risk and pricing, Role of financial markets, banks, institutional investors in CSR, Effects of CSR on valuation, performance, cost of capital, funding and capital structure, Socio-economic aspects and their implications for companies and financial markets, Corporate governance and CSR, Risk management and CSR, CSR reporting and disclosure, ESG backlash and politicization, Sustainability strategy under new constraints, Measurement: information content and reliability of ESG indices, CSR activities and the economy</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026 Climate Finance &amp; Policy (CFP-2026)</t>
+          <t>International Conference in Banking and Financial Studies 2026 (ICBFS 2026)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bari, Italy</t>
+          <t>Parma, Italy</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No submission fee</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>AI-driven Climate Risk Assessment and Prediction, Big Data and ESG Decision-making, Carbon Border Adjustment Mechanisms, Carbon Finance and Pricing, Climate Change and Corporate Behavior, Climate Finance for Energy Efficiency, Carbon Taxes, Climate Agreements and Frameworks, Climate Funds and Public Finance, Climate Risk Assessment and Disclosure, ESG Measurement, Ratings &amp; Data Quality, Financing Climate Adaptation and Resilience, Green Finance, Green Bonds and Socially Responsible Bonds, Just Transition, Nature, Biodiversity &amp; Finance, Role of Technology in Climate Finance, Sustainable Investing, Sustainability Regulation &amp; Political Economy</t>
+          <t>Accounting, auditing, and taxation; Asset allocation and valuation; Banking regulation and financial services; Behavioral and experimental finance/economics; Big data in finance, artificial intelligence, and cybersecurity; Climate finance and sustainability; Corporate finance, IPOs, SEOs, M&amp;A, and crowdfunding; Corporate governance; Country funds, sovereign funds, and hedge funds; Debt markets and instruments; Digital finance, cryptocurrencies, and blockchain; Emerging markets finance; Energy finance and environmental issues; Entrepreneurial finance, venture capital, and private equity; Ethical finance, green finance, ESG, and CSR; Financial accounting and regulation; Financial crises, contagion, integration, and global risk interconnections; Financial engineering and derivatives; Foreign exchange markets and currency issues; Global imbalances and sustainability; Household finance, real estate finance, and microfinance; Market efficiency and behavior; Multinational financial management; Portfolio management and optimization; Risk management and compliance; Small business finance</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026 Global AI Finance Research Conference</t>
+          <t>Colorado Finance Summit 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Taipei, Taiwan</t>
+          <t>Vail, Colorado</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1485,108 +1485,108 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Artificial Intelligence (AI), Big Data and Machine Learning, Blockchain and Cryptocurrencies, Security Token Offerings (STOs) and Initial Coin Offerings (ICOs), Decentralized Finance (DeFi), Peer-to-peer lending, FinTech regulation, High-frequency trading and market liquidity, Green FinTech</t>
+          <t>All areas of finance, theoretical and empirical contributions</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>37th Annual Conference of the Academy of Behavioral Finance &amp; Economics</t>
+          <t>18th Annual Hedge Fund Research Conference</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Santa Monica, California, USA</t>
+          <t>Université Paris Dauphine - PSL, Paris</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>$99.00</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Behavioral/Cognitive Finance &amp; Economics, Neuroscience/Neuromorphic Computing, Political Economy, Biological Anthropology, Brain-Computer Interfaces, Innovative models for decision making and risk taking, Decision Making under risk and uncertainty, Venture Startups &amp; Exits, Trust in Financial/Capital Markets, Financial Management, Entrepreneurship, Sustainable Finance, Behavioral Finance &amp; Economics in Retirement Saving &amp; Planning, Empirical Works in Behavioral Finance, Evidence-Based Financial Planning, Neuromorphic-based Strategies, Nudging Clients and Markets, Behavioral/Cognitive Value Investing</t>
+          <t>Hedge funds, mutual funds, ETFs, private equity funds, institutional investors’ risks and performance, transparency (reporting) and due diligence, financial intermediation activity, hedge fund and broad macroeconomic issues such as systemic risk and contagion, institutional investors’ incentives and activism, portfolio liquidation and liquidity, financial regulation, private equity funds, ETFs</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026 UNSW Asset Pricing Workshop</t>
+          <t>15th LaBS International Banking Workshop</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sydney (NSW, Australia)</t>
+          <t>HSE University and online</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0 AUD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>All areas of Finance, with a special focus on Asset Pricing</t>
+          <t>Banking in Emerging Markets: Challenges and Opportunities, theoretical and empirical research in all fields of Banking or Household finance</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>International Conference in Venice - Artificial Intelligence, Financial Innovation and Credit Risk</t>
+          <t>Private Equity Research Consortium (PERC) Symposium</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Venice, Italy</t>
+          <t>Chapel Hill, NC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1596,71 +1596,71 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Credit Risk and Advanced Analytics, AI- and machine learning-based credit risk models, Explainable AI (XAI) and model transparency in credit scoring, Stress testing, early warning systems and credit cycle analysis, Credit risk under macroeconomic, financial and geopolitical uncertainty, Financial Innovation and Digital Transformation, FinTech, BigTech and new models of credit intermediation, Open banking, open finance and alternative data in credit markets, Innovation in credit markets, securitization and risk transfer, Regulation of financial innovation, Artificial Intelligence, Data Governance and Ethical Risk, Algorithmic bias, fairness and discrimination in credit decisions, Data governance, privacy and cybersecurity in credit systems, Legal accountability and responsibility of AI-driven models, Regulatory implications of AI adoption in financial services, Sustainability and Long-Term Value Creation, ESG factors and climate risk in credit assessment, Sustainable finance and its impact on credit risk and pricing, Credit, access to finance and financial inclusion, The role of financial institutions in supporting the sustainable transition, Systemic Risk, Resilience and Policy Interactions between credit risk and systemic risk, Financial stability in a data-driven and AI-enabled economy, Macroprudential and microprudential policy responses, Coordination between regulators, supervisors and market participants</t>
+          <t>Private equity, buyouts, distressed securities, mezzanine financing, special situations, private credit, venture capital, real estate, real assets</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>36th Annual Conference on Financial Economics and Accounting (CFEA)</t>
+          <t>IMRC 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Toronto, Ontario (Canada)</t>
+          <t>IIM Ahmedabad</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>100 CAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Financial economics and accounting</t>
+          <t>Theoretical and Empirical Asset Pricing, Quality of Financial Reporting and Adoption of IFRS, Market Microstructure and Algorithmic Trading, Insurance / Reinsurance / Pension Funds, Business Cycles, Corporate Finance, Capital Structure and Dividend Policy, Financial Policy Choice, Institutions and Regulation, Enhancing Liquidity in Commodity Derivatives Markets, Public Economics, Asset Allocation and Investment Management, Computational Finance and Financial Econometrics, FDI and Portfolio Capital Flows, Household Finance, International Trade and Exchange Rates, Financial Crises, Systemic Risk and Macro-Finance, Financial Risk Analytics and Management, Financial Analytics, Monetary Policy and Banking, Global Value Chains and Firm Performance, Macroeconomics, Applied Microeconomics</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026 Lugano Real Estate and Urban Economics Conference</t>
+          <t>2026 New Zealand Finance Meeting</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lugano, Switzerland</t>
+          <t>Auckland, New Zealand</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1670,108 +1670,108 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Real estate economics, real estate finance, regional economics, urban economics</t>
+          <t>All topics related to the field of finance</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Santiago Finance Workshop 2026</t>
+          <t>6th Conference on Corporate Policies and Asset Prices (COAP)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Universidad de Chile, Diag. Paraguay 257, Santiago, Chile</t>
+          <t>Nice, France</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>€50</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Any topic in finance or financial economics</t>
+          <t>asset pricing anomalies and their explanations; corporate finance models of asset pricing anomalies; dynamic corporate finance and contracting models and their asset pricing implications; the asset pricing implications of sustainable finance; feedback effects from asset prices to corporate decisions; structural estimation of dynamic models using asset price data</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4th International Conference on Circular Economy, Business Strategy &amp; Management</t>
+          <t>5th Contemporary Issues in Financial Markets and Banking</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2027-02-10</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2027-02-11</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>EM Normandie Business School, Caen campus, France</t>
+          <t>Online Conference</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>USD 175</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>sustainability, ESG, innovation, resilience, circular business models, future of management research</t>
+          <t>Financial resilience; Green, climate and sustainable finance; Decentralised finance and disruptive financial technologies; Theoretical asset pricing; Empirical asset pricing, liquidity and behavioural economics and finance; Risk management; Financial inclusion; Alternative investments; Crowd-funding; Islamic banking; Banking and financial sector stability and regulation; Financial (dis)integration and Brexit; Artificial intelligence, machine and deep learning applications in finance; Corporate finance and sustainable energy financing; Crisis investment and portfolio management; Corporate governance; International financial management and investment; Market microstructure; Household finance; Real estate and property markets; Metaverse and Blockchain technologies in finance; Intersection between finance and economic theory, especially financial applications of game theory, decision theory, and computational financial economics; experimental economics with implications for financial theory and practice.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Climate Finance &amp; Sustainability Conference</t>
+          <t>International Conference on Trade Wars, Geopolitical Fragmentation and Repercussions for Financial and Monetary Stability</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Montréal, QC, Canada</t>
+          <t>Brunel University of London (UK)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sustainability in business, multi-stakeholder governance, managing business impacts on planetary boundaries, ESG factors, sustainability reporting, regulatory competition, climate finance, role of artificial intelligence in sustainability, sustainable business models, responsible consumption, operational resilience, and sustainable supply chain management</t>
+          <t>Art of the (trade) deal and financial costs, Asymmetric impacts on regions, commodity exporters, service-oriented economies and manufacturing centres, Capital flows and sudden stops due to trade wars, Central Banking in the age of trade wars and geopolitical conflicts, Central bank digital currencies (CBDCs), trade wars and geopolitical tensions, Currency weaponisation, competitive devaluation and financial instability, Digitisation, financial decoupling and financial stability during trade conflicts, Emerging markets and international financial flows under trade tensions, Empirical and theoretical analyses of strategic financial policies under trade restrictions, Exorbitant privilege of the US$ in the 21st century and the rise of alternative currencies, European Economic and Monetary Union’s financial integration with the US and the Global South, Financialization in the context of trade wars, Global financial imbalances, causes and financial consequences in the context of trade wars, International financial and monetary architecture and stress management in the age of trade conflict, Inflation targeting, trade wars and geopolitical conflicts, Productivity, innovation and efficiency related to technological spillovers and protectionism, Reallocation of global capital, safe havens and asset price bubbles during trade conflicts, Regional financial and monetary integration and the positive role of regions during trade conflicts, Role of central banks and macroprudential policy during trade conflicts, Sustainable financial development of the Global South and trade wars, Tariffs and non-tariff barriers and their negative financial impact on markets and firms</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>China Accounting and Finance Review (CAFR) Special Issue Conference 2026</t>
+          <t>Labor &amp; Finance Group Fall 2026 Conference</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Zhongnan University of Economics and Law, Wuhan, China</t>
+          <t>Penn State University – Smeal College of Business, State College, PA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1818,71 +1818,71 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>ESG in the AI Era: Challenges and Opportunities, AI-Driven ESG Reporting and Assurance, Algorithmic Bias, Ethics, and Fairness in ESG Analytics, Regulatory Responses to AI-Enabled ESG Practices, AI, Greenwashing, and Corporate Accountability, AI for Sustainable Finance and Investment Decision-Making</t>
+          <t>Human capital, compensation, and incentives; Labor market power, monopsony/oligopsony, and wage setting; Unions, collective bargaining, and worker representation; Organizational design, internal labor markets, and corporate governance; Labor mobility, non-compete agreements, and talent flows; Labor-related disclosure, regulation, and policy; Labor and financial markets, asset pricing, and corporate policies; Entrepreneurship and innovation</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026 FMA Asia/Pacific Conference</t>
+          <t>CUHK-RAPS-RCFS Conference on Asset Pricing and Corporate Finance</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Massey University, Auckland, New Zealand</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>$50 USD (FMA-members), $60 USD (non-members)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Financial decision-making, financial management, current issues in finance</t>
+          <t>Asset Pricing, Corporate Finance</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sixth Biennial Conference on Auto Lending</t>
+          <t>2026 ABFER-JFDS Conference on AI for Finance</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Philadelphia</t>
+          <t>International Institute of Finance, No. 1789 Guangxi Road, Hefei, Anhui, China</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1892,34 +1892,34 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Auto lending, consumer finance, loan pricing, contract design, underwriting, credit risk modeling, dealer intermediation, borrower outcomes, fraud, fair lending, subprime market structure, repossession, servicing, alternative data, electric vehicles, used vehicle prices, auto insurance, fintech, auto asset-backed securities, monetary policy spillovers</t>
+          <t>Applications of artificial intelligence, machine learning, natural language processing, large language models, AI agents, high-performance computing; Use of unstructured and alternative data in investment, auditing, assurance; Social and economic impacts of AI adoption; Ethical, governance, and regulatory considerations of AI in finance; Quantitative investment strategies, portfolio optimization, digital assets, DeFi, and platform finance using machine learning technologies</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Frontiers in Machine Learning and Economics: Methods and Applications</t>
+          <t>Financial Economics Meeting</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Philadelphia</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1929,34 +1929,34 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Methodological advances in analyzing complex and high-dimensional data sets, Methodological advances in natural language processing (particularly with respect to causal inference), Innovative applications of generative AI, The societal impacts of AI and algorithmic decision-making</t>
+          <t>Financial markets &amp; asset pricing, Banking, credit &amp; financial stability, Macroeconomics &amp; international finance, Sustainable finance &amp; climate risk, Quantitative methods &amp; emerging approaches</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Workshop on Innovations in Credit Scoring</t>
+          <t>39th Australasian Finance and Banking Conference</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Virtual</t>
+          <t>Sydney, Australia</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1966,34 +1966,34 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Innovations in credit scoring, alternative data, artificial intelligence, machine learning, risk management, credit access</t>
+          <t>Opportunities and Risks of AI Technology in Finance, CBDCs, Fintech, and Digital Finance, Sustainable Investment</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026 Conference on Real-Time Data Analysis, Methods, and Applications</t>
+          <t>Finance at a Time of Change and Uncertainty</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Philadelphia</t>
+          <t>Renmin University of China, Beijing, China</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2003,34 +2003,34 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>monitoring and forecasting of economic and financial developments, high-frequency data, survey data, text as data, transactions data, granular data, using preliminary and revised data in economic policy formulation and analysis, machine learning applications in real-time macroeconomics, probabilistic forecasts and assessments of crisis risks, related innovative data sets and toolboxes, seasonal and cyclical adjustment for real-time monitoring and forecasting</t>
+          <t>Finance and AI, Finance and politics, Finance and climate change</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026 Jacobs Levy Center Frontiers in Quantitative Finance Conference</t>
+          <t>MIT GCFP 13th Annual Conference</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>Cambridge, MA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2040,145 +2040,145 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>quantitative methods and asset pricing</t>
+          <t>Financial regulation in an era of innovation and disruption, AI’s impact on financial markets, labor markets, and the economy; investor protection and fair lending; new risks to financial stability; changing market structure for equities, bonds, and derivatives; growth of event contracts and prediction markets; growth of non-bank credit; developments in stablecoins, digital currencies, and payment systems; risks in “safe” assets such as sovereign debt; international coordination and comparisons; innovations in market architecture and infrastructure.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>34th Annual PBFEAM and 20th NYCU International conferences</t>
+          <t>EUROFIDAI-ESSEC Paris December Finance Meeting</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>National Yang Ming Chiao Tung University, Hsinchu, Taiwan</t>
+          <t>Pullman Paris Montparnasse Hotel</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>USD $250 (On-line Presenter), USD $300 (On-site Presenter)</t>
+          <t>75€</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>All areas of finance</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026 AIM Investment Conference</t>
+          <t>Chicago Fed/University of Chicago Conference on Municipal Bond Markets</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Austin, Texas</t>
+          <t>Federal Reserve Bank of Chicago</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>75 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>mutual funds, hedge funds, pension funds, investment management</t>
+          <t>Unpublished and highly policy-relevant research papers on municipal bond markets, primary market frictions, secondary market frictions, role of retail investors, government policies targeting investors, effect of state and federal policies on access to external finance</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026 Wharton Conference on Liquidity and Financial Fragility</t>
+          <t>SFS Cavalcade Asia-Pacific 2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>University of Pennsylvania, Philadelphia, PA</t>
+          <t>City University of Hong Kong</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$75 USD</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Coordination failures, self-fulfilling beliefs, and runs; Fragility in banks and non-bank institutions; Liquidity and frictions in financial markets and macroeconomy; Systemic risk and financial regulation; Monetary policy and financial stability; Artificial intelligence (AI) and its implications for financial macroeconomic stability; The rise and potential risks in private credit markets; New payment technologies, stablecoins, tokenization, and their financial stability implications; Geopolitical tensions, trade conflicts, currency competition, and financial fragility; Inflation, interest rate risks, and implications on financial fragility; The real impact of crises and fragility on firms’ financing and investment policies</t>
+          <t>In-depth participation in financial studies, asset pricing, corporate finance</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Towards a New Synthesis in Islamic Finance: Law, Economics and Shari’ah</t>
+          <t>Sustainable Accounting, Finance and Economics International Conference 2026 (SAFE2026)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Online Conference from Durham University, England, UK</t>
+          <t>Bandar Sunway, Malaysia</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2188,14 +2188,14 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Islamic finance, financial innovation, regulatory oversight, governance mechanisms, economic development, sustainability, social equity, inclusive economic development</t>
+          <t>Sustainability-oriented research in accounting, finance, and economics</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>74th Meeting of the EURO Working Group for Commodities and Financial Modelling (EWGCFM)</t>
+          <t>2026 Climate Finance &amp; Policy (CFP-2026)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2205,17 +2205,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Casa de Campo, La Romana, Dominican Republic</t>
+          <t>Bari, Italy</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2225,34 +2225,34 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Asset Pricing, Corporate Finance, Banking and Financial Institutions, Commodities and Energy Markets, Financial Modelling and Econometrics, Blockchain and Cryptocurrencies, Derivatives and Risk Management, Market Microstructure, Sustainable Finance</t>
+          <t>AI-driven Climate Risk Assessment and Prediction, Big Data and ESG Decision-making, Carbon Border Adjustment Mechanisms, Carbon Finance and Pricing, Climate Change and Corporate Behavior, Climate Finance for Energy Efficiency, Carbon Taxes, Climate Agreements and Frameworks, Climate Funds and Public Finance, Climate Risk Assessment and Disclosure, ESG Measurement, Ratings &amp; Data Quality, Financing Climate Adaptation and Resilience, Green Finance, Green Bonds and Socially Responsible Bonds, Just Transition, Nature, Biodiversity &amp; Finance, Role of Technology in Climate Finance, Sustainable Investing, Sustainability Regulation &amp; Political Economy</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FIRN 2026 ANU Money, Credit, and Financial Stability Meeting</t>
+          <t>2026 Global AI Finance Research Conference</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Australian National University (ANU), Canberra, Australia</t>
+          <t>Taipei, Taiwan</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2262,71 +2262,71 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Monetary policy and transmission mechanisms, Credit markets and financial intermediation, Banking, liquidity, and regulation, Financial crises and systemic risk, Macro-finance</t>
+          <t>Artificial Intelligence (AI), Big Data and Machine Learning, Blockchain and Cryptocurrencies, Security Token Offerings (STOs) and Initial Coin Offerings (ICOs), Decentralized Finance (DeFi), Peer-to-peer lending, FinTech regulation, High-frequency trading and market liquidity, Green FinTech</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Inaugural Annual Conference on Insurance</t>
+          <t>37th Annual Conference of the Academy of Behavioral Finance &amp; Economics</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Chicago</t>
+          <t>Santa Monica, California, USA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$99.00 USD</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Life insurance, Property &amp; Casualty insurance, Reinsurance and risk transfer, Mergers and other ownership changes, Private equity ownership and impact on industry, Indexed, variable annuities, and other savings products, Household insurance choices, Insurances’ investment and funding strategies, Catastrophe risk, Impact of insurance regulation</t>
+          <t>Behavioral/Cognitive Finance &amp; Economics, Neuroscience/Neuromorphic Computing, Political Economy, Biological Anthropology, Brain-Computer Interfaces, Development of New Financial &amp; Economic Models, Decision Making under risk and uncertainty, Venture Startups &amp; Exits, Financial Markets, Financial Management of Companies, Entrepreneurship, Innovation, Sustainable Finance, Personal Finance, Behavioral Finance applications, Evidence-Based Financial and Retirement Planning, Behavioral/Cognitive Value Investing</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Payments, Digital Assets, AI and the Future of Financial Markets</t>
+          <t>2026 UNSW Asset Pricing Workshop</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Imperial Business School, London</t>
+          <t>Sydney (NSW, Australia)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2336,34 +2336,34 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Digital platforms, banking, and financial intermediation; Artificial intelligence, machine learning, and financial decision-making; Blockchain, tokenization, digital assets, and decentralized finance; Payment systems, central bank digital currencies, and stablecoins; FinTech regulation, supervision, market design, and financial stability; Data, privacy, cybersecurity, and consumer protection in finance; Entrepreneurial finance, venture capital, and innovation in financial services; Household finance, inclusion, and welfare effects of financial technology; Market microstructure, trading technologies, and liquidity; Competition between banks, platforms, and non-bank financial institutions</t>
+          <t>All areas of Finance, with a special focus on Asset Pricing</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026 Conference on Auditing and Capital Markets</t>
+          <t>International Conference in Venice - Artificial Intelligence, Financial Innovation and Credit Risk</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Washington, DC</t>
+          <t>Venice, Italy</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2373,71 +2373,71 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Economic impact of auditing, audit regulation, audit oversight on capital markets</t>
+          <t>Credit Risk and Advanced Analytics; Financial Innovation and Digital Transformation; Artificial Intelligence, Data Governance and Ethical Risk; Sustainability and Long-Term Value Creation; Systemic Risk, Resilience and Policy</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Future Scholars in Finance Forum</t>
+          <t>36th Annual Conference on Financial Economics and Accounting (CFEA)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Beijing, China</t>
+          <t>Toronto, Ontario (Canada)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>100 CAD</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>All areas of finance</t>
+          <t>Financial economics and accounting</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Prototypes for Humanity 2026 Short Papers Platform</t>
+          <t>2026 Lugano Real Estate and Urban Economics Conference</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dubai, UAE</t>
+          <t>Lugano, Switzerland</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2447,34 +2447,34 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Wellbeing and Human Performance, Infrastructures and Cities, Autonomous Systems and Advanced Manufacturing, Environment, Sustainability and Energy, Mobility and Logistics, Socio-Economic Empowerment, Digital Economies and Future Markets, Open and Speculative</t>
+          <t>real estate economics, real estate finance, regional economics, urban economics</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026 Federal Reserve Stress Testing Research Conference</t>
+          <t>Santiago Finance Workshop 2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Boston, Massachusetts</t>
+          <t>Universidad de Chile, Diag. Paraguay 257, Santiago, Chile</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2484,34 +2484,34 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>The economic and macroprudential effects of stress tests and bank regulation, Novel approaches to modeling bank profitability, financial risks, and operational risks, Design and applications of stress scenarios and reverse stress testing, Nonbank credit intermediation, such as from nonbank financial institutions, private credit, business development companies, and their interactions with stress testing, Financial instruments for risk transfer, such as hedges and synthetic securitizations, and their implications, Recent developments in bank regulation, The impact of emerging technologies on banks and their regulators</t>
+          <t>Any topic in finance or financial economics</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EBA's 15th Policy Research Workshop</t>
+          <t>4th International Conference on Circular Economy, Business Strategy &amp; Management</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>EBA premises (Paris, France) and remotely</t>
+          <t>EM Normandie Business School, Caen campus, France</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2521,34 +2521,34 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Competitiveness and efficiency in the prudential rulebook without undermining resilience; Impacts of efficiency and proportionality; Competition, innovation, market entry, cross border growth and new areas under financial supervision; Proportionate integration of ESG risks in governance, strategy, and remuneration frameworks</t>
+          <t>sustainability, ESG, innovation, resilience, circular business models, future of management research</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Financial Fraud, Misconduct and Market Manipulation Conference</t>
+          <t>Climate Finance &amp; Sustainability Conference</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Lancaster University, England</t>
+          <t>Montréal, QC, Canada</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2558,34 +2558,34 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Theoretical and empirical analysis of financial fraud, Case studies of recent instances of market misconduct, Insider trading, Implication of financial fraud/market manipulation for market efficiency, stability, and asset pricing, Market manipulation at a high-frequency (intraday) level, Fraudulent activities and crypto currency markets, Social networks, fake news, and their effect on financial markets, Money laundering and banking, Conflicts of interests and their implications for various stakeholders and financial markets, Hedge funds/Mutual funds and their involvement in market misconduct, Statistical/ Machine Learning methods for fraud detection, Cyber security and cyber risk management, Regulatory response to financial misconduct, Unintended consequences of politics and regulations</t>
+          <t>Sustainability in business, multi-stakeholder governance, managing business impacts on planetary boundaries, ESG factors, sustainability reporting, climate finance, AI in business sustainability, sustainable business models, responsible consumption, operational resilience, sustainable supply chain management</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>22nd Annual Haskell &amp; White Corporate Reporting and Governance Conference</t>
+          <t>China Accounting and Finance Review (CAFR) Special Issue Conference 2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>California State University, Fullerton</t>
+          <t>Zhongnan University of Economics and Law, Wuhan, China</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2595,108 +2595,108 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>All areas of accounting and finance, corporate reporting, governance, financial markets</t>
+          <t>ESG in the AI Era: Challenges and Opportunities; AI-Driven ESG Reporting and Assurance; Algorithmic Bias, Ethics, and Fairness in ESG Analytics; Regulatory Responses to AI-Enabled ESG Practices; AI, Greenwashing, and Corporate Accountability; AI for Sustainable Finance and Investment Decision-Making</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>25th Annual Bank Research Conference</t>
+          <t>2026 FMA Asia/Pacific Conference</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Arlington, VA</t>
+          <t>Massey University, Auckland, New Zealand</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$50 USD (FMA-members), $60 USD (non-members)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Regulatory reform options and considerations, Risk and resiliency in the financial system, Real effects of financial turmoil, Innovations in financial intermediation, Deposit insurance and stability, Emerging competitive threats to traditional banking, AI and technology in finance, Banks’ role in the 21st Century</t>
+          <t>Financial decision-making, financial management, current issues in finance</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>The Future of Decision-Making and Risk-Taking: Bridging Finance, Economics, Brain, and Behavior</t>
+          <t>Sixth Biennial Conference on Auto Lending</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Santa Monica, California, USA</t>
+          <t>Federal Reserve Bank of Philadelphia</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>$99.00</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Behavioral/Cognitive Finance &amp; Economics, Neuroscience/Neuromorphic Computing, Political Economy, Biological Anthropology, Brain-Computer Interfaces, Development of New Financial &amp; Economic Models, Decision Making under risk and uncertainty, Venture Startups &amp; Exits, Trust in Financial Markets, Personal Finance, and Behavioral Finance applications.</t>
+          <t>Consumer demand and vehicle choice, loan pricing and contract design, underwriting and credit risk modeling, dealer intermediation and markups, borrower outcomes and delinquency dynamics, fraud and identity risk, fair lending and consumer compliance, subprime and near-prime market structure, repossession and loss mitigation, servicing and collections, the role of alternative data and automated decisioning, electric vehicles and evolving collateral risk, used vehicle prices and depreciation, auto insurance interactions, fintech and market structure, auto asset-backed securities, spillovers from monetary policy and macroeconomic shocks.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>17th Emerging Markets Conference</t>
+          <t>Frontiers in Machine Learning and Economics: Methods and Applications</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Mumbai, India</t>
+          <t>Federal Reserve Bank of Philadelphia</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2706,34 +2706,34 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>The sources of economic success or failure in EMs, Finance in EMs (households, financial markets, financial intermediaries, firms and finance, finance and growth), Political economy, law, public administration, regulation in EMs, The impact of populism upon the possibility of sustained growth, Insights into large EMs that matter in and of themselves, Insights from narrow research projects that illuminate EMs in general, The new phase of globalisation and its consequences for international trade, international finance and the nature of the EM firm, Features of a society that enable or disable convergence into the “normal” package of high levels of freedom and prosperity, The puzzles faced by all kinds of decision makers: individuals, civil society actors, firms, all levels of government, Grand challenges such as climate change: implications for EMs and ramifications of choices made in EMs, State capability in EMs, The interplay of military affairs, foreign policy and economics for EMs</t>
+          <t>Methodological advances in analyzing complex and high-dimensional data sets; Methodological advances in natural language processing, particularly with respect to causal inference; Innovative applications of generative AI; The societal impacts of AI and algorithmic decision-making</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026 International Forum on Financial Regulation and RegTech</t>
+          <t>Workshop on Innovations in Credit Scoring</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Beihang University, Beijing, China</t>
+          <t>Virtual</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2743,34 +2743,34 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Financial Regulation &amp; RegTech Innovation, Risk Assessment &amp; Management, AI, LLMs &amp; Financial Infrastructure</t>
+          <t>Innovations in credit scoring, alternative data, artificial intelligence, machine learning, data privacy in risk management, credit access</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026 International Symposium on Climate, Finance, and Sustainability (ISCFS-2026)</t>
+          <t>2026 Conference on Real-Time Data Analysis, Methods, and Applications</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>House of Management Science, Paris Pantheon-Assas University, 1 rue Guy-de-la-Brosse 75005 Paris, France</t>
+          <t>Federal Reserve Bank of Philadelphia</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2780,108 +2780,108 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbon Finance and Taxes, Climate and Economic Modeling in Policy Making, Climate Finance, Climate Negotiations and Scenarios, Climate Risk and Disclosures, Climate-resilient Economies, Energy Derivatives: Pricing and Hedging, Energy Markets: Modeling and Forecasting, Energy, Environment, and Climate Models, Financial and Economic Analysis of Energy Markets, Financial Regulation of Energy and Environmental Markets, Green Finance and Sustainable Investment, Just Energy Transition, Macroeconomic Implications of Net-Zero Carbon Emissions, Nature-based Financial Instruments for Climate Change Mitigation, Natural Resources, Risk, Welfare, and Social Preferences, Renewable Energy, Regulation and Energy Governance, Role of Financial Institutions in Sustainability</t>
+          <t>monitoring and forecasting of economic and financial developments, high-frequency data, survey data, text as data, transactions data, granular data, using preliminary and revised data in economic policy formulation and analysis, machine learning applications in real-time macroeconomics, probabilistic forecasts and assessments of crisis risks, related innovative data sets and toolboxes, seasonal and cyclical adjustment for real-time monitoring and forecasting</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5th Annual Academic - 2026 DeFi &amp; Digital Currencies Conference</t>
+          <t>2026 Jacobs Levy Center Frontiers in Quantitative Finance Conference</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>The Shard, London, UK</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>£45</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>DeFi Protocols, Lending and Borrowing Protocols, Decentralized Exchanges, Blockchain Economics, Stablecoins and CBDCs, Digital Money and Payments, Tokenisation of real-world assets, Traditional and Decentralized Finance Interaction, Digital Finance and Inclusion</t>
+          <t>quantitative methods and asset pricing</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3rd Arne Ryde Conference on Crypto, Fintech and Payments</t>
+          <t>2026 AIM Investment Conference</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Lund, Sweden</t>
+          <t>Austin, Texas</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>75 USD</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Crypto and blockchain technology, Crypto markets, households, and the real economy, Environmental and social impact of crypto markets, Interaction between traditional finance and decentralized finance, Stablecoins, Central Bank Digital Currencies (CBDCs), Financial technology (Fintech), Payment systems, Open banking and data sharing, Digital tools in financial services, Financial inclusion, development, and welfare in digital finance</t>
+          <t>mutual funds, hedge funds, pension funds, investment management</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Institute for Quantitative Investment Research Autumn Residential Seminar 2026</t>
+          <t>2026 Wharton Conference on Liquidity and Financial Fragility</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Ashdown Park Hotel &amp; Country Club, Wych Cross, East Sussex, UK</t>
+          <t>University of Pennsylvania, Philadelphia, PA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2891,34 +2891,34 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>New risks in a changing political environment; papers relevant to investment practitioners</t>
+          <t>Coordination failures, self-fulfilling beliefs, and runs; Fragility in banks and non-bank institutions; Liquidity and frictions in financial markets and macroeconomy; Systemic risk and financial regulation; Monetary policy and financial stability; Artificial intelligence (AI) and its implications for financial macroeconomic stability; The rise and potential risks in private credit markets; New payment technologies, stablecoins, tokenization, and their financial stability implications; Geopolitical tensions, trade conflicts, currency competition, and financial fragility; Inflation, interest rate risks, and implications on financial fragility; The real impact of crises and fragility on firms’ financing and investment policies</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10th Shanghai-Edinburgh-London Finance Conference On Sustainable Finance in the Digital Era</t>
+          <t>Towards a New Synthesis in Islamic Finance: Law, Economics and Shari’ah</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Shanghai and online</t>
+          <t>Online Conference from Durham University, England, UK</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2928,34 +2928,34 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Financial development, financial inclusion and their role in sustainable economic growth; Policy frameworks and regulatory challenges shaping sustainable finance adoption in developed and emerging markets; Cross-border sustainable finance flows and international regulatory coordination; Corporate governance, greenwashing detection, and market responses to ESG commitments; ESG backlash, anti-ESG movements, and the political economy of sustainable finance; AI and machine learning applications in ESG investment strategies, sustainability disclosure, and climate risk modelling; Big data and natural language processing in measuring and monitoring ESG performance; Blockchain applications in carbon markets, green bonds, and regulatory compliance; Digital finance, decentralised finance (DeFi), and emerging technologies in supporting a low-carbon transition; Fintech-enabled green lending, climate insurance, and impact investing.</t>
+          <t>Islamic finance, financial development and stability, cultural perspectives, economic perspectives, legal perspectives, Shari’ah perspectives, financial innovation, regulatory oversight, governance mechanisms, economic development, sustainability, social equity, inclusive economic development</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>22nd Annual Conference of the Asia-Pacific Association of Derivatives</t>
+          <t>74th Meeting of the EURO Working Group for Commodities and Financial Modelling (EWGCFM)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Busan, Korea</t>
+          <t>Casa de Campo, La Romana, Dominican Republic</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2965,71 +2965,71 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Derivatives; Volatility; Risk Management; Asset Pricing; Investments; Corporate Finance; Market Microstructure; Fintech; Regulation; Behavioral Finance</t>
+          <t>Asset Pricing, Corporate Finance, Banking and Financial Institutions, Commodities and Energy Markets, Financial Modelling and Econometrics, Blockchain and Cryptocurrencies, Derivatives and Risk Management, Market Microstructure, Sustainable Finance</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FIRN Melbourne Asset Pricing Meeting</t>
+          <t>FIRN 2026 ANU Money, Credit, and Financial Stability Meeting</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Melbourne, Australia</t>
+          <t>Australian National University (ANU), Canberra, Australia</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>0 AUD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>theoretical and empirical models of asset prices and returns, return predictability, empirical methodology, macro-finance, the study of financial institutions as related to asset prices, information and liquidity in asset markets, behavioural investment studies, asset market structure and microstructure, risk analysis, hedge funds, mutual funds, pension funds, ESG, and alternative investments</t>
+          <t>Monetary policy and transmission mechanisms, Credit markets and financial intermediation, Banking, liquidity, and regulation, Financial crises and systemic risk, Macro-finance</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Johns Hopkins Carey Finance Conference</t>
+          <t>Inaugural Annual Conference on Insurance</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Johns Hopkins Carey Business School, 100 International Drive, Baltimore, MD</t>
+          <t>Federal Reserve Bank of Chicago</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3039,71 +3039,71 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>All areas of finance, particularly early-stage papers that would benefit from feedback and discussion</t>
+          <t>life insurance, Property &amp; Casualty insurance, Reinsurance and risk transfer, Mergers and other ownership changes, Private equity ownership and impact on industry, Indexed, variable annuities, and other savings products, Household insurance choices, Insurances’ investment and funding strategies, Catastrophe risk, Impact of insurance regulation</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>5th Holden Conference in Finance and Real Estate</t>
+          <t>Payments, Digital Assets, AI and the Future of Financial Markets</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bloomington, IN</t>
+          <t>Imperial Business School, London</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>$95 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Empirical and theoretical papers in all finance and real estate areas</t>
+          <t>Digital platforms, banking, and financial intermediation; Artificial intelligence, machine learning, and financial decision-making; Blockchain, tokenization, digital assets, and decentralized finance; Payment systems, central bank digital currencies, and stablecoins; FinTech regulation, supervision, market design, and financial stability; Data, privacy, cybersecurity, and consumer protection in finance; Entrepreneurial finance, venture capital, and innovation in financial services; Household finance, inclusion, and welfare effects of financial technology; Market microstructure, trading technologies, and liquidity; Competition between banks, platforms, and non-bank financial institutions</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>12th P2P Financial Systems International Workshop (P2PFISY 2026)</t>
+          <t>2026 Conference on Auditing and Capital Markets</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Astana, Kazakhstan</t>
+          <t>Washington, DC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3113,71 +3113,71 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Regulation &amp; Compliance in Digital Asset Markets, Fraud, Financial Crime &amp; Forensics in Crypto Markets, CBDCs and Digital Public Infrastructure, Stablecoins and Digital Payment Systems, Artificial Intelligence in Financial Systems, Consumer Protection, Data Governance, and Trust in Digital Finance, Tokenisation of Real-World Assets (RWA)</t>
+          <t>Economic impact of auditing, audit regulation, audit oversight on capital markets, auditing issuers and brokers and dealers</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026 Annual Community Bank Research Conference</t>
+          <t>Future Scholars in Finance Forum</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of St. Louis in St. Louis, MO</t>
+          <t>Beijing, China</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>0 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>The role of community banks in the U.S. financial system, the provision of financial services to households, small businesses, and small farms, impact of community banks on local/state economic activity, community banks’ response to financial and economic shocks and the associated policy responses, the effects of regulatory policy on community banks, quantifying regulatory and compliance costs, intended and unintended effects of regulatory requirements, antitrust policy and community banks, challenges and opportunities faced by community banks, competition from large banks, credit unions, and nonbanks including financial technology firms, funding and liquidity issues, collaborations/partnerships with financial technology and crypto firms, payments issues, the effects of rapid technological advances in banking, operational risk, advantages and disadvantages of the community bank business model, bank consolidation, noninterest/fee income, benefits of local knowledge and strong relationships, costs of operating at a small scale.</t>
+          <t>All areas of finance</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Stigler Center-CEPR Political Economy of Finance Conference 2026: Crony Capitalism in 21st Century America</t>
+          <t>Prototypes for Humanity 2026 Short Papers Platform</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Gleacher Center - Chicago</t>
+          <t>Dubai, UAE</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3187,71 +3187,71 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Crony capitalism in 21st century America</t>
+          <t>Wellbeing and Human Performance, Infrastructures and Cities, Autonomous Systems and Advanced Manufacturing, Environment, Sustainability and Energy, Mobility and Logistics, Socio-Economic Empowerment, Digital Economies and Future Markets, Open and Speculative</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>15th Fixed Income and Financial Institutions (FIFI) Conference</t>
+          <t>2026 Federal Reserve Stress Testing Research Conference</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>University of South Carolina in Columbia, SC</t>
+          <t>Boston, Massachusetts</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>75 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>fixed income, commercial and investment banks, asset management and mutual fund companies, short sellers, hedge funds, broker-dealers, insurance companies</t>
+          <t>The economic and macroprudential effects of stress tests and bank regulation, Novel approaches to modeling bank profitability, financial risks, and operational risks, Design and applications of stress scenarios and reverse stress testing, Nonbank credit intermediation, Financial instruments for risk transfer, Recent developments in bank regulation, The impact of emerging technologies on banks and their regulators</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Higher Education Finance Research Conference</t>
+          <t>EBA's 15th Policy Research Workshop</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Philadelphia</t>
+          <t>EBA premises (Paris, France) and remotely</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3261,71 +3261,71 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>financial aid, student debt, higher education finance</t>
+          <t>Competitiveness and efficiency in the prudential rulebook without undermining resilience, Impacts of efficiency and proportionality, Competition, innovation, market entry, cross border growth and new areas under financial supervision, Proportionate integration of ESG risks in governance, strategy, and remuneration frameworks</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Wharton–Chicago–Harvard Insolvency and Restructuring Conference (WCHIRC)</t>
+          <t>3rd Financial Fraud, Misconduct and Market Manipulation Conference</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>University of Pennsylvania, Philadelphia, PA</t>
+          <t>Lancaster University, England</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>0 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Corporate financial distress and bankruptcy, Liability management and out-of-court restructurings, Chapter 11 and formal reorganization processes, Consumer bankruptcy, Leveraged lending and private credit, Creditor governance and capital structure dynamics, Distressed debt markets and asset pricing, Financial contracting and covenant design, Bankruptcy law, courts, and institutional design, Operational restructuring and firm performance</t>
+          <t>Theoretical and empirical analysis of financial fraud, case studies of recent instances of market misconduct, insider trading, implications of financial fraud/market manipulation for market efficiency, stability, and asset pricing, market manipulation at a high-frequency (intraday) level, fraudulent activities and cryptocurrency markets, social networks, fake news, and their effect on financial markets, money laundering and banking, conflicts of interests and their implications for various stakeholders and financial markets, hedge funds/mutual funds and their involvement in market misconduct, statistical/machine learning methods for fraud detection, cyber security and cyber risk management, regulatory response to financial misconduct, unintended consequences of politics and regulations</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Financial Decision-Making Conference 2026</t>
+          <t>22nd Annual Haskell &amp; White Corporate Reporting and Governance Conference</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Bozeman, MT</t>
+          <t>California State University, Fullerton</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3335,108 +3335,108 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>household finance, financial literacy and education, consumer financial behavior, retirement and savings decisions, financial education interventions, fintech and digital finance, financial advice and delegation, debt and credit decisions, insurance decisions, behavioral finance, and financial inclusion</t>
+          <t>All areas of accounting and finance, corporate reporting, governance, and financial markets</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Finance and Real Estate Conference 2026</t>
+          <t>25th Annual Bank Research Conference</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Miami University, Oxford, OH</t>
+          <t>Arlington, VA</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>$50 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Asset pricing and valuation, Corporate finance, Real estate markets and investment, Risk management and financial regulation, Urban economics and housing policy, Sustainable and green finance, Behavioral finance</t>
+          <t>Regulatory reform options and considerations, Risk and resiliency in the financial system, Real effects of financial turmoil, Innovations in financial intermediation, Deposit insurance and stability, Emerging competitive threats to traditional banking, AI and technology in finance, Banks’ role in the 21st Century</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>UGA Fall Finance Conference 2026</t>
+          <t>The Future of Decision-Making and Risk-Taking: Bridging Finance, Economics, Brain, and Behavior</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Athens, GA</t>
+          <t>Santa Monica, California, USA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>70 USD</t>
+          <t>$99.00 USD</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>All areas of finance</t>
+          <t>Behavioral/Cognitive Finance &amp; Economics, Neuroscience/Neuromorphic Computing, Political Economy, Biological Anthropology, Brain-Computer Interfaces, Development of New Financial &amp; Economic Models, Advancing Knowledge and Understanding, Applications: Behavioral Finance in Practice</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Inquire Europe Autumn Conference: “Expectations and Asset Prices”</t>
+          <t>17th Emerging Markets Conference</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Prague, Czech Republic</t>
+          <t>Mumbai, India</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3446,88 +3446,88 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>deviations from rational expectations and their implications; optimism and pessimism in asset valuations and market dynamics; investment strategies and anomalies; factor investing; strategic and tactical asset allocation; portfolio choice under model and parameter uncertainty; short selling; institutional investing and asset management</t>
+          <t>The sources of economic success or failure in EMs, Finance in EMs, Political economy, law, public administration, regulation in EMs, The impact of populism upon the possibility of sustained growth, Insights into large EMs that matter, Insights from narrow research projects, The new phase of globalisation and its consequences, Features of a society that enable or disable convergence, The puzzles faced by decision makers, Grand challenges such as climate change, State capability in EMs, The interplay of military affairs, foreign policy and economics for EMs</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>WFE’s Sustainability Conference 2026</t>
+          <t>2026 International Forum on Financial Regulation and RegTech</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Beihang University, Beijing, China</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2000 CNY (Regular/Faculty), 1000 CNY (Student)</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Transition finance and market design, Regulatory fragmentation and divergence, Sustainability reporting, Nature and biodiversity in capital markets, Just transition, social and gender finance, Proportionality for SMEs and emerging markets, Carbon market architecture</t>
+          <t>Financial regulation, Regulatory Technology (RegTech), FinTech, financial security, risk assessment and management, AI and Large Language Models (LLMs) in finance</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026 FMA Annual Meeting</t>
+          <t>2026 International Symposium on Climate, Finance, and Sustainability (ISCFS-2026)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Tampa, FL</t>
+          <t>House of Management Science, Paris Pantheon-Assas University, France</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>$75 (current FMA members); $85 (non-members)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Financial decision-making, financial management, all areas of finance</t>
+          <t>Carbon Finance and Taxes, Climate and Economic Modeling in Policy Making, Climate Finance, Climate Negotiations and Scenarios, Climate Risk and Disclosures, Climate-resilient Economies, Energy Derivatives: Pricing and Hedging, Energy Markets: Modeling and Forecasting, Energy, Environment, and Climate Models, Financial and Economic Analysis of Energy Markets, Financial Regulation of Energy and Environmental Markets, Green Finance and Sustainable Investment, Just Energy Transition, Macroeconomic Implications of Net-Zero Carbon Emissions, Nature-based Financial Instruments for Climate Change Mitigation, Natural Resources, Risk, Welfare, and Social Preferences, Renewable Energy, Regulation and Energy Governance, Role of Financial Institutions in Sustainability</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3rd AI in Finance Conference</t>
+          <t>5th Annual Academic - 2026 DeFi &amp; Digital Currencies Conference</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3537,54 +3537,54 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Montréal, QC, Canada</t>
+          <t>The Shard, London, UK</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>£45</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Machine learning and artificial intelligence in asset pricing and financial econometrics, Portfolio management, trading strategies, and risk management using AI, Large language models (LLMs), NLP, and textual analysis in finance, Corporate finance applications including M&amp;A and investment decisions, Banking, credit markets, and financial intermediation, Cryptocurrency, digital assets, and decentralized finance, ESG, sustainability, and climate finance, Financial regulation, policy analysis, and central bank communication, Real estate finance and urban economics, Alternative data and high-dimensional financial datasets, Investor behavior, sentiment, and attention, Macroeconomic and financial risk forecasting.</t>
+          <t>DeFi Protocols, Lending and Borrowing Protocols, Decentralized Exchanges (DEXs), Blockchain Economics, Stablecoins and CBDCs, Digital Money and Payments, Tokenisation of real-world assets, Traditional and Decentralized Finance Interaction, Digital Finance and Inclusion</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026 Summer Research Conference</t>
+          <t>3rd Arne Ryde Conference on Crypto, Fintech and Payments</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Indian School of Business, Hyderabad Campus</t>
+          <t>Lund, Sweden</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3594,34 +3594,34 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Recent Advances in Finance, corporate finance, asset pricing, behavioral finance, financial intermediation, household finance, market microstructure</t>
+          <t>Crypto and blockchain technology, Crypto markets, households, and the real economy, Environmental and social impact of crypto markets, Interaction between traditional finance and decentralized finance, Stablecoins, Central Bank Digital Currencies (CBDCs), Financial technology (Fintech), Payment systems, Open banking and data sharing, Digital tools in financial services, Financial inclusion, development, and welfare in digital finance</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>International Risk Management Conference 2026</t>
+          <t>Institute for Quantitative Investment Research Autumn Residential Seminar 2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Warsaw, Poland</t>
+          <t>Ashdown Park Hotel &amp; Country Club, Wych Cross, East Sussex, UK</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3631,108 +3631,108 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Asset pricing; Banking; Financial econometrics; Capital markets; Financial intermediation; Corporate finance; Financial crises; Corporate governance; Market microstructure; Financial regulation; International corporate finance; Risk management; Emerging market; Corporate investment decision; Global risk markets; Macro-financial linkages; Financial policy securitization; Behavioural finance; Financial integration; Mathematical &amp; computational finance; Stochastic optimization approaches in finance; Mergers &amp; acquisitions; Modelling, money and liquidity; Sustainable finance; Climate change risk; AI innovation; crypto and related assets and technology.</t>
+          <t>New risks in a changing political environment, innovative and high-quality research related to investment management</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Second USTC Frontiers in Finance Conference</t>
+          <t>10th Shanghai-Edinburgh-London Finance Conference On Sustainable Finance in the Digital Era</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>International Finance Institute, University of Science and Technology of China, No. 1789 Guangxi Road, Binhu New District, Hefei City, Anhui Province, P.R. China</t>
+          <t>Shanghai and online</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>0 CNY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>All topics of finance</t>
+          <t>Financial development, financial inclusion, and their role in sustainable economic growth; Policy frameworks and regulatory challenges shaping sustainable finance adoption in developed and emerging markets; Cross-border sustainable finance flows and international regulatory coordination; Corporate governance, greenwashing detection, and market responses to ESG commitments; ESG backlash, anti-ESG movements, and the political economy of sustainable finance; AI and machine learning applications in ESG investment strategies, sustainability disclosure, and climate risk modelling; Big data and natural language processing in measuring and monitoring ESG performance; Blockchain applications in carbon markets, green bonds, and regulatory compliance; Digital finance, decentralised finance (DeFi), and emerging technologies in supporting a low-carbon transition; Fintech-enabled green lending, climate insurance, and impact investing.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Fischer-Shain Research Conference 2026</t>
+          <t>22nd Annual Conference of the Asia-Pacific Association of Derivatives</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>Busan, Korea</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>50 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>financial intermediation, banking, financial services</t>
+          <t>Derivatives; Volatility; Risk Management; Asset Pricing; Investments; Corporate Finance; Market Microstructure; Fintech; Regulation; Behavioral Finance</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ECB Money Market Conference 2026</t>
+          <t>FIRN Melbourne Asset Pricing Meeting</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>European Central Bank, Frankfurt am Main, Germany</t>
+          <t>Melbourne, Australia</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3742,34 +3742,34 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Money markets and monetary policy implementation; Money markets and technological innovation (stable coins, CBDCs, instant payments, AI impacts); The functioning of money markets (role of non-bank financial institutions, funding strategies, effects of central clearing, macroeconomic implications of volatile short-term rates and geopolitical developments)</t>
+          <t>theoretical and empirical models of asset prices and returns, return predictability, empirical methodology, macro-finance, the study of financial institutions as related to asset prices, information and liquidity in asset markets, behavioural investment studies, asset market structure and microstructure, risk analysis, hedge funds, mutual funds, pension funds, ESG, and alternative investments</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Finance in the Digital Age (FiDA) Workshop</t>
+          <t>Johns Hopkins Carey Finance Conference</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Calgary, Canada</t>
+          <t>Johns Hopkins Carey Business School, 100 International Drive, Baltimore, MD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3779,108 +3779,108 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>AI, DeFi, robo-advisors, neurofinance</t>
+          <t>All areas of finance, particularly early-stage papers</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>7th LTI@UniTO/Bank of Italy Workshop on Long-term investors’ trends: theory and practice</t>
+          <t>5th Holden Conference in Finance and Real Estate</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bank of Italy, Rome, Italy</t>
+          <t>Bloomington, IN</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$95 USD</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Long-term investors’ strategies and behavior, long-term investors’ role in financing the real economy, shifting equilibria in government bond markets, evolution of sustainable investment strategies, challenges for long-term investors from equity market concentration, non-bank investors in credit intermediation, rise of cryptocurrencies and fintech, emerging trends in asset allocation and risk management, shock transmission mechanisms in financial institutions, use of big data and AI in investment processes, innovations in financial markets, geopolitical risks' effect on banks vs. non-banks, effects of demographic transitions on financial markets</t>
+          <t>Empirical and theoretical papers in all finance and real estate areas</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>7th Annual RCF-ECGI Corporate Finance and Governance Conference</t>
+          <t>12th P2P Financial Systems International Workshop (P2PFISY 2026)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Madrid, Spain, and virtually</t>
+          <t>Astana, Kazakhstan</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>€350 in person (for conference dinner, lunches, and coffee breaks), €50 online option (for administrative / tech support)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>capital structure, corporate and securities law, corporate culture, corporate failure, corporate finance and public policy, corporate governance, corporate restructuring, corporate social responsibility, crowdfunding, dividends, payout policy, repurchases, entrepreneurial finance, family business, financial contracting, financial intermediation, financial literacy, fintech, fraud, innovation, IPOs and SEOs, mergers and acquisitions, misconduct, private debt, private equity, trade credit, socially responsible investments, sustainable finance, real options, venture capital</t>
+          <t>Regulation &amp; Compliance in Digital Asset Markets, Fraud, Financial Crime &amp; Forensics in Crypto Markets, CBDCs and Digital Public Infrastructure, Stablecoins and Digital Payment Systems, Artificial Intelligence in Financial Systems, Consumer Protection, Data Governance, and Trust in Digital Finance, Tokenisation of Real-World Assets (RWA)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Fintech and Financial Institutions Research Conference</t>
+          <t>2026 Annual Community Bank Research Conference</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Philadelphia, Philadelphia, PA</t>
+          <t>Federal Reserve Bank of St. Louis in St. Louis, MO</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3890,145 +3890,145 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Interlinkages of the fintech sector and the broader financial system, economic consequences and impacts of the fintech sector, regulatory implications of the fintech sector</t>
+          <t>The role of community banks in the U.S. financial system, the provision of financial services to households, small businesses, and small farms, impact of community banks on local/state economic activity, community banks’ response to financial and economic shocks and the associated policy responses, the effects of regulatory policy on community banks, quantifying regulatory and compliance costs, intended and unintended effects of regulatory requirements, antitrust policy and community banks, challenges and opportunities faced by community banks, competition from large banks, credit unions, and nonbanks including financial technology firms, funding and liquidity issues including FHLB advances and central bank lending facilities, collaborations/partnerships with financial technology and crypto firms, payments issues, the effects of new payment technologies and trends, the effects of rapid technological advances in banking, operational risk, advantages and disadvantages of the community bank business model, bank consolidation, noninterest/fee income, benefits of local knowledge and strong relationships, costs of operating at a small scale</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Aarhus Finance Forum 2026</t>
+          <t>Stigler Center-CEPR Political Economy of Finance Conference 2026: Crony Capitalism in 21st Century America</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Aarhus, Denmark</t>
+          <t>Gleacher Center - Chicago</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>375 DKK</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Financial Decisions under Uncertainty and Ambiguity, Household Finance, Real Estate Finance, Corporate Finance, Climate Finance, Digital Finance, Asset Pricing</t>
+          <t>Crony capitalism in 21st century America, political economy dynamics, relationship between economic and political power</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>15th CDI Conference on Derivatives</t>
+          <t>15th Fixed Income and Financial Institutions (FIFI) Conference</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Montreal, Canada</t>
+          <t>University of South Carolina in Columbia, SC</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>75 USD</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>fixed income, commercial and investment banks, asset management and mutual fund companies, short sellers, hedge funds, broker-dealers, insurance companies</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Conference on CSR, the Economy and Financial Markets</t>
+          <t>Higher Education Finance Research Conference</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Düsseldorf, Germany</t>
+          <t>Federal Reserve Bank of Philadelphia</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>€ 150 for regular participants, € 100 for PhD students</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Climate risk and pricing, Role of financial markets, banks, institutional investors in CSR, Effects of CSR on valuation, performance, cost of capital, funding and capital structure, Socio-economic aspects and their implications for companies and financial markets, Corporate governance and CSR, Risk management and CSR, CSR reporting and disclosure, ESG backlash and politicization, Sustainability strategy under new constraints, Measurement of ESG indices, CSR activities and the economy</t>
+          <t>Financial aid, student debt, higher education finance</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Vietnam Symposium on Global Economy (VSGE2026)</t>
+          <t>Wharton–Chicago–Harvard Insolvency and Restructuring Conference (WCHIRC)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City, Vietnam</t>
+          <t>University of Pennsylvania, Philadelphia, PA</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4038,34 +4038,34 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Geopolitical, macroeconomic policy, trade and foreign direct investment, climate change and public finance, finance and sustainable investment, digitalization, urbanization, AI's economic impacts, global governance</t>
+          <t>Corporate financial distress and bankruptcy, Liability management and out-of-court restructurings, Chapter 11 and formal reorganization processes, Consumer bankruptcy, Leveraged lending and private credit, Creditor governance and capital structure dynamics, Distressed debt markets and asset pricing, Financial contracting and covenant design, Bankruptcy law, courts, and institutional design, Operational restructuring and firm performance</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>21st Annual Conference on Asia-Pacific Financial Markets (CAFM)</t>
+          <t>Financial Decision-Making Conference 2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>CONRAD Seoul</t>
+          <t>Bozeman, MT</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4075,108 +4075,108 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>All areas of finance</t>
+          <t>household finance, financial literacy and education, consumer financial behavior, retirement and savings decisions, financial education interventions, fintech and digital finance, financial advice and delegation, debt and credit decisions, insurance decisions, behavioral finance, financial inclusion</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>India Finance Conference (IFC) 2026</t>
+          <t>Finance and Real Estate Conference 2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Indian Institute of Management Bangalore</t>
+          <t>Miami University, Oxford, OH</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$50 USD</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Theoretical and empirical asset pricing, Corporate finance, capital structure and dividend policy, Asset allocation and investment management, Financial crises, systemic risk and macro-finance, Quality of financial reporting and adoption of IFRS, Corporate governance, executive compensation and ownership structure, Computational finance and financial econometrics, Financial Econometrics, Financial risk analytics and management, Market microstructure and algorithmic trading, Financial policy choice, institutions and regulation, Financial Analytics, ESG, Climate Finance, Blended Finance, Insurance / Reinsurance / Pension Funds, Enhancing liquidity in commodity derivatives markets, Financial Literacy and Financial Education</t>
+          <t>Asset pricing and valuation, Corporate finance, Real estate markets and investment, Risk management and financial regulation, Urban economics and housing policy, Sustainable and green finance, Behavioral finance</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Edinburgh Financial Technology Conference</t>
+          <t>UGA Fall Finance Conference 2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Athens, GA</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>70 USD</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>The application of AI and Machine Learning in finance; The application of distributed ledger technologies in finance; Cryptofinance; Cyber risk in finance; The microstructure of modern financial markets (algorithmic/high frequency trading, dark trading, blockchain settlements, etc.); Behavioural economics in financial technology; Alternative data (structured and unstructured datasets); Crowdsourcing and investment strategy; New exchange traded financial derivatives; Financial stability risks from the development of FinTech; RegTech; Open banking</t>
+          <t>All areas of finance</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>5th Conference in Sustainable Finance</t>
+          <t>Inquire Europe Autumn Conference: “Expectations and Asset Prices”</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>University of Luxembourg</t>
+          <t>Prague, Czech Republic</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4186,34 +4186,34 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>any topic in sustainable finance</t>
+          <t>Expectations and asset prices, deviations from rational expectations, implications of optimism and pessimism in asset valuations, investment strategies and anomalies, factor investing, tactical asset allocation, portfolio choice under uncertainty, short selling, institutional investing, asset management</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>7th CEAR-RSI Household Finance Workshop</t>
+          <t>WFE’s Sustainability Conference 2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>HEC Montréal</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4223,51 +4223,51 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Consumption-saving decisions and investment choices, Financial literacy and education, Pensions and retirement, Financial planning and advice, Financial delinquency and bankruptcy, Household insurance and risk management</t>
+          <t>Transition finance and market design, Regulatory fragmentation and divergence, Sustainability reporting, Nature and biodiversity in capital markets, Just transition, social and gender finance, Proportionality for SMEs and emerging markets, Carbon market architecture</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Next-Gen AI and Autonomous Finance (NGAI) workshop</t>
+          <t>2026 FMA Annual Meeting</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Rennes School of Business, Rennes, France</t>
+          <t>Tampa, FL</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$75 (current FMA members); $85 (non-members)</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Autonomous agents &amp; decision-making in finance; AI-driven trading, portfolio optimization &amp; market microstructure; Risk, robustness, and model governance; Ethics, fairness, transparency &amp; societal impacts of financial AI; Financial decision making and AI; Bias and stereotyping in relation to AI driven finance; AI, money and financial value formation</t>
+          <t>Financial decision-making, financial management, and related topics</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>12th Annual ICGS Conference</t>
+          <t>3rd AI in Finance Conference</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4277,17 +4277,17 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>HEC Montréal (Quebec, Canada)</t>
+          <t>Montréal, QC, Canada</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4297,14 +4297,14 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Behavioral perspectives on executives, boards, investors, and other governance actors; Institutional and political approaches to governance; Implications of AI adoption for governance; Evolving forms of activism/engagement; Reconfiguration of governance systems under geopolitical crises; Governance mechanisms for managing state-firm relations.</t>
+          <t>Machine learning and artificial intelligence in asset pricing and financial econometrics, Portfolio management, trading strategies, and risk management using AI, Large language models (LLMs), NLP, and textual analysis in finance, Corporate finance applications including M&amp;A and investment decisions, Banking, credit markets, and financial intermediation, Cryptocurrency, digital assets, and decentralized finance, ESG, sustainability, and climate finance, Financial regulation, policy analysis, and central bank communication, Real estate finance and urban economics, Alternative data and high-dimensional financial datasets, Investor behavior, sentiment, and attention, Macroeconomic and financial risk forecasting, AI in Sustainability and Climate Finance, AI and Real Estate</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Vienna Festival of Finance Theory 2026</t>
+          <t>2026 Summer Research Conference</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4314,54 +4314,54 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Vienna, Austria</t>
+          <t>Indian School of Business, Hyderabad Campus</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>65 EUR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Corporate finance theory, financial intermediation theory</t>
+          <t>Recent Advances in Finance, corporate finance and its interface with asset pricing, behavioral finance, financial intermediation, household finance, market microstructure</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>The 11th (2026) Cross Country Perspectives in Finance (CCPF) Conference</t>
+          <t>International Risk Management Conference 2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>both online and on-site (Nanjing, China)</t>
+          <t>Warsaw, Poland</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4371,108 +4371,108 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>credit, banking, asset pricing, market liquidity, corporate finance, corporate governance, entrepreneurial finance</t>
+          <t>Asset pricing; Banking; Financial econometrics; Capital markets; Financial intermediation; Corporate finance; Financial crises; Corporate governance; Market microstructure; Financial regulation; International corporate finance; Risk management; Emerging market; Corporate investment decision; Global risk markets; Macro-financial linkages; Financial policy securitization; Behavioural finance; Financial integration; Mathematical &amp; computational finance; Stochastic optimization approaches in finance; Mergers &amp; acquisitions; Modelling, money and liquidity; Sustainable finance; Climate change risk; AI innovation; crypto and related assets and technology</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>6th Annual Bristol Financial Markets Conference</t>
+          <t>The Second USTC Frontiers in Finance Conference</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bristol, UK</t>
+          <t>International Finance Institute, University of Science and Technology of China, No. 1789 Guangxi Road, Binhu New District, Hefei City, Anhui Province, P.R.China</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>0 GBP</t>
+          <t>0 CNY</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Skill, performance, and evaluation in delegated portfolio management; The rise of passive investment and its effects on financial markets; New developments and trends in delegation: ESG / thematic/private markets; Machine learning and AI in asset management; Textual analysis and news coverage in delegated investment decisions; The role of index providers in delegated portfolio management</t>
+          <t>All topics of finance</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Inaugural CEIBS-APS Centre for Financial Markets (CAC) Academic Conference</t>
+          <t>Fischer-Shain Research Conference 2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>China Europe International Business School (CEIBS), Shanghai, China</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>50 USD</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>asset pricing, macro-finance, the impact of institutional features on capital market dynamics</t>
+          <t>financial intermediation, banking, financial services</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Dauphine Finance PhD Workshop</t>
+          <t>ECB Money Market Conference 2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Paris, France</t>
+          <t>European Central Bank, Frankfurt am Main, Germany</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4482,34 +4482,34 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Papers in all areas of Finance and Financial Economics</t>
+          <t>Money markets and monetary policy implementation, technological innovation in money markets (e.g., stable coins, CBDCs), functioning of money markets, role of non-bank financial institutions, funding strategies, central clearing effects, macroeconomic implications of volatile short-term rates</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>14th Helsinki Finance Summit on Investor Behavior</t>
+          <t>Finance in the Digital Age (FiDA) Workshop</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Helsinki/Espoo, Finland</t>
+          <t>Calgary, Canada</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4519,256 +4519,256 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Investor behavior, behavior of different investor types, market microstructure and investor trading behavior, behavioral biases and performance of investment strategies, household consumption, borrowing, saving, and portfolio choice, investor education, financial literacy, and sophistication, behavior of finance professionals and the impact of professional advice, biological, psychological, and cultural foundations of investor behavior, influence of analysts, media, and news coverage on investment decisions, social influence and networks in finance, impact of investor behavior on corporate policies and decision-making</t>
+          <t>AI, DeFi, robo-advisors, neurofinance</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026 Clemson Finance Research Conference</t>
+          <t>7th LTI@UniTO/Bank of Italy Workshop on Long-term investors’ trends: theory and practice</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Clemson, SC</t>
+          <t>Bank of Italy, Rome, Italy</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>$75 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>corporate finance, asset pricing, investment, banking, asset management, household finance, labor economics, behavioral finance, Fintech, real estate</t>
+          <t>Long-term investors’ strategies and behavior in times of geopolitical fragmentation, rising protectionism and technological breakthroughs; Long-term investors’ role in the financing of the real economy and in fostering growth; Shifting equilibria in government bond markets driven by quantitative tightening, rising indebtedness and macroeconomic uncertainty; The evolution of sustainable investment strategies and green lash risks; Challenges for long-term investors stemming from increasing equity market concentration; The rising importance of non-bank investors in credit intermediation and its consequences for the transmission of monetary policy; The rise of cryptocurrencies, emerging financial technologies (fintech) and their impact on investment strategies; Emerging trends in asset allocation and risk management for long-term investors, including insurance companies, pension funds, and mutual funds; Shock transmission mechanisms from the real economy to financial institutions and the amplification of shocks through credit chains, fire sales, and other procyclical processes; The use of big data and artificial intelligence to assess in the investment processes and in the management of the exposure to risk factors; Innovations in financial markets and opportunities for financial institutions; Geopolitical risks and their effect on banks vs. non-bank intermediaries; The effects of the demographic transitions on financial markets and the role of long-term investors in tackling them.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Politics in Finance 2026 Conference</t>
+          <t>7th Annual RCF-ECGI Corporate Finance and Governance Conference</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>McDonough School of Business, Rafik B. Hariri Building 37th and O Streets, N.W Washington, D.C. 20057 USA</t>
+          <t>Madrid, Spain, and virtually</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>$75 USD</t>
+          <t>€350 in person / €50 online</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>The role of political connections and political ideologies in shaping capital market forces; How political ideologies affect the decision making by firms and workers; Political connections and corruption in developing economies; The political economy of financial development; The interaction between government and financial institutions; Implications of political uncertainty and political connections for asset prices and corporate policies; Political economy of financial regulation and financial crises</t>
+          <t>capital structure, corporate and securities law, corporate culture, corporate failure, corporate finance and public policy, corporate governance, corporate restructuring, corporate social responsibility, crowdfunding, dividends, payout policy, repurchases, entrepreneurial finance, family business, financial contracting, financial intermediation, financial literacy, fintech, fraud, innovation, IPOs and SEOs, mergers and acquisitions, misconduct, private debt, private equity, trade credit, socially responsible investments, sustainable finance, real options, venture capital</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>11th SDU Finance Workshop on Corporate Finance</t>
+          <t>Fintech and Financial Institutions Research Conference</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>University of Southern Denmark (SDU), Odense, Denmark</t>
+          <t>Federal Reserve Bank of Philadelphia, Philadelphia, PA</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>300 DKK (approx. 40 EUR)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Corporate Finance -- Dynamics, Uncertainty, and Strategic Decisions</t>
+          <t>Economic consequences and impacts of the fintech sector, regulatory implications of the fintech sector</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Northern Finance Association 2026 Annual Meeting</t>
+          <t>Aarhus Finance Forum 2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Quebec City, Canada</t>
+          <t>Aarhus, Denmark</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Canadian $75 (about US $55) per paper</t>
+          <t>375 DKK</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Topics from all areas of finance including asset pricing, corporate finance, financial intermediation, investments, with special interest in Canadian financial markets, insurance, household finance, sustainable finance, fintech, and AI</t>
+          <t>Financial Decisions under Uncertainty and Ambiguity, Household Finance, Real Estate Finance, Corporate Finance, Climate Finance, Digital Finance, Asset Pricing</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>London Business School 2026 Summer Finance Symposium</t>
+          <t>15th CDI Conference on Derivatives</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>London Business School</t>
+          <t>Montreal, Canada</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>£50 GBP</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Papers from all areas of finance</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Sustainability, Technology, and the Transformation of Accounting and Finance (STTAF26)</t>
+          <t>Conference on CSR, the Economy and Financial Markets</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Bahrain</t>
+          <t>Düsseldorf, Germany</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>€ 150 for regular participants and € 100 for PhD students</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Climate Finance, Artificial Intelligence (AI) and Machine Learning in Finance and Accounting, Green Finance, Sustainable Finance, ESG Reporting, and Climate Risk, FinTech, Blockchain, and Digital Currencies, Corporate Governance and Technological Innovation, Big Data in Accounting and Finance, Green Accounting and Carbon Disclosure, RegTech and Financial Compliance, Data Analytics and Financial Decision-Making, Digital Transformation in Public Sector Accounting, Ethical Implications of AI and Automation in Financial Services, Evolving Accounting Standards in Response to Sustainability/Technology</t>
+          <t>Climate risk and pricing, Role of financial markets, banks, institutional investors in CSR, Effects of CSR on valuation, performance, cost of capital, funding and capital structure, Socio-economic aspects and their implications for companies and financial markets, Corporate governance and CSR, Risk management and CSR, CSR reporting and disclosure, ESG backlash and politicization, Sustainability strategy under new constraints, Measurement: information content and reliability of ESG indices, CSR activities and the economy</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>11th International Conference on Accounting and Finance (ICOAF-2026)</t>
+          <t>2026 Vietnam Symposium on Global Economy (VSGE2026)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Danang, Vietnam</t>
+          <t>Ho Chi Minh City, Vietnam</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4778,34 +4778,34 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Accounting, Finance, and Banking</t>
+          <t>Geopolitical, macroeconomic policy and development; Trade, foreign direct investment, and global value chain; Climate change, green transition, and public finance; Finance, stability, and sustainable investment; Digitalization, labor markets, and social protection; Urbanization, regional development and resilience; AI, growth, economic impacts, and government policies; Global governance, institutions, and international cooperation.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Liechtenstein Workshop on AI in Finance 2026</t>
+          <t>India Finance Conference (IFC) 2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Vaduz, Liechtenstein</t>
+          <t>Indian Institute of Management Bangalore</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4815,34 +4815,34 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>forecasting financial variables with AI, asset allocation and asset management with AI, AI-based factor models, natural language processing and large language models in finance, AI applications in corporate finance</t>
+          <t>Theoretical and empirical asset pricing, Corporate finance, capital structure and dividend policy, Asset allocation and investment management, Financial crises, systemic risk and macro-finance, Quality of financial reporting and adoption of IFRS, Corporate governance, executive compensation and ownership structure, Computational finance and financial econometrics, Financial risk analytics and management, Market microstructure and algorithmic trading, Financial policy choice, institutions and regulation, Financial Analytics, ESG, Climate Finance, Blended Finance, Insurance / Reinsurance / Pension Funds, Enhancing liquidity in commodity derivatives markets, Financial Literacy and Financial Education</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>3rd Modern Finance Conference (MFC 2026)</t>
+          <t>Edinburgh Financial Technology Conference</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Krakow, Poland</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4852,71 +4852,71 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Asset pricing and valuation, Banking and financial services, Behavioral finance and decision making, Capital structure, Corporate finance, Corporate governance, Cryptocurrencies, Derivatives, Economic development, Exchange rates and currency markets, Finance and accounting standards, Financial econometrics and quantitative methods, Financial markets and instruments, Financial, management, and tax accounting, Financial regulation and supervision, Financial stability, Fintech and financial innovation, Green finance, Investment and portfolio management, Insurance, Market microstructure, Mergers and acquisitions, Microfinance, Monetary policy and central banking, Risk management, Sustainable finance and responsible investment</t>
+          <t>The application of AI and Machine Learning in finance, The application of distributed ledger technologies in finance, Cryptofinance, Cyber risk in finance, The microstructure of modern financial markets: algorithmic/high frequency trading, dark trading, blockchain settlements etc., Behavioural economics in financial technology, Alternative data (structured and unstructured datasets), Crowdsourcing and investment strategy, New exchange traded financial derivatives, Financial stability risks from the development of FinTech, RegTech, Open banking</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>The First University of Maryland/Singapore Management University/UBS Quant Investment Forum: AI and Finance</t>
+          <t>5th Conference in Sustainable Finance</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>University of Luxembourg</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>95 SGD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>AI for Investments &amp; Asset Pricing, Alternative Data and Investment Insights, Portfolio &amp; Risk Management, Algorithmic Trading &amp; Market Impact</t>
+          <t>Any topic in sustainable finance</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026 City University of Hong Kong International Finance Conference</t>
+          <t>7th CEAR-RSI Household Finance Workshop</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>City University of Hong Kong</t>
+          <t>HEC Montréal</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4926,71 +4926,71 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Corporate Finance, Asset Pricing</t>
+          <t>Consumption-saving decisions and investment choices, Financial literacy and education, Pensions and retirement, Financial planning and advice, Financial delinquency and bankruptcy, Household insurance and risk management</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026 Research Summer Workshop on Regulated Funds and Retail-oriented Investment Products</t>
+          <t>Next-Gen AI and Autonomous Finance (NGAI) workshop</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Washington, DC, USA</t>
+          <t>Rennes School of Business, Rennes, France</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>50 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Regulated funds, retail-oriented investment products, mutual fund industry</t>
+          <t>Autonomous agents &amp; decision-making in finance, AI-driven trading, portfolio optimization &amp; market microstructure, Risk, robustness, and model governance, Ethics, fairness, transparency &amp; societal impacts of financial AI, Financial decision making and AI, Bias and stereotyping in relation to AI driven finance, AI, money and financial value formation.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026 Vietnam Symposium in Entrepreneurship, Finance, and Innovation</t>
+          <t>12th Annual ICGS Conference</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Hanoi, Vietnam</t>
+          <t>HEC Montréal, Quebec, Canada</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5000,24 +5000,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>AI, Big Data, and Machine Learning Applications in Finance; Asset Pricing; Bankruptcy and Liquidation; Biodiversity Finance; Climate Finance; Corporate Finance and Governance; Corporate Responsibility and Sustainability; Crypto Assets, Blockchain, and Decentralized Finance; Electronic Markets, Trading Platforms, and Market Microstructure; ESG and Sustainable Finance; Financial Markets; Household Finance; Information Disclosure, Market Efficiency, and Transparency; Portfolio and Investment Decisions; FinTech, Alternative Finance, and Digital Financial Infrastructure; Tokenomics, Digital Currencies, and Payment Systems; Business Model Innovation and Corporate Digital Transformation; Digital Innovation, Knowledge Management, and Innovation Systems; Digital Human Resources and the Future of Work; Innovation Management and Growth Strategies; Innovation and Industrial Policy; Institutions, Regulation, and Innovation Systems; Science, R&amp;D, and the Economics of Knowledge Creation; Sustainability in the Digital Economy; Crowdfunding, Peer-to-Peer Lending, and Platform-Based Finance; Entrepreneurship, Intrapreneurship, and Innovation; Entrepreneurship in Emerging and Transition Markets; Family-Owned Businesses and Governance; Governance and Financing of High-Tech Firms; New Venture Creation and Performance; Social and Sustainable Entrepreneurship; Startups, SMEs, and Resource Allocation; Venture Financing and Entrepreneurial Growth</t>
+          <t>Behavioral perspectives on governance, institutional and political approaches, implications of AI adoption, evolving forms of activism, reconfiguration of governance under geopolitical crises, governance mechanisms for managing state-firm relations</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>12th IWH-FIN-FIRE Workshop on “Challenges to Financial Stability”</t>
+          <t>Vienna Festival of Finance Theory 2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -5027,81 +5027,81 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Halle Institute for Economic Research (IWH), Halle/Saale Germany</t>
+          <t>Vienna, Austria</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>65 EUR</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>regulation and financial intermediation, corporate finance, law, politics and finance, monetary policy, inflation and financial resilience, macroprudential policy and real estate, financial networks and systemic risk, pricing of climate risk in financial markets, ecological hazards and the behaviour of firms and households, governance of financial firms and markets, private credit and risk transfer</t>
+          <t>Corporate finance theory, financial intermediation theory</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Bridging Theory and Empirical Research in Finance</t>
+          <t>The 11th (2026) Cross Country Perspectives in Finance (CCPF) Conference</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Boston College</t>
+          <t>Nanjing, China (online and on-site)</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>$50</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>corporate finance, corporate governance, financial intermediation, agency and delegation, information and securities, financial markets</t>
+          <t>cross-country factors, credit, banking, asset pricing, market liquidity, corporate finance, corporate governance, entrepreneurial finance</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>11th Bank of Finland and European Systemic Risk Board Joint Conference on AI and Systemic Risk Analytics</t>
+          <t>6th Annual Bristol Financial Markets Conference</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bank of Finland, Helsinki</t>
+          <t>Bristol, UK</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5111,14 +5111,14 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Use of Large Language Models (LLM) and trustworthy AI, AI and changing interdependencies in the financial markets, Cyber security and operational risks as sources of systemic risk, AI and Quantum Computing as potential source of new systemic risks, Use of AI with big data for systemic risk analytics, Risks and opportunities stemming from disruptive innovations in financial technology (FinTech), Analysing emerging risks from interconnectedness of the financial system, Identifying risks from market-based finance, Modelling geopolitical risks, Using systemic risk analytics to support macro-prudential policy and regulation, Evidence of macroprudential policy measures</t>
+          <t>Skill, performance, and evaluation in delegated portfolio management; The rise of passive investment and its effects on financial markets; New developments and trends in delegation: ESG / thematic/private markets; Machine learning and AI in asset management; Textual analysis and news coverage in delegated investment decisions; The role of index providers in delegated portfolio management</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Bank of Finland and CEPR Joint conference on Navigating Monetary Policy by the Northern Lights</t>
+          <t>Inaugural CEIBS-APS Centre for Financial Markets (CAC) Academic Conference</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Saariselkä, Lapland</t>
+          <t>China Europe International Business School (CEIBS), Shanghai, China</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -5148,34 +5148,34 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Monetary Policy Transmission, Inflation Dynamics and Expectations; Heterogeneity in Macro and Monetary Economics Models; Monetary-Fiscal Interactions; Technological Advances, Financial Market Developments, and Central Banks; Geopolitical Shocks and Monetary Policy; Central bank credibility and independence</t>
+          <t>asset pricing, macro-finance, impact of institutional features on capital market dynamics</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026 FIRN/UQ Asset Management Meeting</t>
+          <t>Dauphine Finance PhD Workshop</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Brisbane, Australia</t>
+          <t>Paris, France</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -5185,34 +5185,34 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>asset management, FinTech, mutual funds, hedge funds, pension funds, ETFs, alternative investments, data assets/markets, digital finance, platform finance, financial technology, artificial intelligence, big data in asset management</t>
+          <t>Papers in all areas of Finance and Financial Economics</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>World Finance &amp; Banking Symposium</t>
+          <t>14th Helsinki Finance Summit on Investor Behavior</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>University of Latvia, Riga</t>
+          <t>Helsinki/Espoo, Finland</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -5222,219 +5222,219 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>All areas of finance, economics, and banking</t>
+          <t>Investor behavior, behavior of different investor types, market microstructure, behavioral biases, household consumption, investor education, finance professionals, biological and psychological foundations of investor behavior, influence of analysts and media, social influence and networks, impact of investor behavior on corporate policies</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Research Symposium on Finance and Economics (RSFE) 2026</t>
+          <t>2026 Clemson Finance Research Conference</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Krea University, Andhra Pradesh, India</t>
+          <t>Clemson, SC</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>75 USD</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Various topics in the field of finance and economics</t>
+          <t>corporate finance, asset pricing, investment, banking, asset management, household finance, labor economics, behavioral finance, Fintech, real estate</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Annual Meeting of the Central Bank Research Association CEBRA</t>
+          <t>Politics in Finance 2026 Conference</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Copenhagen, Denmark</t>
+          <t>McDonough School of Business, Rafik B. Hariri Building 37th and O Streets, N.W Washington, D.C. 20057 USA</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$75 USD</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Monetary Policy Transmission, Expectations, and Communication; Inflation and Price Dynamics; Macro-Finance and Financial Stability; Fiscal–Monetary Interactions and Policy Making; International Macroeconomics, Trade, and Geoeconomics; Firms, Productivity, and the Real Economy; Data, Methods, and Artificial Intelligence</t>
+          <t>The role of political connections and political ideologies in shaping capital market forces, How political ideologies affect the decision making by firms and workers, Political connections and corruption in developing economies, The political economy of financial development, The interaction between government and financial institutions, Implications of political uncertainty and political connections for asset prices and corporate policies, Political economy of financial regulation and financial crises</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>IBEFA Annual Meeting at the 2027 ASSA Conference</t>
+          <t>11th SDU Finance Workshop on Corporate Finance -- Dynamics, Uncertainty, and Strategic Decisions</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2027-01-03</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2027-01-05</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Washington, DC</t>
+          <t>University of Southern Denmark (SDU), Odense, Denmark</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>US$100 per paper; US$75 for papers solely authored by PhD students</t>
+          <t>300 DKK (approx. 40 EUR)</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>banking; financial risk measurement and management; non-bank financial intermediation and private credit; FinTech; the role of AI in financial intermediation; geo-economic fragmentation and capital flows; sustainable finance; household finance; financial market structure and regulation; monetary policy</t>
+          <t>Corporate Finance, Dynamics, Uncertainty, Strategic Decisions</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>CSEF- CEPR Conference on Labor and Finance</t>
+          <t>Northern Finance Association 2026 Annual Meeting</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Villa Orlandi Conference Centre, University of Naples Federico II, Capri (Italy)</t>
+          <t>Quebec City, Canada</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CAD 75</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Interaction between financial and labor markets, technological innovation, job-skill matches, firms’ employment policies, role of employees in governance and financing of companies, responses of wages, employment, and career trajectories to shocks, risk-sharing arrangements between firms and workers</t>
+          <t>Papers on any topic related to finance, including asset pricing, corporate finance, financial intermediation, investments, Canadian financial markets, insurance, household finance, sustainable finance, fintech, and AI.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Happy Valley Finance Conference</t>
+          <t>London Business School 2026 Summer Finance Symposium</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>State College, PA</t>
+          <t>London Business School</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>£50</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>all areas of finance</t>
+          <t>Papers from all areas of finance</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>3rd CEPR-SAFE Frankfurt Hub Conference of RPNs</t>
+          <t>Sustainability, Technology, and the Transformation of Accounting and Finance (STTAF26)</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>House of Finance, Campus Westend, Frankfurt, Germany</t>
+          <t>Bahrain</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5444,34 +5444,34 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Fintech and Financial Institutions, Regulatory framework revisions, CBDC blockchains and stablecoins, Sovereign bonds and sovereign bond capital regulation, Payment systems and European sovereignty, Safe assets and exchange rate dynamics under world polarization, Private credit and financial stability, Climate regulation U-turn and implications for climate finance, Defence policy needs and European financial architecture</t>
+          <t>Climate Finance, Artificial Intelligence (AI) and Machine Learning in Finance and Accounting, Green Finance, Sustainable Finance, ESG Reporting, and Climate Risk, FinTech, Blockchain, and Digital Currencies, Corporate Governance and Technological Innovation, Big Data in Accounting and Finance, Green Accounting and Carbon Disclosure, RegTech and Financial Compliance, Data Analytics and Financial Decision-Making, Digital Transformation in Public Sector Accounting, Ethical Implications of AI and Automation in Financial Services, Evolving Accounting Standards in Response to Sustainability/Technology</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Conference on The Industrial Organization of Financial Markets</t>
+          <t>11th International Conference on Accounting and Finance (ICOAF-2026)</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>SKEMA Business School, Sophia Antipolis (Nice) campus, France</t>
+          <t>Danang, Vietnam</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5481,219 +5481,219 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>market structure and competition, innovation and strategic behavior in the organization of the financial markets, payment card industry, lending and digital banking, primary and secondary markets for equity, government debt and corporate debt, financial regulation and competition policy, interbank lending markets, retail funding markets, credit markets, including mortgages</t>
+          <t>Accounting, Finance, and Banking, encompassing both theoretical and empirical studies</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Fourteenth Oxford Financial Intermediation Theory Conference (OxFIT)</t>
+          <t>Liechtenstein Workshop on AI in Finance 2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Saïd Business School, University of Oxford</t>
+          <t>Vaduz, Liechtenstein</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>£65</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Financial crises, Governance of financial institutions, The role of central banks and regulators, Financial innovation, International regulatory coordination, Certification in financial markets</t>
+          <t>forecasting financial variables with AI, asset allocation and asset management with AI, AI-based factor models, natural language processing and large language models in finance, AI applications in corporate finance</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>University of Washington 7th Summer Finance Conference</t>
+          <t>3rd Modern Finance Conference (MFC 2026)</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Seattle, Washington</t>
+          <t>Krakow, Poland</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>80 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>All areas of finance, with encouragement for submissions from junior faculty and preliminary papers</t>
+          <t>Asset pricing and valuation, Banking and financial services, Behavioral finance and decision making, Capital structure, Corporate finance, Corporate governance, Cryptocurrencies, Derivatives, Economic development, Exchange rates and currency markets, Finance and accounting standards, Financial econometrics and quantitative methods, Financial markets and instruments, Financial, management, and tax accounting, Financial regulation and supervision, Financial stability, Fintech and financial innovation, Green finance, Investment and portfolio management, Insurance, Market microstructure, Mergers and acquisitions, Microfinance, Monetary policy and central banking, Risk management, Sustainable finance and responsible investment</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>4th Tilburg Finance Summit</t>
+          <t>First University of Maryland/Singapore Management University/UBS Quant Investment Forum: AI and Finance</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Tilburg, Netherlands</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>95 SGD</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Asset Pricing and Behavioral Finance</t>
+          <t>AI for Investments &amp; Asset Pricing, Alternative Data and Investment Insights, Portfolio &amp; Risk Management, Algorithmic Trading &amp; Market Impact</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026 PHBS–IER conference on “Technology, Innovation, Platforms, and Economic Performance”</t>
+          <t>2026 City University of Hong Kong International Finance Conference</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Peking University HSBC Business School, Shenzhen, China</t>
+          <t>City University of Hong Kong</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>0 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Innovation, Technology Emergence, and Technology Transfer; Technology Adoption, Diffusion, and Automation; Resource Reallocation, Productivity, and Aggregate Dynamics; Geoeconomics and Technology Policy: Fragmentation, Trade, and Innovation; Trading Platforms and Digital Markets: Design, Competition, and Information; Institutions, Finance, Digital Payments, and Regulation in the Digital Economy</t>
+          <t>Corporate Finance, Asset Pricing</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>7th Canadian Sustainable Finance Network Conference</t>
+          <t>2026 Research Summer Workshop on Regulated Funds and Retail-oriented Investment Products</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Alberta School of Business, University of Alberta, Edmonton, Canada</t>
+          <t>Washington, DC, USA</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>0 CAD</t>
+          <t>50 USD</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>sustainable finance and the intersection of corporate governance and sustainability</t>
+          <t>Regulated funds, retail-oriented investment products, mutual fund industry</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026 Global Finance Conference</t>
+          <t>2026 Vietnam Symposium in Entrepreneurship, Finance, and Innovation</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>University of Azores, Portugal</t>
+          <t>Hanoi, Vietnam</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5703,108 +5703,108 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Energy, Sustainability, Fintech including AI, Climate change, Alternative Investments, Asset &amp; Wealth Management, Asset Allocation/Sovereign Funds/Hedge Funds/ETFs/SWFs, Banking &amp; Financial Services – Integrations – Linkages, Corporate Governance/Executive Compensation, Country Risk/Debt Issues/Insurance/Reinsurance, Derivatives/Financial Engineering, E-Business/E-Finance/Social Media, Emerging Markets/BRICS, Entrepreneurship/Venture Capital Global Perspectives, Ethics/Legal/Regulatory, Accounting, Auditing and Taxation Issues, Financial Crises and Bubbles: Causes/Impacts/Solutions, Financial Technology including AI, ML &amp; Financial Information Systems, Foreign Currency Issues – Global Multi-Currency System, Future of Global Economy- Imbalances, Sustainability, CSR, Climate Issues, Global Trade Issues – Free Trade – Trade Barriers &amp; Protections, IPOs/SEOS/Stock buybacks/Privatization, Market Behavior Efficiency/Inefficiency, Mergers and Acquisitions/Corporate and State SWFs, Non-Traditional Banking &amp; Financial Services, Portfolio Flows and Foreign Direct Investment, Private Equity, Real estate - global perspectives, Valuation, Portfolio Management and Managing Financial Risk</t>
+          <t>AI, Big Data, and Machine Learning Applications in Finance; Asset Pricing; Bankruptcy and Liquidation; Biodiversity Finance; Climate Finance; Corporate Finance and Governance; Corporate Responsibility and Sustainability; Crypto Assets, Blockchain, and Decentralized Finance; Electronic Markets, Trading Platforms, and Market Microstructure; ESG and Sustainable Finance; Financial Markets; Household Finance; Information Disclosure, Market Efficiency, and Transparency; Portfolio and Investment Decisions; FinTech, Alternative Finance, and Digital Financial Infrastructure; Tokenomics, Digital Currencies, and Payment Systems; Business Model Innovation and Corporate Digital Transformation; Digital Innovation, Knowledge Management, and Innovation Systems; Digital Human Resources and the Future of Work; Innovation Management and Growth Strategies; Innovation and Industrial Policy; Institutions, Regulation, and Innovation Systems; Science, R&amp;D, and the Economics of Knowledge Creation; Sustainability in the Digital Economy; Crowdfunding, Peer-to-Peer Lending, and Platform-Based Finance; Entrepreneurship, Intrapreneurship, and Innovation; Entrepreneurship in Emerging and Transition Markets; Family-Owned Businesses and Governance; Governance and Financing of High-Tech Firms; New Venture Creation and Performance; Social and Sustainable Entrepreneurship; Startups, SMEs, and Resource Allocation; Venture Financing and Entrepreneurial Growth</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Bayes Junior Asset Management and Asset Pricing Workshop</t>
+          <t>12th IWH-FIN-FIRE Workshop on “Challenges to Financial Stability”</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Bayes Business School, London</t>
+          <t>Halle Institute for Economic Research (IWH), Halle/Saale Germany</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>£50</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Asset management, Asset pricing</t>
+          <t>regulation and financial intermediation, corporate finance, law, politics and finance, monetary policy, inflation and financial resilience, macroprudential policy and real estate, financial networks and systemic risk, pricing of climate risk in financial markets, ecological hazards and the behaviour of firms and households, governance of financial firms and markets, private credit and risk transfer</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Second Annual Notre Dame Investment Management Conference</t>
+          <t>Bridging Theory and Empirical Research in Finance</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>University of Notre Dame - Notre Dame, Indiana</t>
+          <t>Boston College</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>USD 70</t>
+          <t>$50</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Demand Based Asset Pricing, Inelastic Markets Hypothesis, New Methods in Asset Pricing (Machine Learning, Artificial Intelligence (AI), unstructured data), Time series and Cross-Sectional Predictability, Portfolio Allocation for Long Term Investors, Retirement decisions and choices, Behavioral finance</t>
+          <t>corporate finance, corporate governance, financial intermediation, agency and delegation, information and securities, financial markets</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Future Finance Fest (3f)</t>
+          <t>11th Bank of Finland and European Systemic Risk Board Joint Conference on AI and Systemic Risk Analytics</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Bank of Finland, Helsinki</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5814,108 +5814,108 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>AI, asset pricing, banking, behavioral finance, big data, blockchain, CBDCs, compliance, crowdfunding, cryptocurrencies, cybersecurity, decentralized finance, digital finance, embedded finance, fintech, financial infrastructure, financial inclusion, financial innovation, financial intermediation, financial markets, household finance, insurtech, machine learning, market microstructure, payments, platforms, regulation, risk management, stablecoins, tokenization, text analytics.</t>
+          <t>Use of Large Language Models (LLM) and trustworthy AI; AI and changing interdependencies in the financial markets; Cyber security and operational risks as sources of systemic risk; AI and Quantum Computing as potential source of new systemic risks; Use of AI with big data for systemic risk analytics; Risks and opportunities stemming from disruptive innovations in financial technology (FinTech); Analysing emerging risks from interconnectedness of the financial system; Identifying risks from market-based finance; Modelling geopolitical risks; Using systemic risk analytics to support macro-prudential policy and regulation; Evidence of macroprudential policy measures</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026 FMA Applied Finance Conference</t>
+          <t>Bank of Finland and CEPR Joint conference on Navigating Monetary Policy by the Northern Lights</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>St. John's University - Manhattan Campus, New York, NY</t>
+          <t>Saariselkä, Lapland</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>$50 USD (FMA-members) and $60 USD (non-members)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>high-quality papers from scholars and practitioners in the fields of finance and accounting that inform practice, address contemporary global issues, and introduce new hypotheses for research</t>
+          <t>Monetary Policy Transmission, Inflation Dynamics and Expectations; Heterogeneity in Macro and Monetary Economics Models; Monetary-Fiscal Interactions; Technological Advances, Financial Market Developments, and Central Banks; Geopolitical Shocks and Monetary Policy; Central bank credibility and independence</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Exeter Sustainable Finance Conference 2026</t>
+          <t>2026 FIRN/UQ Asset Management Meeting</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>University of Exeter Business School, Exeter, UK</t>
+          <t>Brisbane, Australia</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>0 GBP</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Sustainable finance, interdisciplinary research approaches</t>
+          <t>asset management, FinTech, mutual funds, hedge funds, pension funds, ETFs, alternative investments, data assets/markets, digital finance, platform finance, financial technology, artificial intelligence, big data in asset management</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>9th Cryptocurrency Research Conference (CRC2026)</t>
+          <t>World Finance &amp; Banking Symposium</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Santiago, Chile</t>
+          <t>University of Latvia, Riga</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5925,1006 +5925,118 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>cryptocurrencies, digital finance, FinTech, tokenomics, blockchain economics</t>
+          <t>All areas of finance, economics, and banking</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Accountability in a Sustainable World Conference</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Virtual</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>200 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Non-academic-friendly summaries of research, sustainability, accountability in research</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>33rd Finance Forum</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Alicante, Spain</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>50 €</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Financial Economics research, including Asset Pricing, Corporate Finance, Banking, Portfolio Choice and Asset Management, Microstructure, Regulation, Financial Stability, and Macrofinance</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>3rd Workshop on Recent Trends and New Developments in Sustainable, Green and International Finance</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Nice, France</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>220 EUR (academics and professionals), 180 EUR (Ph.D. students)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>sustainable finance, green finance, climate finance, international finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Alpine Finance Summit (AFS) 2026</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Garmisch-Partenkirchen, Germany</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>50 EUR</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>Asset Pricing, Investments, Sustainable Finance, FinTech</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>22nd Annual Conference of the Asia-Pacific Association of Derivatives</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Busan, Korea</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>Derivatives; Volatility; Risk Management; Asset Pricing; Investments; Corporate Finance; Market Microstructure; Fintech; Regulation; Behavioral Finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>NBER-SAIF Conference on AI and Financial Markets</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Virtual</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>The impact of investment in AI and supporting technologies on corporate earnings and share prices; the effects of AI on portfolio choices and trading behavior of financial market participants; the role of AI in creating new measures of economic activity; the uses of AI in financial market regulation and risk detection; the consequences of AI for the financial advice industry; the macroeconomic effects of AI on economy-wide discount rates.</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>12th Workshop on Banking and Institutions</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Bank of Finland, Helsinki</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>banking and institutions, geopolitics and banking, political economy of banking, banking and society, banking in emerging markets, climate and banking, monetary policy and institutions</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>ENTFIN 2026 Conference</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Kedge Business School, Marseille, France</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>Venture capital; private equity, and buyouts; Business angels and early-stage financing; Crowdfunding; token offerings, and digital finance; Entrepreneurial banking and credit relationships; Corporate governance, contracts, and monitoring; Financial innovation; FinTech, and AI in entrepreneurial finance; ESG, sustainability, and impact finance; Entrepreneurial ecosystems and regional financing gaps; Entrepreneurial risk-taking and behavioral finance; Impact assessment for publicly supported financial instruments.</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>9th Short-Term Funding Markets Conference</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>Federal Reserve Board, Washington, D.C.</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>0 USD</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>Maturity and liquidity transformation by financial intermediaries, Repo markets and clearing institutions, Theories of frictions and fragility in funding markets, Effects of regulation and central bank intervention, Securities lending, Money creation and demand for safe assets, Fintech and encrypted currency</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>21st Central Bank Conference on the Microstructure of Financial Markets</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Eltville am Rhein, Germany</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>Artificial intelligence and market microstructure, The functioning and resilience of sovereign bond and repo markets</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>2026 PRIVATE EQUITY RESEARCH CONSORTIUM (PERC) EUROPE SYMPOSIUM</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>Oxford, England</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>private equity, buyouts, distressed securities, mezzanine financing, special situations, private credit, venture capital, real estate, real assets</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Lake District Workshop in Corporate Finance</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Windermere, Lake District, United Kingdom</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>£60</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>Corporate finance, mergers and acquisitions, corporate governance, financial institutions</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>8th Annual Workshop on Financial Institutions Research</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>Gateway Conference Center, Federal Reserve Bank of St. Louis; St. Louis, MO USA</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>Bank Regulation, Supervision, and Compliance; Bank Risk-taking, Stability, and Financial Crises; Lending and Credit Allocation; Bank Governance, Ownership, and Compensation; Bank Disclosure, Accounting, and the Information Environment; Deposits, Funding Structure, and Liability Management; Financial Technology, Innovation, and Bank Competition</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Southern Finance Association 2026 Annual Meeting</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>2026-11-21</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>LaQuinta Resort, Palm Springs, CA</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>50 USD</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>Papers on any area of finance, panel discussions, special sessions, tutorials</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>International Accounting &amp; Finance Doctoral Symposium (IAFDS)</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>Cagliari, Sardinia, Italy</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>£300</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>Original empirical and theoretical papers in accounting and finance (including banking), focusing on significant and impactful issues within these fields.</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>13th Annual Conference on Risk Governance</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>University of Siegen, Siegen/Germany</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>Risk Governance in the boardroom, Risk Governance and the monitoring role of supervisory boards, Balancing risk and opportunity, Stakeholder influence and external pressure, Sustainability and Risk Governance, Understanding black swans, Strategic resilience at the top, Considering risk strategies on bank boards, Tackling digitalization-related risks, The role of artificial intelligence for board decisions, Machine learning and risk-responsive decision-making</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>SHoF Annual Conference on the Future of Private Capital Markets</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>Private equity and private credit market structure, Private capital strategies and performance, The interaction between private and public capital markets, Private capital and corporate investment, productivity, and innovation, Structured lending within the private market, Fund organization, governance, and incentives, Financing of infrastructure and energy transition, Risk-taking and financial stability implications, The role of private capital in downturns and periods of financial stress, Regulatory and policy implications of the growth of private markets, ESG, sustainability, and impact in private capital markets</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>CU Denver 9th Annual J.P. Morgan Center International Commodities Symposium</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>Denver, CO</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>Recent developments in commodity business, research on global commodity sectors (energy, metals and minerals, agriculture), commodity futures, derivatives, and related research topics</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Bocconi-Bristol Second Sustainability and Green Finance Research Workshop</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Bocconi University, Milan (Italy)</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>New Global Challenges: Climate Change, Biodiversity Loss, and Geopolitical Risk</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Alliance for Research on Corporate Sustainability (ARCS) 18th Annual Research Conference</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>Nanyang Business School, Nanyang Technological University (Singapore)</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>Climate change/risk management, decarbonization challenges and opportunities, technology/AI-driven sustainability solutions, corporate impacts on biodiversity and nature-based business solutions, sustainability reporting and disclosure, sustainable/responsible supply chains, sustainable finance, green marketing, green entrepreneurship, renewable energy investments, cleantech innovation, sustainable natural resource management, business/NGO partnerships, sustainable mobility, social dimensions of sustainability such as inequality, fair wages and working conditions, social and environmental justice, cross-border impacts of geopolitical and regulatory dynamics, and “base of the pyramid” (BoP) development strategies.</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Finance Research Revolution Conference</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>Weggis, Switzerland</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>CHF 75 per paper</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>Machine learning for the cross-section of returns, Big data analysis, Large language models and unstructured data, Non-standard datasets for return predictions, Systematic expectations mistakes and predictable returns, Feasible and implementable portfolios, Predictable turning points</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>2026 FMA European Conference</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>Braga, Portugal</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>$75 USD (FMA-members), $85 USD (non-members)</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>40th Annual Mitsui Symposium: Private Capital Markets</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>Ann Arbor, Michigan</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>Technology and Private Markets, Private Markets and Real Economic Outcomes, Access to and Democratization of Private Markets, Private Equity and Venture Capital, Private Credit and Direct Lending, Private Real Assets, Entrepreneurship and Innovation</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Third Chicago Booth Treasury Markets Conference</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>Chicago, Illinois</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>Debt sustainability and public finance, Interactions between monetary and fiscal policy, The international role of U.S. Treasuries and the U.S. dollar, Market structure and fragilities in Treasury markets, Treasury basis trades and leveraged intermediation, Interactions between funding markets and Treasury markets, Liquidity provision, market-making capacity, and regulatory constraints, Financial stability implications of Treasury market dynamics</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Cambridge Corporate Finance Theory Symposium 2026</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>Cambridge, UK</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>£50</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>Theoretical corporate finance, banking, market micro-structure, asset pricing, financial accounting</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>The Fifth Annual Conference on Financial Markets</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>UCLA Anderson, Los Angeles, CA</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>financial markets</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>2026 Global Entrepreneurship and Innovation Research Conference (GEIRC)</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>Cambridge, United Kingdom</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>200 USD</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>Entrepreneurship and innovation, scaling frontier technologies, industrial policy and innovation, university-industry collaboration, global innovation networks, innovation finance, universities and policy in the new geopolitical era</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>

--- a/public/conference_list.xlsx
+++ b/public/conference_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G152"/>
+  <dimension ref="A1:G136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,138 +456,138 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Fifth Annual Junior Faculty Business &amp; Financial Law Workshop</t>
+          <t>UWFC 2027</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-02-04</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-02-07</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Philadelphia, University of Pennsylvania</t>
+          <t>The Cliff Lodge at Snowbird, Utah</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$105 USD</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corporations, securities, finance, accounting, banking, bankruptcy, tax, and general business law</t>
+          <t>financial economics</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SGF Conference 2027</t>
+          <t>European Winter Finance Summit</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2027-04-09</t>
+          <t>2027-03-14</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2027-04-09</t>
+          <t>2027-03-17</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Zurich, Switzerland</t>
+          <t>Hotel Arlberghaus, Zürs, Austria</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CHF 60</t>
+          <t>EUR 50</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>All topic areas of finance</t>
+          <t>Contributions from all areas of finance</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HEC-HKUST-NUS Workshop on Sustainable Finance</t>
+          <t>Sustainability, Trade and Digital Finance (STDF)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2027-02-10</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2027-02-11</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Paris and Hong Kong</t>
+          <t>Department of Banking &amp; Finance, University of Jos, Nigeria</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>USD 100</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sustainable finance</t>
+          <t>Artificial Intelligence in Finance, Stock Market Trading &amp; Investment, FinTech &amp; Digital Finance, Quantitative Finance &amp; Financial Econometrics, AI, ESG &amp; Sustainable Investment, Emerging Markets</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>22nd International Behavioural Finance Conference (IBFC)</t>
+          <t>16th Workshop on Exchange Rates</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>University of Chicago, Booth School of Business, Gleacher Center</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -597,34 +597,34 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Behavioural Asset Pricing, Behavioural Corporate, Biases and Heuristics, Cryptocurrencies, Financial Analysts, Personal Financial Behavior, Financial Markets, Investment Decisions, Mergers and Acquisitions, Political Environment, Retail Investors, Sentiment, Climate Finance, CSR and ESG</t>
+          <t>Drivers of exchange rates and related asset prices, exchange rates and the transmission of monetary policy, FX interventions and supply side shocks, exchange rates and macrofinancial stability frameworks, FX risk premia and their drivers, global linkages between capital flows, foreign exchange rates and risk appetite, international use of currencies and implications for exchange rates, implications of digital and tokenised assets for FX markets</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>European Winter Finance Conference 2027</t>
+          <t>2026 NBS Conference on AI for Finance</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2027-01-10</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hotel Armancette, Saint-Gervais-les-Bains (near Megève), France</t>
+          <t>Nanyang Technological University (Singapore)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -634,34 +634,34 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Generative AI, Foundation Models, and Financial Decision-Making; AI-Driven Asset Pricing, Portfolio Management, and Investment Strategies; Machine Learning for Financial Forecasting and Market Prediction; Alternative Data, Natural Language Processing, and Financial Analytics; AI in Banking, Credit Risk Assessment, and Financial Intermediation; AI, FinTech Innovation, and the Future of Financial Services; Human-AI Collaboration in Financial Markets and Corporate Finance; AI for Climate Finance, ESG Analysis, and Sustainable Investing; AI Governance, Regulation, Ethics, and Responsible Innovation in Finance</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>International Conference in Venice - Artificial Intelligence, Financial Innovation and Credit Risk</t>
+          <t>Risk Theory Society Meeting 2027</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2027-05-28</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2027-05-30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Venice, Italy</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,34 +671,34 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Credit risk, financial innovation, artificial intelligence, financial stability, sustainability, design of credit markets</t>
+          <t>Insurance economics, financial economics related to insurance markets, actuarial science, economic analysis of risk and uncertainty</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Prediction Markets Conference</t>
+          <t>IIM Calcutta-NYU Stern India Research Conference</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Yale School of Management, New Haven, Connecticut</t>
+          <t>WEBINAR</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -708,108 +708,108 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Theoretical and empirical research on prediction markets</t>
+          <t>finance, economics, accounting, challenges and implications of major policy initiatives in India, Indian financial markets, effect of AI on the economies of India, China, and the US</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>63rd Annual Eastern Finance Association Meeting</t>
+          <t>UNC Duke Corporate Finance Conference</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2027-04-07</t>
+          <t>2027-04-02</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2027-04-10</t>
+          <t>2027-04-03</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>Chapel Hill</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>75 USD</t>
+          <t>100 USD</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>All areas of finance</t>
+          <t>Papers in all areas of corporate finance</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Oklahoma Aerospace and Defense Finance Conference</t>
+          <t>3rd LSU Finance Mardi Gras Conference</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2027-03-26</t>
+          <t>2027-02-05</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2027-03-27</t>
+          <t>2027-02-06</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Norman, Oklahoma</t>
+          <t>Baton Rouge, LA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>75 USD</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Theoretical and empirical papers on any aviation, space, or defense finance research topic, including but not limited to venture capital and private equity financing, fiscal impacts of rearmament, capital structure determinants, sustainability in military aviation, risk management, asset pricing, and more.</t>
+          <t>All topics in finance</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Massey Sustainable Finance Conference</t>
+          <t>Financial Research Association 2026 Annual Conference</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Queenstown, New Zealand</t>
+          <t>Las Vegas, NV, USA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -819,71 +819,71 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Artificial intelligence and machine learning applications in Sustainable Finance, Alternative data on firms' digital transformation, Behavioral Finance/Economics and its implications to climate transition, Blue economy, Carbon market and carbon credit, Carbon price forecasting techniques, Circular economy, Corporate Social Responsibility, Climate Finance, Climate risks: assessment and management, Climate transition and portfolio management, Cryptocurrency and digital finance interactions with Sustainable Finance, Diversity, equity and inclusion in Finance, Digital finance, Fintech, and sustainability, Environmental, Social and Governance, Financial markets and climate transition, Household Finance and sustainability, Green Finance, Green Finance and energy security, (Renewable) Energy Finance, Renewable Energy and Sustainability, Sustainable Finance and Accounting</t>
+          <t>New finance papers of general interest to the profession, early work, research by junior scholars</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3rd Annual Boca Finance and Real Estate Conference</t>
+          <t>Winter Finance Summit in Asia 2027</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2027-03-01</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2027-03-04</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Florida Atlantic University, Boca Raton, Florida, USA</t>
+          <t>Iwate, Japan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>$50 USD</t>
+          <t>JPY8,000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>All topics related to finance and real estate</t>
+          <t>All areas of finance and real estate finance, particularly early-stage research not previously presented at major conferences</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>22nd Annual Olin Finance Conference at WashU</t>
+          <t>Stern/Salomon Microstructure Conference</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Washington University in St. Louis</t>
+          <t>Stern School, New York University</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -893,125 +893,125 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>asset pricing, behavioral finance, corporate finance, financial intermediation, household finance, development finance, labor finance</t>
+          <t>The economics of securities markets, theoretical, empirical, and experimental analyses of the role of information in the price-discovery process, definition, measurement, and determinants of liquidity, costs and benefits of alternate trading mechanisms and market structures, measurement and control of transactions costs, role of regulation and the evolution of market design, domestic and international comparisons of trading costs, cross-border listing and trading securities, trading technology and information systems, practical implications of market design for risk management, financial engineering</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>16th Workshop on Exchange Rates</t>
+          <t>3rd Annual Boca Finance and Real Estate Conference</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Florida Atlantic University, Boca Raton, Florida, USA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$50 USD</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Drivers of exchange rates and related asset prices from a financial perspective; Exchange rates and the transmission of monetary policy; FX interventions and supply side shocks; Exchange rates and macrofinancial stability frameworks; FX risk premia and their drivers; Global linkages between capital flows, foreign exchange rates and risk appetite; The international use of currencies and its implications for exchange rates; Implications of digital and tokenised assets for FX markets</t>
+          <t>Finance and real estate</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Southwestern Finance Association 2027 Annual Meeting</t>
+          <t>1st Arctic Finance Conference</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2027-02-17</t>
+          <t>2027-06-24</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-06-27</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Las Vegas, NV</t>
+          <t>Svolvær, Lofoten, Norway</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CHF 60</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>All aspects of finance and financial education</t>
+          <t>Empirical and theoretical contributions from all areas of finance</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>34th Annual PBFEAM and 20th NYCU International conferences</t>
+          <t>22nd International Behavioural Finance Conference (IBFC)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>National Yang Ming Chiao Tung University, Hsinchu, Taiwan</t>
+          <t>University of Chicago, Booth School of Business, Gleacher Center</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>USD $250 for On-line Presenter &amp; USD $300 for On-site Presenter</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Behavioural Asset Pricing, Behavioural Corporate Finance, Biases and Heuristics, Cryptocurrencies, Financial Analysts, Personal Financial Behavior, Financial Markets, Investment Decisions, Mergers and Acquisitions, Political Environment, Retail Investors, Sentiment, Climate Finance, CSR and ESG</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Financial Research Association 2026 Annual Conference</t>
+          <t>2026 Sydney Banking and Financial Stability Conference</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, USA</t>
+          <t>The University of Sydney Business School, Sydney, Australia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1041,34 +1041,34 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>New finance papers of general interest to the profession, early work, research by junior scholars</t>
+          <t>Banking, financial stability, financial intermediation, financial institutions and markets, fintech, cryptocurrency, central bank digital currency, corporate finance, asset pricing, investment and funds management, macro finance</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Fisher AI in Business Conference</t>
+          <t>2026 VINS Annual Conference</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ohio State University, Columbus</t>
+          <t>NYU Shanghai, Shanghai, China</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1078,71 +1078,71 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>AI’s impact on business functions and organizational transformation; multi-agent AI systems and human-AI collaboration; AI-driven customer and employee experiences; AI, sustainability, and ESG; building and scaling AI ventures; AI governance, ethics, and regulation; AI’s influence on strategy and competition; AI’s impact on work and society; measuring AI effectiveness; and AI applications in healthcare, education, and other high-stakes domains.</t>
+          <t>Applications in Asset Management &amp; Trading, Market Microstructure &amp; Liquidity, Emerging Financial &amp; Operational Risks, Governance &amp; Regulation</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>21st Annual Conference on Asia-Pacific Financial Markets (CAFM)</t>
+          <t>Finance Down Under: Building on the Best from the Cellars of Finance</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2027-02-25</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2027-02-27</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CONRAD Seoul</t>
+          <t>Melbourne, Australia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>US$100</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>All areas of finance</t>
+          <t>asset pricing, corporate finance, data and AI in finance, and all other areas of finance</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026 Derivative Markets Conference</t>
+          <t>FMA Annual Meeting</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Auckland, New Zealand</t>
+          <t>Tampa, FL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1152,61 +1152,61 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>All topics related to derivative markets</t>
+          <t>Corporate Finance, Asset Pricing / Investments, Fintech and AI, Financial Institutions, Household Finance, Sustainable Finance</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2027 Midwest Finance Association Annual Meeting</t>
+          <t>34th Annual PBFEAM and 20th NYCU International conferences</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2027-03-18</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2027-03-20</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>National Yang Ming Chiao Tung University, Hsinchu, Taiwan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>75 USD</t>
+          <t>USD $250 for On-line Presenter &amp; USD $300 for On-site Presenter</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>corporate finance, financial institutions, asset pricing, asset management</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2027 Bretton Woods Accounting and Finance Ski Conference</t>
+          <t>11th Annual Young Scholars Finance Consortium</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2027-03-03</t>
+          <t>2027-03-04</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1216,118 +1216,118 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bretton Woods, New Hampshire</t>
+          <t>The George Hotel, College Station, Texas</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>89 USD</t>
+          <t>100 USD</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>All areas of accounting and finance</t>
+          <t>corporate finance and governance, financial markets and intermediation, household finance</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3rd LSU Finance Mardi Gras Conference</t>
+          <t>5th Frankfurt/Mannheim Workshop on Digital Finance</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2027-02-05</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2027-02-06</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA</t>
+          <t>Frankfurt am Main, Germany</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>75 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>All topics in finance</t>
+          <t>digital assets, decentralized finance (DeFi), FinTech, AI</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Financial Econometrics Conference</t>
+          <t>CBER-Tokenomics 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2027-04-21</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2027-04-23</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lancaster University, England</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>30 GBP</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>High-frequency econometrics, Market microstructure, Forecasting, Asset Pricing and investments, Risk neutral density estimation, Fintech &amp; blockchain, Cryptocurrencies, Climate econometrics, Volatility modelling, Artificial intelligence &amp; machine learning, Factor models, Term structure models, Risk modelling, Real time detection of extreme market events, Options &amp; derivatives modelling, Multivariate &amp; high dimensional time series modelling</t>
+          <t>token and protocol design, decentralized finance, stablecoins and digital payments, DAOs and decentralized governance, tokenized real-world assets, prediction markets, AI agents and decentralized AI, economic world models, applications of large language models to macroeconomic, financial, and economy-wide modelling</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026 Sydney Banking and Financial Stability Conference</t>
+          <t>21st Annual Conference on Asia-Pacific Financial Markets (CAFM)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>The University of Sydney Business School, Sydney, Australia</t>
+          <t>CONRAD Seoul</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1337,145 +1337,145 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Banking, financial stability, financial intermediation, financial institutions and markets, fintech, cryptocurrency and central bank digital currency, financial system stability, corporate finance, asset pricing, investment and funds management, macro finance</t>
+          <t>All areas of finance</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IIMB-CCGS International Corporate Governance &amp; Sustainability Conference 2026</t>
+          <t>2026 Vietnam Symposium in Climate Transition (VSCT-2026)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Indian Institute of Management, Bangalore, India</t>
+          <t>The University of Danang - University of Economics, Danang, Vietnam</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Waived for selected Paper Presenters</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Corporate governance and sustainability, Geo-political, economy, supply chain risk and corporate governance, AI, Data Analytics, and Machine Learning: Technology &amp; Governance, Bridging Management and Law for a Responsible Corporation, Corporate Governance and Executive Leadership, Internal &amp; External Mechanisms of Corporate Governance, Corporate Governance in Today’s Business Environment, Board Diversity, Governance for sustainable value creation, Governance in Startups, family business &amp; SMEs, Managing the right balance: Shareholders and Stakeholders, Role of Auditors and Institutional Investors, Corporate Disclosures &amp; Reporting Practices, Environment, Social and Governance, Enterprise Risk Management, Cyber Security &amp; Governance</t>
+          <t>Behavioral finance/economics and its implications for climate transition, Blue economy, Carbon market, Circular economy, Climate change: mitigation and adaptation, Climate change: policy and regulations, Climate finance, Climate risks: assessment and management, Climate transition and COVID-19 recovery, Climate transition and portfolio management, Corporate Social Responsibility (CSR), Energy and environmental issues, Energy markets and energy transition, Environmental, Social and Governance (ESG), Financial markets and climate transition, Geopolitical risk and climate change mitigation, Just climate transition, Low-carbon technologies and innovation, Artificial intelligence and climate transition, Management of extractive industries, Responsible behaviors and sustainability in family business, Responsible business conduct and SDG goals, Role of management, business strategies, and SDG goals, Sustainable business model innovation, Sustainable entrepreneurship, Sustainable infrastructure investment, Sustainable production and consumption, Sustainable key performance indicators</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Conference on CSR, the Economy and Financial Markets</t>
+          <t>2026 Conference on Auditing and Capital Markets</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Düsseldorf, Germany</t>
+          <t>Washington, DC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>€ 150 for regular participants and € 100 for PhD students</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climate risk and pricing, Role of financial markets, banks, institutional investors in CSR, Effects of CSR on valuation, performance, cost of capital, funding and capital structure, Socio-economic aspects and their implications for companies and financial markets, Corporate governance and CSR, Risk management and CSR, CSR reporting and disclosure, ESG backlash and politicization, Sustainability strategy under new constraints, Measurement: information content and reliability of ESG indices, CSR activities and the economy</t>
+          <t>Economic impact of auditing, audit regulation, audit oversight on capital markets</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>International Conference in Banking and Financial Studies 2026 (ICBFS 2026)</t>
+          <t>3rd American Conference of the Academy of Sustainable Finance, Accounting, Accountability &amp; Governance (ASFAAG) 2027</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2027-03-10</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2027-03-12</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Parma, Italy</t>
+          <t>Bentley University, Waltham, Massachusetts</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>No submission fee</t>
+          <t>$400 (Full-time Academics/Practitioners), $300 (Full-time PhD Students), $250 (Online Presentations)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Accounting, auditing, and taxation; Asset allocation and valuation; Banking regulation and financial services; Behavioral and experimental finance/economics; Big data in finance, artificial intelligence, and cybersecurity; Climate finance and sustainability; Corporate finance, IPOs, SEOs, M&amp;A, and crowdfunding; Corporate governance; Country funds, sovereign funds, and hedge funds; Debt markets and instruments; Digital finance, cryptocurrencies, and blockchain; Emerging markets finance; Energy finance and environmental issues; Entrepreneurial finance, venture capital, and private equity; Ethical finance, green finance, ESG, and CSR; Financial accounting and regulation; Financial crises, contagion, integration, and global risk interconnections; Financial engineering and derivatives; Foreign exchange markets and currency issues; Global imbalances and sustainability; Household finance, real estate finance, and microfinance; Market efficiency and behavior; Multinational financial management; Portfolio management and optimization; Risk management and compliance; Small business finance</t>
+          <t>AI, Digital Transformation, Green Innovation, Systemic Resilience, Climate Finance, Climate Change: Mitigation and Adaptation, Sustainable Business Practices, Policy and Regulation, ESG Disclosures, Artificial Intelligence in Sustainability, Managing the Triple Bottom Line, Corporate Social Responsibility, Financial Innovation and Climate Transition, Carbon Emissions, Biodiversity Finance, Green Banking, Governance and Corporate Accountability, Financing Gaps in Sustainability, Political Risk and Sustainability, Market Mechanisms for Natural Resource Resilience</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Colorado Finance Summit 2026</t>
+          <t>Finance at a Time of Change and Uncertainty — Journal of Corporate Finance &amp; Renmin University of China Conference</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vail, Colorado</t>
+          <t>Renmin University of China, Beijing, China</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1485,24 +1485,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>All areas of finance, theoretical and empirical contributions</t>
+          <t>Finance and AI, Finance and politics, Finance and climate change</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>18th Annual Hedge Fund Research Conference</t>
+          <t>Fifth Annual Junior Faculty Business &amp; Financial Law Workshop</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Université Paris Dauphine - PSL, Paris</t>
+          <t>Philadelphia, University of Pennsylvania</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1522,71 +1522,71 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hedge funds, mutual funds, ETFs, private equity funds, institutional investors’ risks and performance, transparency (reporting) and due diligence, financial intermediation activity, hedge fund and broad macroeconomic issues such as systemic risk and contagion, institutional investors’ incentives and activism, portfolio liquidation and liquidity, financial regulation, private equity funds, ETFs</t>
+          <t>Corporations, securities, finance, accounting, banking, bankruptcy, tax, general business law</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>15th LaBS International Banking Workshop</t>
+          <t>SGF Conference 2027</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2027-04-09</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2027-04-09</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>HSE University and online</t>
+          <t>Zurich, Switzerland</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CHF 60</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Banking in Emerging Markets: Challenges and Opportunities, theoretical and empirical research in all fields of Banking or Household finance</t>
+          <t>All topic areas of finance</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Private Equity Research Consortium (PERC) Symposium</t>
+          <t>HEC-HKUST-NUS Workshop on Sustainable Finance</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Chapel Hill, NC</t>
+          <t>Paris and Hong Kong</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1596,34 +1596,34 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Private equity, buyouts, distressed securities, mezzanine financing, special situations, private credit, venture capital, real estate, real assets</t>
+          <t>Sustainable Finance</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>IMRC 2026</t>
+          <t>European Winter Finance Conference 2027</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2027-01-10</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2027-01-13</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>IIM Ahmedabad</t>
+          <t>Hotel Armancette, Saint-Gervais-les-Bains (near Megève), France</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1633,34 +1633,34 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Theoretical and Empirical Asset Pricing, Quality of Financial Reporting and Adoption of IFRS, Market Microstructure and Algorithmic Trading, Insurance / Reinsurance / Pension Funds, Business Cycles, Corporate Finance, Capital Structure and Dividend Policy, Financial Policy Choice, Institutions and Regulation, Enhancing Liquidity in Commodity Derivatives Markets, Public Economics, Asset Allocation and Investment Management, Computational Finance and Financial Econometrics, FDI and Portfolio Capital Flows, Household Finance, International Trade and Exchange Rates, Financial Crises, Systemic Risk and Macro-Finance, Financial Risk Analytics and Management, Financial Analytics, Monetary Policy and Banking, Global Value Chains and Firm Performance, Macroeconomics, Applied Microeconomics</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026 New Zealand Finance Meeting</t>
+          <t>International Conference in Venice - Artificial Intelligence, Financial Innovation and Credit Risk</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Auckland, New Zealand</t>
+          <t>Venice, Italy</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1670,108 +1670,108 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>All topics related to the field of finance</t>
+          <t>Artificial Intelligence, Financial Innovation, Credit Risk, Sustainability, Stability, Responsibility in a Data-Driven Financial System</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6th Conference on Corporate Policies and Asset Prices (COAP)</t>
+          <t>Prediction Markets Conference</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nice, France</t>
+          <t>Yale School of Management, New Haven, Connecticut</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>€50</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>asset pricing anomalies and their explanations; corporate finance models of asset pricing anomalies; dynamic corporate finance and contracting models and their asset pricing implications; the asset pricing implications of sustainable finance; feedback effects from asset prices to corporate decisions; structural estimation of dynamic models using asset price data</t>
+          <t>Theoretical and empirical research on prediction markets</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5th Contemporary Issues in Financial Markets and Banking</t>
+          <t>63rd Annual Eastern Finance Association Meeting</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2027-02-10</t>
+          <t>2027-04-07</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2027-02-11</t>
+          <t>2027-04-10</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Online Conference</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>USD 175</t>
+          <t>$75 USD</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Financial resilience; Green, climate and sustainable finance; Decentralised finance and disruptive financial technologies; Theoretical asset pricing; Empirical asset pricing, liquidity and behavioural economics and finance; Risk management; Financial inclusion; Alternative investments; Crowd-funding; Islamic banking; Banking and financial sector stability and regulation; Financial (dis)integration and Brexit; Artificial intelligence, machine and deep learning applications in finance; Corporate finance and sustainable energy financing; Crisis investment and portfolio management; Corporate governance; International financial management and investment; Market microstructure; Household finance; Real estate and property markets; Metaverse and Blockchain technologies in finance; Intersection between finance and economic theory, especially financial applications of game theory, decision theory, and computational financial economics; experimental economics with implications for financial theory and practice.</t>
+          <t>All areas of finance</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>International Conference on Trade Wars, Geopolitical Fragmentation and Repercussions for Financial and Monetary Stability</t>
+          <t>Oklahoma Aerospace and Defense Finance Conference</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2027-03-26</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2027-03-27</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Brunel University of London (UK)</t>
+          <t>Norman, Oklahoma</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Art of the (trade) deal and financial costs, Asymmetric impacts on regions, commodity exporters, service-oriented economies and manufacturing centres, Capital flows and sudden stops due to trade wars, Central Banking in the age of trade wars and geopolitical conflicts, Central bank digital currencies (CBDCs), trade wars and geopolitical tensions, Currency weaponisation, competitive devaluation and financial instability, Digitisation, financial decoupling and financial stability during trade conflicts, Emerging markets and international financial flows under trade tensions, Empirical and theoretical analyses of strategic financial policies under trade restrictions, Exorbitant privilege of the US$ in the 21st century and the rise of alternative currencies, European Economic and Monetary Union’s financial integration with the US and the Global South, Financialization in the context of trade wars, Global financial imbalances, causes and financial consequences in the context of trade wars, International financial and monetary architecture and stress management in the age of trade conflict, Inflation targeting, trade wars and geopolitical conflicts, Productivity, innovation and efficiency related to technological spillovers and protectionism, Reallocation of global capital, safe havens and asset price bubbles during trade conflicts, Regional financial and monetary integration and the positive role of regions during trade conflicts, Role of central banks and macroprudential policy during trade conflicts, Sustainable financial development of the Global South and trade wars, Tariffs and non-tariff barriers and their negative financial impact on markets and firms</t>
+          <t>Surging venture capital and private equity financing of aerospace and defense companies; Has the Starlink satcom network become SpaceX’s unique financial and economic flywheel?; Fiscal and financial impacts of the Rearmament of the West and incorporation of Ukraine into the alliance; Capital structure determinants for aerospace and defense companies; Will M&amp;A consolidate the space industry as it has the aviation and defense industries?; Sustainability and energy transition in military aviation; Funding of and financial returns from GPS and satellite company investments; Risk management, insurance, and financial engineering in aerospace and defense companies; Can one million satellites really create an orbital data center network?; Asset pricing of and financial returns from aerospace and defense investments; Will SpaceX’s record $86 billion IPO change the financing opportunity set of space companies?; Financing and investment challenges in the evolving commercial aircraft manufacturing duopoly; Differential impacts of asset characteristics on bankruptcy risk in aerospace and defense companies; Behavioral characteristics and leadership styles of aerospace company founders and CEOs; Impacts of international ownership and transit restrictions in the global aviation industry; Obsolescence risk and the financing of space companies; Why are airports state-owned in the US, but privately owned in other developed countries?; Cybersecurity investment and risk management in defense systems; Does government ownership and subsidization help or hurt Chinese space development?; Why is asset leasing pervasive in aviation, modest in defense, and non-existent in the space industry?; The importance of government contracts in promoting aerospace and defense industrial development; How will Lunar Base Alpha and Mars Colony One be financed?; Financial and strategic implications of the rise of drone, missile, and hypersonic warfare; Contrasting payout policies (dividends and share repurchases) of aviation, space, and defense companies; Paying for talent when cash is scarce: executive compensation in aerospace and defense start-ups</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Labor &amp; Finance Group Fall 2026 Conference</t>
+          <t>2026 Massey Sustainable Finance Conference</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Penn State University – Smeal College of Business, State College, PA</t>
+          <t>Queenstown, New Zealand</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1818,34 +1818,34 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Human capital, compensation, and incentives; Labor market power, monopsony/oligopsony, and wage setting; Unions, collective bargaining, and worker representation; Organizational design, internal labor markets, and corporate governance; Labor mobility, non-compete agreements, and talent flows; Labor-related disclosure, regulation, and policy; Labor and financial markets, asset pricing, and corporate policies; Entrepreneurship and innovation</t>
+          <t>Artificial intelligence and machine learning applications in Sustainable Finance, Alternative data on firms' digital transformation, Behavioral Finance/Economics and its implications to climate transition, Blue economy, Carbon market and carbon credit, Carbon price forecasting techniques, Circular economy, Corporate Social Responsibility, Climate Finance, Climate risks: assessment and management, Climate transition and portfolio management, Cryptocurrency and digital finance interactions with Sustainable Finance, Diversity, equity and inclusion in Finance, Digital finance, Fintech, and sustainability, Environmental, Social and Governance, Financial markets and climate transition, Household Finance and sustainability, Green Finance, Green Finance and energy security, (Renewable) Energy Finance, Renewable Energy and Sustainability, Sustainable Finance and Accounting</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CUHK-RAPS-RCFS Conference on Asset Pricing and Corporate Finance</t>
+          <t>22nd Annual Olin Finance Conference at WashU</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Washington University in St. Louis</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1855,34 +1855,34 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Asset Pricing, Corporate Finance</t>
+          <t>asset pricing, behavioral finance, corporate finance, financial intermediation, household finance, development finance, labor finance</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026 ABFER-JFDS Conference on AI for Finance</t>
+          <t>Southwestern Finance Association 2027 Annual Meeting</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2027-02-17</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>International Institute of Finance, No. 1789 Guangxi Road, Hefei, Anhui, China</t>
+          <t>Las Vegas, NV</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1892,34 +1892,34 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Applications of artificial intelligence, machine learning, natural language processing, large language models, AI agents, high-performance computing; Use of unstructured and alternative data in investment, auditing, assurance; Social and economic impacts of AI adoption; Ethical, governance, and regulatory considerations of AI in finance; Quantitative investment strategies, portfolio optimization, digital assets, DeFi, and platform finance using machine learning technologies</t>
+          <t>All aspects of finance and financial education, panel discussions, tutorials</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Financial Economics Meeting</t>
+          <t>Fisher AI in Business Conference</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Ohio State University, Columbus</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1929,34 +1929,34 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Financial markets &amp; asset pricing, Banking, credit &amp; financial stability, Macroeconomics &amp; international finance, Sustainable finance &amp; climate risk, Quantitative methods &amp; emerging approaches</t>
+          <t>AI’s impact on business functions and organizational transformation; multi-agent AI systems and human-AI collaboration; AI-driven customer and employee experiences; AI, sustainability, and ESG; building and scaling AI ventures; AI governance, ethics, and regulation; AI’s influence on strategy and competition; AI’s impact on work and society; measuring AI effectiveness; and AI applications in healthcare, education, and other high-stakes domains.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>39th Australasian Finance and Banking Conference</t>
+          <t>2026 Derivative Markets Conference</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sydney, Australia</t>
+          <t>Auckland, New Zealand</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1966,145 +1966,145 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Opportunities and Risks of AI Technology in Finance, CBDCs, Fintech, and Digital Finance, Sustainable Investment</t>
+          <t>All topics related to derivative markets</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Finance at a Time of Change and Uncertainty</t>
+          <t>2027 Midwest Finance Association Annual Meeting</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2027-03-18</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2027-03-20</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Renmin University of China, Beijing, China</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>75 USD</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Finance and AI, Finance and politics, Finance and climate change</t>
+          <t>corporate finance, financial institutions, asset pricing, asset management</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MIT GCFP 13th Annual Conference</t>
+          <t>2027 Bretton Woods Accounting and Finance Ski Conference</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2027-03-03</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2027-03-06</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cambridge, MA</t>
+          <t>Bretton Woods, New Hampshire</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>89 USD</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Financial regulation in an era of innovation and disruption, AI’s impact on financial markets, labor markets, and the economy; investor protection and fair lending; new risks to financial stability; changing market structure for equities, bonds, and derivatives; growth of event contracts and prediction markets; growth of non-bank credit; developments in stablecoins, digital currencies, and payment systems; risks in “safe” assets such as sovereign debt; international coordination and comparisons; innovations in market architecture and infrastructure.</t>
+          <t>All areas of accounting and finance</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>EUROFIDAI-ESSEC Paris December Finance Meeting</t>
+          <t>Financial Econometrics Conference</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2027-04-21</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2027-04-23</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Pullman Paris Montparnasse Hotel</t>
+          <t>Lancaster University, England</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>75€</t>
+          <t>£30 GBP</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>All areas of finance</t>
+          <t>High-frequency econometrics, Market microstructure, Forecasting, Asset Pricing and investments, Risk neutral density estimation, Fintech &amp; blockchain, Cryptocurrencies, Climate econometrics, Volatility modelling, Artificial intelligence &amp; machine learning, Factor models, Term structure models, Risk modelling, Real time detection of extreme market events, Options &amp; derivatives modelling, Multivariate &amp; high dimensional time series modelling</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Chicago Fed/University of Chicago Conference on Municipal Bond Markets</t>
+          <t>IIMB-CCGS International Corporate Governance &amp; Sustainability Conference 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Chicago</t>
+          <t>Indian Institute of Management, Bangalore, India</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2114,71 +2114,71 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Unpublished and highly policy-relevant research papers on municipal bond markets, primary market frictions, secondary market frictions, role of retail investors, government policies targeting investors, effect of state and federal policies on access to external finance</t>
+          <t>Corporate governance, sustainability, geo-political risks, supply chain risk, AI, data analytics, machine learning, bridging management and law, corporate governance and executive leadership, internal and external mechanisms of corporate governance, board diversity, governance for sustainable value creation, governance in startups, family business &amp; SMEs, shareholders and stakeholders balance, role of auditors and institutional investors, corporate disclosures, environment, social and governance, enterprise risk management, cyber security and governance.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SFS Cavalcade Asia-Pacific 2026</t>
+          <t>Conference on CSR, the Economy and Financial Markets</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>City University of Hong Kong</t>
+          <t>Düsseldorf, Germany</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>$75 USD</t>
+          <t>€150 for regular participants; €100 for PhD students</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>In-depth participation in financial studies, asset pricing, corporate finance</t>
+          <t>Climate risk and pricing; Role of financial markets, banks, institutional investors in CSR; Effects of CSR on valuation, performance, cost of capital, funding and capital structure; Socio-economic aspects and their implications for companies and financial markets; Corporate governance and CSR; Risk management and CSR; CSR reporting and disclosure; ESG backlash and politicization; Sustainability strategy under new constraints; Measurement: information content and reliability of ESG indices; CSR activities and the economy</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sustainable Accounting, Finance and Economics International Conference 2026 (SAFE2026)</t>
+          <t>International Conference in Banking and Financial Studies 2026 (ICBFS 2026)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bandar Sunway, Malaysia</t>
+          <t>Parma, Italy</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2188,34 +2188,34 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sustainability-oriented research in accounting, finance, and economics</t>
+          <t>Accounting, auditing, and taxation; Asset allocation and valuation; Banking regulation and financial services; Behavioral and experimental finance/economics; Big data in finance, artificial intelligence, and cybersecurity; Climate finance and sustainability; Corporate finance, IPOs, SEOs, M&amp;A, and crowdfunding; Corporate governance; Country funds, sovereign funds, and hedge funds; Debt markets and instruments; Digital finance, cryptocurrencies, and blockchain; Emerging markets finance; Energy finance and environmental issues; Entrepreneurial finance, venture capital, and private equity; Ethical finance, green finance, ESG, and CSR; Financial accounting and regulation; Financial crises, contagion, integration, and global risk interconnections; Financial engineering and derivatives; Foreign exchange markets and currency issues; Global imbalances and sustainability; Household finance, real estate finance, and microfinance; Market efficiency and behavior; Multinational financial management; Portfolio management and optimization; Risk management and compliance; Small business finance</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026 Climate Finance &amp; Policy (CFP-2026)</t>
+          <t>Colorado Finance Summit 2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bari, Italy</t>
+          <t>Vail, Colorado</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2225,34 +2225,34 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>AI-driven Climate Risk Assessment and Prediction, Big Data and ESG Decision-making, Carbon Border Adjustment Mechanisms, Carbon Finance and Pricing, Climate Change and Corporate Behavior, Climate Finance for Energy Efficiency, Carbon Taxes, Climate Agreements and Frameworks, Climate Funds and Public Finance, Climate Risk Assessment and Disclosure, ESG Measurement, Ratings &amp; Data Quality, Financing Climate Adaptation and Resilience, Green Finance, Green Bonds and Socially Responsible Bonds, Just Transition, Nature, Biodiversity &amp; Finance, Role of Technology in Climate Finance, Sustainable Investing, Sustainability Regulation &amp; Political Economy</t>
+          <t>All areas of finance, both theoretical and empirical contributions</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026 Global AI Finance Research Conference</t>
+          <t>18th Annual Hedge Fund Research Conference</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Taipei, Taiwan</t>
+          <t>Université Paris Dauphine - PSL, Paris</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2262,71 +2262,71 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Artificial Intelligence (AI), Big Data and Machine Learning, Blockchain and Cryptocurrencies, Security Token Offerings (STOs) and Initial Coin Offerings (ICOs), Decentralized Finance (DeFi), Peer-to-peer lending, FinTech regulation, High-frequency trading and market liquidity, Green FinTech</t>
+          <t>Hedge funds, mutual funds, ETFs, private equity funds, institutional investors’ risks and performance, transparency and due diligence, financial intermediation activity, systemic risk and contagion, institutional investors’ incentives and activism, portfolio liquidation and liquidity, financial regulation</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>37th Annual Conference of the Academy of Behavioral Finance &amp; Economics</t>
+          <t>15th LaBS International Banking Workshop</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Santa Monica, California, USA</t>
+          <t>HSE University and online</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>$99.00 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Behavioral/Cognitive Finance &amp; Economics, Neuroscience/Neuromorphic Computing, Political Economy, Biological Anthropology, Brain-Computer Interfaces, Development of New Financial &amp; Economic Models, Decision Making under risk and uncertainty, Venture Startups &amp; Exits, Financial Markets, Financial Management of Companies, Entrepreneurship, Innovation, Sustainable Finance, Personal Finance, Behavioral Finance applications, Evidence-Based Financial and Retirement Planning, Behavioral/Cognitive Value Investing</t>
+          <t>Banking in Emerging Markets: Challenges and Opportunities, theoretical and empirical research in all fields of Banking, Household finance</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026 UNSW Asset Pricing Workshop</t>
+          <t>Private Equity Research Consortium (PERC) Symposium</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sydney (NSW, Australia)</t>
+          <t>Chapel Hill, NC</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2336,34 +2336,34 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>All areas of Finance, with a special focus on Asset Pricing</t>
+          <t>Private equity, buyouts, distressed securities, mezzanine financing, special situations, private credit, venture capital, real estate, real assets</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>International Conference in Venice - Artificial Intelligence, Financial Innovation and Credit Risk</t>
+          <t>IMRC 2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Venice, Italy</t>
+          <t>IIM Ahmedabad</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2373,14 +2373,14 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Credit Risk and Advanced Analytics; Financial Innovation and Digital Transformation; Artificial Intelligence, Data Governance and Ethical Risk; Sustainability and Long-Term Value Creation; Systemic Risk, Resilience and Policy</t>
+          <t>Theoretical and Empirical Asset Pricing, Quality of Financial Reporting and Adoption of IFRS, Market Microstructure and Algorithmic Trading, Insurance / Reinsurance / Pension Funds, Business Cycles, Corporate Finance, Capital Structure and Dividend Policy, Financial Policy Choice, Institutions and Regulation, Enhancing Liquidity in Commodity Derivatives Markets, Public Economics, Asset Allocation and Investment Management, Computational Finance and Financial Econometrics, FDI and Portfolio Capital Flows, Household Finance, International Trade and Exchange Rates, Financial Crises, Systemic Risk and Macro-Finance, Financial Risk Analytics and Management, Financial Analytics, Monetary Policy and Banking, Global Value Chains and Firm Performance, Macroeconomics, Applied Microeconomics</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>36th Annual Conference on Financial Economics and Accounting (CFEA)</t>
+          <t>2026 New Zealand Finance Meeting</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2390,128 +2390,128 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Toronto, Ontario (Canada)</t>
+          <t>Auckland, New Zealand</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>100 CAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Financial economics and accounting</t>
+          <t>All topics related to the field of finance</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026 Lugano Real Estate and Urban Economics Conference</t>
+          <t>6th Conference on Corporate Policies and Asset Prices (COAP)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Lugano, Switzerland</t>
+          <t>Nice, France, EDHEC Business School</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>€50</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>real estate economics, real estate finance, regional economics, urban economics</t>
+          <t>Asset pricing anomalies and their explanations, corporate finance models of asset pricing anomalies, dynamic corporate finance and contracting models and their asset pricing implications, asset pricing implications of sustainable finance, feedback effects from asset prices to corporate decisions, structural estimation of dynamic models using asset price data</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Santiago Finance Workshop 2026</t>
+          <t>5th Contemporary Issues in Financial Markets and Banking</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2027-02-10</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2027-02-11</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Universidad de Chile, Diag. Paraguay 257, Santiago, Chile</t>
+          <t>Online Conference</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>USD 175</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Any topic in finance or financial economics</t>
+          <t>Financial resilience; Green, climate and sustainable finance; Decentralised finance and disruptive financial technologies; Theoretical asset pricing; Empirical asset pricing, liquidity and behavioural economics and finance; Risk management; Financial inclusion; Alternative investments; Crowd-funding; Islamic banking; Banking and financial sector stability and regulation; Financial (dis)integration and Brexit; Artificial intelligence, machine and deep learning applications in finance; Corporate finance and sustainable energy financing; Crisis investment and portfolio management; Corporate governance; International financial management and investment; Market microstructure; Household finance; Real estate and property markets; Metaverse and Blockchain technologies in finance; Intersection between finance and economic theory, especially financial applications of game theory, decision theory, and computational financial economics; experimental economics with implications for financial theory and practice.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>4th International Conference on Circular Economy, Business Strategy &amp; Management</t>
+          <t>International Conference on Trade Wars, Geopolitical Fragmentation and Repercussions for Financial and Monetary Stability</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>EM Normandie Business School, Caen campus, France</t>
+          <t>Brunel University of London (UK)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2521,34 +2521,34 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>sustainability, ESG, innovation, resilience, circular business models, future of management research</t>
+          <t>Art of the (trade) deal and financial costs; Asymmetric impacts on regions, commodity exporters, service-oriented economies and manufacturing centres; Capital flows and sudden stops due to trade wars; Central Banking in the age of trade wars and geopolitical conflicts; Central bank digital currencies (CBDCs), trade wars and geopolitical tensions; Currency weaponisation, competitive devaluation and financial instability; Digitisation, financial decoupling and financial stability during trade conflicts; Emerging markets and international financial flows under trade tensions; Empirical and theoretical analyses of strategic financial policies under trade restrictions; Exorbitant privilege of the US$ in the 21st century and the rise of alternative currencies; European Economic and Monetary Union’s financial integration with the US and the Global South; Financialization in the context of trade wars; Global financial imbalances, causes and financial consequences in the context of trade wars; International financial and monetary architecture and stress management in the age of trade conflict; Inflation targeting, trade wars and geopolitical conflicts; Productivity, innovation and efficiency related to technological spillovers and protectionism; Reallocation of global capital, safe havens and asset price bubbles during trade conflicts; Regional financial and monetary integration and the positive role of regions during trade conflicts; Role of central banks and macroprudential policy during trade conflicts; Sustainable financial development of the Global South and trade wars; Tariffs and non-tariff barriers and their negative financial impact on markets and firms</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Climate Finance &amp; Sustainability Conference</t>
+          <t>Labor &amp; Finance Group Fall 2026 Conference</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Montréal, QC, Canada</t>
+          <t>Penn State University – Smeal College of Business, State College, PA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2558,34 +2558,34 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sustainability in business, multi-stakeholder governance, managing business impacts on planetary boundaries, ESG factors, sustainability reporting, climate finance, AI in business sustainability, sustainable business models, responsible consumption, operational resilience, sustainable supply chain management</t>
+          <t>Human capital, compensation, and incentives; Labor market power, monopsony/oligopsony, and wage setting; Unions, collective bargaining, and worker representation; Organizational design, internal labor markets, and corporate governance; Labor mobility, non-compete agreements, and talent flows; Labor-related disclosure, regulation, and policy; Labor and financial markets, asset pricing, and corporate policies; Entrepreneurship and innovation</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>China Accounting and Finance Review (CAFR) Special Issue Conference 2026</t>
+          <t>CUHK-RAPS-RCFS Conference on Asset Pricing and Corporate Finance</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Zhongnan University of Economics and Law, Wuhan, China</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2595,71 +2595,71 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>ESG in the AI Era: Challenges and Opportunities; AI-Driven ESG Reporting and Assurance; Algorithmic Bias, Ethics, and Fairness in ESG Analytics; Regulatory Responses to AI-Enabled ESG Practices; AI, Greenwashing, and Corporate Accountability; AI for Sustainable Finance and Investment Decision-Making</t>
+          <t>Asset Pricing, Corporate Finance</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026 FMA Asia/Pacific Conference</t>
+          <t>2026 ABFER-JFDS Conference on AI for Finance</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Massey University, Auckland, New Zealand</t>
+          <t>International Institute of Finance, No. 1789 Guangxi Road, Hefei, Anhui, China</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>$50 USD (FMA-members), $60 USD (non-members)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Financial decision-making, financial management, current issues in finance</t>
+          <t>Applications of artificial intelligence, machine learning, natural language processing, large language models, AI agents, high-performance computing, and other novel analytical methods in finance and financial economics; Use of unstructured and alternative data in investment, auditing, assurance, and related fields; Social and economic impacts of AI adoption; Ethical, governance, and regulatory considerations of AI in finance; Quantitative investment strategies, portfolio optimization, digital assets, DeFi, and platform finance using machine learning technologies or other AI models.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sixth Biennial Conference on Auto Lending</t>
+          <t>Financial Economic Meeting</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Philadelphia</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2669,34 +2669,34 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Consumer demand and vehicle choice, loan pricing and contract design, underwriting and credit risk modeling, dealer intermediation and markups, borrower outcomes and delinquency dynamics, fraud and identity risk, fair lending and consumer compliance, subprime and near-prime market structure, repossession and loss mitigation, servicing and collections, the role of alternative data and automated decisioning, electric vehicles and evolving collateral risk, used vehicle prices and depreciation, auto insurance interactions, fintech and market structure, auto asset-backed securities, spillovers from monetary policy and macroeconomic shocks.</t>
+          <t>Financial markets &amp; asset pricing, Banking, credit &amp; financial stability, Macroeconomics &amp; international finance, Sustainable finance &amp; climate risk, Quantitative methods &amp; emerging approaches</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Frontiers in Machine Learning and Economics: Methods and Applications</t>
+          <t>39th Australasian Finance and Banking Conference</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Philadelphia</t>
+          <t>Sydney, Australia</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2706,34 +2706,34 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Methodological advances in analyzing complex and high-dimensional data sets; Methodological advances in natural language processing, particularly with respect to causal inference; Innovative applications of generative AI; The societal impacts of AI and algorithmic decision-making</t>
+          <t>Opportunities and Risks of AI Technology in Finance, CBDCs, Fintech, and Digital Finance, Sustainable Investment</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Workshop on Innovations in Credit Scoring</t>
+          <t>MIT GCFP 13th Annual Conference</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Virtual</t>
+          <t>Cambridge, MA</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2743,71 +2743,71 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Innovations in credit scoring, alternative data, artificial intelligence, machine learning, data privacy in risk management, credit access</t>
+          <t>financial regulation in an era of innovation and disruption, AI’s impact on financial markets, labor markets and the economy, investor protection and fair lending, new risks to financial stability, changing market structure for equities, bonds, and derivatives, growth of event contracts and prediction markets, growth of non-bank credit, developments in stablecoins, digital currencies and payment systems, risks in “safe” assets such as sovereign debt, international coordination and comparisons, innovations in market architecture and infrastructure</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026 Conference on Real-Time Data Analysis, Methods, and Applications</t>
+          <t>EUROFIDAI-ESSEC Paris December Finance Meeting</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Philadelphia</t>
+          <t>Pullman Paris Montparnasse Hotel</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>75€</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>monitoring and forecasting of economic and financial developments, high-frequency data, survey data, text as data, transactions data, granular data, using preliminary and revised data in economic policy formulation and analysis, machine learning applications in real-time macroeconomics, probabilistic forecasts and assessments of crisis risks, related innovative data sets and toolboxes, seasonal and cyclical adjustment for real-time monitoring and forecasting</t>
+          <t>Latest research in all areas of finance</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026 Jacobs Levy Center Frontiers in Quantitative Finance Conference</t>
+          <t>Chicago Fed/University of Chicago Conference on Municipal Bond Markets</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>Federal Reserve Bank of Chicago</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2817,71 +2817,71 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>quantitative methods and asset pricing</t>
+          <t>Unpublished and highly policy-relevant research papers on municipal bond markets, including primary market frictions, secondary market frictions, the role of retail investors, and the effect of state and federal policies on state and local government access to external finance.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026 AIM Investment Conference</t>
+          <t>SFS Cavalcade Asia-Pacific 2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Austin, Texas</t>
+          <t>City University of Hong Kong</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>75 USD</t>
+          <t>$75 USD</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>mutual funds, hedge funds, pension funds, investment management</t>
+          <t>Fixed Income, Asset Pricing, Corporate Finance</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026 Wharton Conference on Liquidity and Financial Fragility</t>
+          <t>Sustainable Accounting, Finance and Economics International Conference 2026 (SAFE2026)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>University of Pennsylvania, Philadelphia, PA</t>
+          <t>Bandar Sunway, Malaysia</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2891,34 +2891,34 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Coordination failures, self-fulfilling beliefs, and runs; Fragility in banks and non-bank institutions; Liquidity and frictions in financial markets and macroeconomy; Systemic risk and financial regulation; Monetary policy and financial stability; Artificial intelligence (AI) and its implications for financial macroeconomic stability; The rise and potential risks in private credit markets; New payment technologies, stablecoins, tokenization, and their financial stability implications; Geopolitical tensions, trade conflicts, currency competition, and financial fragility; Inflation, interest rate risks, and implications on financial fragility; The real impact of crises and fragility on firms’ financing and investment policies</t>
+          <t>Sustainability-oriented research in accounting, finance, and economics</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Towards a New Synthesis in Islamic Finance: Law, Economics and Shari’ah</t>
+          <t>2026 CLIMATE FINANCE &amp; POLICY (CFP-2026)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Online Conference from Durham University, England, UK</t>
+          <t>Bari, Italy</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2928,34 +2928,34 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Islamic finance, financial development and stability, cultural perspectives, economic perspectives, legal perspectives, Shari’ah perspectives, financial innovation, regulatory oversight, governance mechanisms, economic development, sustainability, social equity, inclusive economic development</t>
+          <t>AI-driven Climate Risk Assessment and Prediction, Big Data and ESG Decision-making, Carbon Border Adjustment Mechanisms, Carbon Finance and Pricing, Climate Change and Corporate Behavior, Climate Finance for Energy Efficiency, Carbon Taxes, Climate Agreements and Frameworks, Climate Funds and Public Finance, Climate Risk Assessment and Disclosure, ESG Measurement, Ratings &amp; Data Quality, Financing Climate Adaptation and Resilience, Green Finance, Green Bonds and Socially Responsible Bonds, Just Transition, Nature, Biodiversity &amp; Finance, Role of Technology in Climate Finance, Sustainable Investing, Sustainability Regulation &amp; Political Economy</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>74th Meeting of the EURO Working Group for Commodities and Financial Modelling (EWGCFM)</t>
+          <t>2026 Global AI Finance Research Conference</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Casa de Campo, La Romana, Dominican Republic</t>
+          <t>Taipei, Taiwan</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2965,108 +2965,108 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Asset Pricing, Corporate Finance, Banking and Financial Institutions, Commodities and Energy Markets, Financial Modelling and Econometrics, Blockchain and Cryptocurrencies, Derivatives and Risk Management, Market Microstructure, Sustainable Finance</t>
+          <t>Artificial Intelligence (AI), Big Data and Machine Learning, Blockchain and Cryptocurrencies, Security Token Offerings (STOs) and Initial Coin Offerings (ICOs), Decentralized Finance (DeFi), Peer-to-peer lending, FinTech regulation, High-frequency trading and market liquidity, Green FinTech</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FIRN 2026 ANU Money, Credit, and Financial Stability Meeting</t>
+          <t>37th Annual Conference of the Academy of Behavioral Finance &amp; Economics</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Australian National University (ANU), Canberra, Australia</t>
+          <t>Santa Monica, California, USA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$99.00 USD</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Monetary policy and transmission mechanisms, Credit markets and financial intermediation, Banking, liquidity, and regulation, Financial crises and systemic risk, Macro-finance</t>
+          <t>Behavioral/Cognitive Finance &amp; Economics, Neuroscience/Neuromorphic Computing, Political Economy, Biological Anthropology, Brain-Computer Interfaces</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Inaugural Annual Conference on Insurance</t>
+          <t>2026 UNSW Asset Pricing Workshop</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Chicago</t>
+          <t>Sydney (NSW, Australia)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0 AUD</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>life insurance, Property &amp; Casualty insurance, Reinsurance and risk transfer, Mergers and other ownership changes, Private equity ownership and impact on industry, Indexed, variable annuities, and other savings products, Household insurance choices, Insurances’ investment and funding strategies, Catastrophe risk, Impact of insurance regulation</t>
+          <t>All areas of Finance with a special focus on Asset Pricing</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Payments, Digital Assets, AI and the Future of Financial Markets</t>
+          <t>International Conference in Venice - Artificial Intelligence, Financial Innovation and Credit Risk</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Imperial Business School, London</t>
+          <t>Venice, Italy</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3076,71 +3076,71 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Digital platforms, banking, and financial intermediation; Artificial intelligence, machine learning, and financial decision-making; Blockchain, tokenization, digital assets, and decentralized finance; Payment systems, central bank digital currencies, and stablecoins; FinTech regulation, supervision, market design, and financial stability; Data, privacy, cybersecurity, and consumer protection in finance; Entrepreneurial finance, venture capital, and innovation in financial services; Household finance, inclusion, and welfare effects of financial technology; Market microstructure, trading technologies, and liquidity; Competition between banks, platforms, and non-bank financial institutions</t>
+          <t>Credit risk, financial innovation, artificial intelligence, sustainability, stability, responsibility, risk management, digital transformation, regulation, ethical risk, and systemic risk.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026 Conference on Auditing and Capital Markets</t>
+          <t>36th Annual Conference on Financial Economics and Accounting (CFEA)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Washington, DC</t>
+          <t>Toronto, Ontario (Canada)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>100 CAD</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Economic impact of auditing, audit regulation, audit oversight on capital markets, auditing issuers and brokers and dealers</t>
+          <t>Financial economics and accounting</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Future Scholars in Finance Forum</t>
+          <t>2026 Lugano Real Estate and Urban Economics Conference</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Beijing, China</t>
+          <t>Lugano, Switzerland</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3150,34 +3150,34 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>All areas of finance</t>
+          <t>real estate finance, urban economics, real estate economics, regional economics</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Prototypes for Humanity 2026 Short Papers Platform</t>
+          <t>Santiago Finance Workshop 2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dubai, UAE</t>
+          <t>Universidad de Chile, Diag. Paraguay 257, Santiago, Chile</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3187,34 +3187,34 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Wellbeing and Human Performance, Infrastructures and Cities, Autonomous Systems and Advanced Manufacturing, Environment, Sustainability and Energy, Mobility and Logistics, Socio-Economic Empowerment, Digital Economies and Future Markets, Open and Speculative</t>
+          <t>Any topic in finance or financial economics</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026 Federal Reserve Stress Testing Research Conference</t>
+          <t>4th International Conference on Circular Economy, Business Strategy &amp; Management</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Boston, Massachusetts</t>
+          <t>EM Normandie Business School, Caen campus, France</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3224,34 +3224,34 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>The economic and macroprudential effects of stress tests and bank regulation, Novel approaches to modeling bank profitability, financial risks, and operational risks, Design and applications of stress scenarios and reverse stress testing, Nonbank credit intermediation, Financial instruments for risk transfer, Recent developments in bank regulation, The impact of emerging technologies on banks and their regulators</t>
+          <t>sustainability, ESG, innovation, resilience, circular business models, future of management research</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EBA's 15th Policy Research Workshop</t>
+          <t>Climate Finance &amp; Sustainability Conference</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>EBA premises (Paris, France) and remotely</t>
+          <t>Montréal, QC, Canada</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3261,34 +3261,34 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Competitiveness and efficiency in the prudential rulebook without undermining resilience, Impacts of efficiency and proportionality, Competition, innovation, market entry, cross border growth and new areas under financial supervision, Proportionate integration of ESG risks in governance, strategy, and remuneration frameworks</t>
+          <t>Sustainability in business across various disciplines including strategy and management, accounting and finance, entrepreneurship and innovation, marketing and responsible consumption, supply chain and operations management</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3rd Financial Fraud, Misconduct and Market Manipulation Conference</t>
+          <t>China Accounting and Finance Review (CAFR) Special Issue Conference 2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Lancaster University, England</t>
+          <t>Zhongnan University of Economics and Law, Wuhan, China</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3298,71 +3298,71 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Theoretical and empirical analysis of financial fraud, case studies of recent instances of market misconduct, insider trading, implications of financial fraud/market manipulation for market efficiency, stability, and asset pricing, market manipulation at a high-frequency (intraday) level, fraudulent activities and cryptocurrency markets, social networks, fake news, and their effect on financial markets, money laundering and banking, conflicts of interests and their implications for various stakeholders and financial markets, hedge funds/mutual funds and their involvement in market misconduct, statistical/machine learning methods for fraud detection, cyber security and cyber risk management, regulatory response to financial misconduct, unintended consequences of politics and regulations</t>
+          <t>ESG in the AI Era: Challenges and Opportunities; AI-Driven ESG Reporting and Assurance; Algorithmic Bias, Ethics, and Fairness in ESG Analytics; Regulatory Responses to AI-Enabled ESG Practices; AI, Greenwashing, and Corporate Accountability; AI for Sustainable Finance and Investment Decision-Making</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>22nd Annual Haskell &amp; White Corporate Reporting and Governance Conference</t>
+          <t>2026 FMA Asia/Pacific Conference</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>California State University, Fullerton</t>
+          <t>Massey University, Auckland, New Zealand</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$50 USD (FMA-members), $60 USD (non-members)</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>All areas of accounting and finance, corporate reporting, governance, and financial markets</t>
+          <t>Financial decision-making, financial management, related topics</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>25th Annual Bank Research Conference</t>
+          <t>Sixth Biennial Conference on Auto Lending</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Arlington, VA</t>
+          <t>Federal Reserve Bank of Philadelphia</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3372,71 +3372,71 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Regulatory reform options and considerations, Risk and resiliency in the financial system, Real effects of financial turmoil, Innovations in financial intermediation, Deposit insurance and stability, Emerging competitive threats to traditional banking, AI and technology in finance, Banks’ role in the 21st Century</t>
+          <t>auto lending, consumer finance, consumer demand and vehicle choice, loan pricing and contract design, underwriting and credit risk modeling, dealer intermediation and markups, borrower outcomes and delinquency dynamics, fraud and identity risk, fair lending and consumer compliance, subprime and near-prime market structure, repossession and loss mitigation, servicing and collections, alternative data and automated decisioning, electric vehicles and evolving collateral risk, used vehicle prices and depreciation, auto insurance interactions, fintech and market structure, auto asset-backed securities, spillovers from monetary policy and macroeconomic shocks</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>The Future of Decision-Making and Risk-Taking: Bridging Finance, Economics, Brain, and Behavior</t>
+          <t>Frontiers in Machine Learning and Economics: Methods and Applications</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2023-07-12</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Santa Monica, California, USA</t>
+          <t>Federal Reserve Bank of Philadelphia</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>$99.00 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Behavioral/Cognitive Finance &amp; Economics, Neuroscience/Neuromorphic Computing, Political Economy, Biological Anthropology, Brain-Computer Interfaces, Development of New Financial &amp; Economic Models, Advancing Knowledge and Understanding, Applications: Behavioral Finance in Practice</t>
+          <t>Methodological advances in analyzing complex and high-dimensional data sets, Methodological advances in natural language processing (particularly with respect to causal inference), Innovative applications of generative AI, The societal impacts of AI and algorithmic decision-making</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>17th Emerging Markets Conference</t>
+          <t>Workshop on Innovations in Credit Scoring</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Mumbai, India</t>
+          <t>Virtual</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3446,71 +3446,71 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>The sources of economic success or failure in EMs, Finance in EMs, Political economy, law, public administration, regulation in EMs, The impact of populism upon the possibility of sustained growth, Insights into large EMs that matter, Insights from narrow research projects, The new phase of globalisation and its consequences, Features of a society that enable or disable convergence, The puzzles faced by decision makers, Grand challenges such as climate change, State capability in EMs, The interplay of military affairs, foreign policy and economics for EMs</t>
+          <t>Innovations in credit scoring, alternative data, artificial intelligence, machine learning, risk management, credit access</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026 International Forum on Financial Regulation and RegTech</t>
+          <t>2026 Conference on Real-Time Data Analysis, Methods, and Applications</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Beihang University, Beijing, China</t>
+          <t>Federal Reserve Bank of Philadelphia</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2000 CNY (Regular/Faculty), 1000 CNY (Student)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Financial regulation, Regulatory Technology (RegTech), FinTech, financial security, risk assessment and management, AI and Large Language Models (LLMs) in finance</t>
+          <t>monitoring and forecasting of economic and financial developments, high-frequency data, survey data, text as data, transactions data, granular data, using preliminary and revised data in economic policy formulation and analysis, machine learning applications in real-time macroeconomics, probabilistic forecasts and assessments of crisis risks, related innovative data sets and toolboxes, seasonal and cyclical adjustment for real-time monitoring and forecasting</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026 International Symposium on Climate, Finance, and Sustainability (ISCFS-2026)</t>
+          <t>2026 Jacobs Levy Center Frontiers in Quantitative Finance Conference</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>House of Management Science, Paris Pantheon-Assas University, France</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3520,71 +3520,71 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbon Finance and Taxes, Climate and Economic Modeling in Policy Making, Climate Finance, Climate Negotiations and Scenarios, Climate Risk and Disclosures, Climate-resilient Economies, Energy Derivatives: Pricing and Hedging, Energy Markets: Modeling and Forecasting, Energy, Environment, and Climate Models, Financial and Economic Analysis of Energy Markets, Financial Regulation of Energy and Environmental Markets, Green Finance and Sustainable Investment, Just Energy Transition, Macroeconomic Implications of Net-Zero Carbon Emissions, Nature-based Financial Instruments for Climate Change Mitigation, Natural Resources, Risk, Welfare, and Social Preferences, Renewable Energy, Regulation and Energy Governance, Role of Financial Institutions in Sustainability</t>
+          <t>Quantitative methods and asset pricing</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5th Annual Academic - 2026 DeFi &amp; Digital Currencies Conference</t>
+          <t>2026 AIM Investment Conference</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>The Shard, London, UK</t>
+          <t>Austin, Texas</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>£45</t>
+          <t>75 USD</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>DeFi Protocols, Lending and Borrowing Protocols, Decentralized Exchanges (DEXs), Blockchain Economics, Stablecoins and CBDCs, Digital Money and Payments, Tokenisation of real-world assets, Traditional and Decentralized Finance Interaction, Digital Finance and Inclusion</t>
+          <t>mutual funds, hedge funds, pension funds, investment management</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3rd Arne Ryde Conference on Crypto, Fintech and Payments</t>
+          <t>2026 Wharton Conference on Liquidity and Financial Fragility</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Lund, Sweden</t>
+          <t>University of Pennsylvania, Philadelphia, PA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3594,34 +3594,34 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Crypto and blockchain technology, Crypto markets, households, and the real economy, Environmental and social impact of crypto markets, Interaction between traditional finance and decentralized finance, Stablecoins, Central Bank Digital Currencies (CBDCs), Financial technology (Fintech), Payment systems, Open banking and data sharing, Digital tools in financial services, Financial inclusion, development, and welfare in digital finance</t>
+          <t>Coordination failures, self-fulfilling beliefs, and runs; Fragility in banks and non-bank institutions; Liquidity and frictions in financial markets and macroeconomy; Systemic risk and financial regulation; Monetary policy and financial stability; Artificial intelligence (AI) and its implications for financial macroeconomic stability; The rise and potential risks in private credit markets; New payment technologies, stablecoins, tokenization, and their financial stability implications; Geopolitical tensions, trade conflicts, currency competition, and financial fragility; Inflation, interest rate risks, and implications on financial fragility; The real impact of crises and fragility on firms’ financing and investment policies</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Institute for Quantitative Investment Research Autumn Residential Seminar 2026</t>
+          <t>Towards a New Synthesis in Islamic Finance: Law, Economics and Shari’ah</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ashdown Park Hotel &amp; Country Club, Wych Cross, East Sussex, UK</t>
+          <t>Online Conference from Durham University, England, UK</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3631,34 +3631,34 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>New risks in a changing political environment, innovative and high-quality research related to investment management</t>
+          <t>Islamic finance, financial innovation, regulatory oversight, governance mechanisms, economic development, sustainability, social equity, inclusive economic development</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10th Shanghai-Edinburgh-London Finance Conference On Sustainable Finance in the Digital Era</t>
+          <t>74th Meeting of the EURO Working Group for Commodities and Financial Modelling (EWGCFM)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Shanghai and online</t>
+          <t>Casa de Campo, La Romana, Dominican Republic</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3668,34 +3668,34 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Financial development, financial inclusion, and their role in sustainable economic growth; Policy frameworks and regulatory challenges shaping sustainable finance adoption in developed and emerging markets; Cross-border sustainable finance flows and international regulatory coordination; Corporate governance, greenwashing detection, and market responses to ESG commitments; ESG backlash, anti-ESG movements, and the political economy of sustainable finance; AI and machine learning applications in ESG investment strategies, sustainability disclosure, and climate risk modelling; Big data and natural language processing in measuring and monitoring ESG performance; Blockchain applications in carbon markets, green bonds, and regulatory compliance; Digital finance, decentralised finance (DeFi), and emerging technologies in supporting a low-carbon transition; Fintech-enabled green lending, climate insurance, and impact investing.</t>
+          <t>Asset Pricing, Corporate Finance, Banking and Financial Institutions, Commodities and Energy Markets, Financial Modelling and Econometrics, Blockchain and Cryptocurrencies, Derivatives and Risk Management, Market Microstructure, and Sustainable Finance</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>22nd Annual Conference of the Asia-Pacific Association of Derivatives</t>
+          <t>FIRN 2026 ANU Money, Credit, and Financial Stability Meeting</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Busan, Korea</t>
+          <t>Australian National University (ANU), Canberra, Australia</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3705,34 +3705,34 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Derivatives; Volatility; Risk Management; Asset Pricing; Investments; Corporate Finance; Market Microstructure; Fintech; Regulation; Behavioral Finance</t>
+          <t>Monetary policy and transmission mechanisms, Credit markets and financial intermediation, Banking, liquidity, and regulation, Financial crises and systemic risk, Macro-finance</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>FIRN Melbourne Asset Pricing Meeting</t>
+          <t>Inaugural Annual Conference on Insurance</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Melbourne, Australia</t>
+          <t>Federal Reserve Bank of Chicago</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3742,34 +3742,34 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>theoretical and empirical models of asset prices and returns, return predictability, empirical methodology, macro-finance, the study of financial institutions as related to asset prices, information and liquidity in asset markets, behavioural investment studies, asset market structure and microstructure, risk analysis, hedge funds, mutual funds, pension funds, ESG, and alternative investments</t>
+          <t>life insurance, Property &amp; Casualty insurance, Reinsurance and risk transfer, Mergers and other ownership changes, Private equity ownership and impact on industry, Indexed, variable annuities, and other savings products, Household insurance choices, Insurances’ investment and funding strategies, Catastrophe risk, Impact of insurance regulation</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Johns Hopkins Carey Finance Conference</t>
+          <t>Payments, Digital Assets, AI and the Future of Financial Markets</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Johns Hopkins Carey Business School, 100 International Drive, Baltimore, MD</t>
+          <t>Imperial Business School, London</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3779,71 +3779,71 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>All areas of finance, particularly early-stage papers</t>
+          <t>Digital platforms, banking, and financial intermediation; Artificial intelligence, machine learning, and financial decision-making; Blockchain, tokenization, digital assets, and decentralized finance; Payment systems, central bank digital currencies, and stablecoins; FinTech regulation, supervision, market design, and financial stability; Data, privacy, cybersecurity, and consumer protection in finance; Entrepreneurial finance, venture capital, and innovation in financial services; Household finance, inclusion, and welfare effects of financial technology; Market microstructure, trading technologies, and liquidity; Competition between banks, platforms, and non-bank financial institutions</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>5th Holden Conference in Finance and Real Estate</t>
+          <t>Future Scholars in Finance Forum</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bloomington, IN</t>
+          <t>Beijing, China</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>$95 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Empirical and theoretical papers in all finance and real estate areas</t>
+          <t>All areas of finance</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>12th P2P Financial Systems International Workshop (P2PFISY 2026)</t>
+          <t>Prototypes for Humanity 2026 Short Papers Platform</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Astana, Kazakhstan</t>
+          <t>Dubai, UAE</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3853,34 +3853,34 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Regulation &amp; Compliance in Digital Asset Markets, Fraud, Financial Crime &amp; Forensics in Crypto Markets, CBDCs and Digital Public Infrastructure, Stablecoins and Digital Payment Systems, Artificial Intelligence in Financial Systems, Consumer Protection, Data Governance, and Trust in Digital Finance, Tokenisation of Real-World Assets (RWA)</t>
+          <t>Wellbeing and Human Performance, Infrastructures and Cities, Autonomous Systems and Advanced Manufacturing, Environment, Sustainability and Energy, Mobility and Logistics, Socio-Economic Empowerment, Digital Economies and Future Markets, Open and Speculative</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026 Annual Community Bank Research Conference</t>
+          <t>2026 Federal Reserve Stress Testing Research Conference</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of St. Louis in St. Louis, MO</t>
+          <t>Boston, Massachusetts</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3890,34 +3890,34 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>The role of community banks in the U.S. financial system, the provision of financial services to households, small businesses, and small farms, impact of community banks on local/state economic activity, community banks’ response to financial and economic shocks and the associated policy responses, the effects of regulatory policy on community banks, quantifying regulatory and compliance costs, intended and unintended effects of regulatory requirements, antitrust policy and community banks, challenges and opportunities faced by community banks, competition from large banks, credit unions, and nonbanks including financial technology firms, funding and liquidity issues including FHLB advances and central bank lending facilities, collaborations/partnerships with financial technology and crypto firms, payments issues, the effects of new payment technologies and trends, the effects of rapid technological advances in banking, operational risk, advantages and disadvantages of the community bank business model, bank consolidation, noninterest/fee income, benefits of local knowledge and strong relationships, costs of operating at a small scale</t>
+          <t>The economic and macroprudential effects of stress tests and bank regulation, Novel approaches to modeling bank profitability, financial risks, and operational risks, Design and applications of stress scenarios and reverse stress testing, Nonbank credit intermediation, Financial instruments for risk transfer, Recent developments in bank regulation, The impact of emerging technologies on banks and their regulators</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Stigler Center-CEPR Political Economy of Finance Conference 2026: Crony Capitalism in 21st Century America</t>
+          <t>EBA's 15th Policy Research Workshop</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Gleacher Center - Chicago</t>
+          <t>EBA premises (Paris, France) and remotely</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3927,71 +3927,71 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Crony capitalism in 21st century America, political economy dynamics, relationship between economic and political power</t>
+          <t>Competitiveness and efficiency in the prudential rulebook without undermining resilience; Impacts of efficiency and proportionality; Competition, innovation, market entry, cross border growth and new areas under financial supervision; Proportionate integration of ESG risks in governance, strategy, and remuneration frameworks</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>15th Fixed Income and Financial Institutions (FIFI) Conference</t>
+          <t>3rd Financial Fraud, Misconduct and Market Manipulation Conference</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>University of South Carolina in Columbia, SC</t>
+          <t>Lancaster University, England</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>75 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>fixed income, commercial and investment banks, asset management and mutual fund companies, short sellers, hedge funds, broker-dealers, insurance companies</t>
+          <t>Theoretical and empirical analysis of financial fraud, Case studies of recent instances of market misconduct, Insider trading, Implication of financial fraud/market manipulation for market efficiency, stability, and asset pricing, Market manipulation at a high-frequency (intraday) level, Fraudulent activities and crypto currency markets, Social networks, fake news, and their effect on financial markets, Money laundering and banking, Conflicts of interests and their implications for various stakeholders and financial markets, Hedge funds/Mutual funds and their involvement in market misconduct, Statistical/Machine Learning methods for fraud detection, Cyber security and cyber risk management, Regulatory response to financial misconduct, Unintended consequences of politics and regulations</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Higher Education Finance Research Conference</t>
+          <t>22nd Annual Haskell &amp; White Corporate Reporting and Governance Conference</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Philadelphia</t>
+          <t>California State University, Fullerton</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4001,34 +4001,34 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Financial aid, student debt, higher education finance</t>
+          <t>All areas of accounting and finance, including interdisciplinary research related to corporate reporting, governance, and financial markets</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Wharton–Chicago–Harvard Insolvency and Restructuring Conference (WCHIRC)</t>
+          <t>25th Annual Bank Research Conference</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>University of Pennsylvania, Philadelphia, PA</t>
+          <t>Arlington, VA</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4038,145 +4038,145 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Corporate financial distress and bankruptcy, Liability management and out-of-court restructurings, Chapter 11 and formal reorganization processes, Consumer bankruptcy, Leveraged lending and private credit, Creditor governance and capital structure dynamics, Distressed debt markets and asset pricing, Financial contracting and covenant design, Bankruptcy law, courts, and institutional design, Operational restructuring and firm performance</t>
+          <t>Regulatory reform options and considerations, Risk and resiliency in the financial system, Real effects of financial turmoil, Innovations in financial intermediation, Deposit insurance and stability, Emerging competitive threats to traditional banking, AI and technology in finance, Banks’ role in the 21st Century</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Financial Decision-Making Conference 2026</t>
+          <t>The Future of Decision-Making and Risk-Taking: Bridging Finance, Economics, Brain, and Behavior</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Bozeman, MT</t>
+          <t>Santa Monica, California, USA</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$99.00 USD</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>household finance, financial literacy and education, consumer financial behavior, retirement and savings decisions, financial education interventions, fintech and digital finance, financial advice and delegation, debt and credit decisions, insurance decisions, behavioral finance, financial inclusion</t>
+          <t>Behavioral/Cognitive Finance &amp; Economics, Neuroscience/Neuromorphic Computing, Political Economy, Biological Anthropology, Brain-Computer Interfaces, Development of New Financial &amp; Economic Models, Decision Making under risk and uncertainty, Venture Startups &amp; Exits, Trust in Financial/Capital Markets, Financial Management of Companies, Entrepreneurship and Innovation, Personal Finance, Behavioral Finance applications, Empirical Works in AI generated databases, Evidence-Based Financial Planning, Neuromorphic-based Strategies, Regulation and Valuation.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Finance and Real Estate Conference 2026</t>
+          <t>17th Emerging Markets Conference</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Miami University, Oxford, OH</t>
+          <t>Mumbai, India</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>$50 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Asset pricing and valuation, Corporate finance, Real estate markets and investment, Risk management and financial regulation, Urban economics and housing policy, Sustainable and green finance, Behavioral finance</t>
+          <t>The sources of economic success or failure in EMs; Finance in EMs; Political economy, law, public administration, regulation in EMs; The impact of populism upon the possibility of sustained growth; Insights into large EMs; Insights from narrow research projects; The new phase of globalisation; Features of a society enabling or disabling convergence; The puzzles faced by decision makers; Grand challenges such as climate change; State capability in EMs; The interplay of military affairs, foreign policy and economics for EMs</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>UGA Fall Finance Conference 2026</t>
+          <t>2026 International Forum on Financial Regulation and RegTech</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Athens, GA</t>
+          <t>Beihang University, Beijing, China</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>70 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>All areas of finance</t>
+          <t>Financial Regulation &amp; RegTech Innovation, Risk Assessment &amp; Management, AI, LLMs &amp; Financial Infrastructure</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Inquire Europe Autumn Conference: “Expectations and Asset Prices”</t>
+          <t>2026 International Symposium on Climate, Finance, and Sustainability (ISCFS-2026)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Prague, Czech Republic</t>
+          <t>House of Management Science, Paris Pantheon-Assas University, 1 rue Guy-de-la-Brosse 75005 Paris, France</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4186,108 +4186,108 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Expectations and asset prices, deviations from rational expectations, implications of optimism and pessimism in asset valuations, investment strategies and anomalies, factor investing, tactical asset allocation, portfolio choice under uncertainty, short selling, institutional investing, asset management</t>
+          <t>Carbon Finance and Taxes, Climate and Economic Modeling in Policy Making, Climate Finance, Climate Negotiations and Scenarios, Climate Risk and Disclosures, Climate-resilient Economies, Energy Derivatives: Pricing and Hedging, Energy Markets: Modeling and Forecasting, Energy, Environment, and Climate Models, Financial and Economic Analysis of Energy Markets, Financial Regulation of Energy and Environmental Markets, Green Finance and Sustainable Investment, Just Energy Transition, Macroeconomic Implications of Net-Zero Carbon Emissions, Nature-based Financial Instruments for Climate Change Mitigation, Natural Resources, Risk, Welfare, and Social Preferences, Renewable Energy, Regulation and Energy Governance, Role of Financial Institutions in Sustainability</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>WFE’s Sustainability Conference 2026</t>
+          <t>5th Annual Academic - 2026 DeFi &amp; Digital Currencies Conference</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>The Shard, London, UK</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>£45</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Transition finance and market design, Regulatory fragmentation and divergence, Sustainability reporting, Nature and biodiversity in capital markets, Just transition, social and gender finance, Proportionality for SMEs and emerging markets, Carbon market architecture</t>
+          <t>DeFi Protocols, Lending and Borrowing Protocols, Decentralized Exchanges, Blockchain Economics, Stablecoins and CBDCs, Digital Money and Payments, Tokenisation of real-world assets, Traditional and Decentralized Finance Interaction, Digital Finance and Inclusion</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026 FMA Annual Meeting</t>
+          <t>3rd Arne Ryde Conference on Crypto, Fintech and Payments</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Tampa, FL</t>
+          <t>Lund, Sweden</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>$75 (current FMA members); $85 (non-members)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Financial decision-making, financial management, and related topics</t>
+          <t>Crypto and blockchain technology, Crypto markets and the real economy, Environmental and social impact of crypto markets, Interaction between traditional finance and decentralized finance, Stablecoins, Central Bank Digital Currencies (CBDCs), Financial technology (Fintech), Payment systems, Open banking and data sharing, Digital tools in financial services, Financial inclusion, development, and welfare in digital finance</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>3rd AI in Finance Conference</t>
+          <t>Institute for Quantitative Investment Research Autumn Residential Seminar 2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Montréal, QC, Canada</t>
+          <t>Ashdown Park Hotel &amp; Country Club, Wych Cross, East Sussex, UK</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4297,34 +4297,34 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Machine learning and artificial intelligence in asset pricing and financial econometrics, Portfolio management, trading strategies, and risk management using AI, Large language models (LLMs), NLP, and textual analysis in finance, Corporate finance applications including M&amp;A and investment decisions, Banking, credit markets, and financial intermediation, Cryptocurrency, digital assets, and decentralized finance, ESG, sustainability, and climate finance, Financial regulation, policy analysis, and central bank communication, Real estate finance and urban economics, Alternative data and high-dimensional financial datasets, Investor behavior, sentiment, and attention, Macroeconomic and financial risk forecasting, AI in Sustainability and Climate Finance, AI and Real Estate</t>
+          <t>New risks in a changing political environment</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026 Summer Research Conference</t>
+          <t>10th Shanghai-Edinburgh-London Finance Conference On Sustainable Finance in the Digital Era</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Indian School of Business, Hyderabad Campus</t>
+          <t>Shanghai and online</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4334,34 +4334,34 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Recent Advances in Finance, corporate finance and its interface with asset pricing, behavioral finance, financial intermediation, household finance, market microstructure</t>
+          <t>Financial development, financial inclusion, policy frameworks for sustainable finance, cross-border sustainable finance, corporate governance, ESG backlash, AI applications in ESG investment, big data in ESG performance, blockchain applications in carbon markets, digital finance and low-carbon transition, fintech-enabled green lending</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>International Risk Management Conference 2026</t>
+          <t>22nd Annual Conference of the Asia-Pacific Association of Derivatives</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Warsaw, Poland</t>
+          <t>Busan, Korea</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4371,145 +4371,145 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Asset pricing; Banking; Financial econometrics; Capital markets; Financial intermediation; Corporate finance; Financial crises; Corporate governance; Market microstructure; Financial regulation; International corporate finance; Risk management; Emerging market; Corporate investment decision; Global risk markets; Macro-financial linkages; Financial policy securitization; Behavioural finance; Financial integration; Mathematical &amp; computational finance; Stochastic optimization approaches in finance; Mergers &amp; acquisitions; Modelling, money and liquidity; Sustainable finance; Climate change risk; AI innovation; crypto and related assets and technology</t>
+          <t>Derivatives; Volatility; Risk Management; Asset Pricing; Investments; Corporate Finance; Market Microstructure; Fintech; Regulation; Behavioral Finance</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>The Second USTC Frontiers in Finance Conference</t>
+          <t>FIRN Melbourne Asset Pricing Meeting</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>International Finance Institute, University of Science and Technology of China, No. 1789 Guangxi Road, Binhu New District, Hefei City, Anhui Province, P.R.China</t>
+          <t>Melbourne, Australia</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>0 CNY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>All topics of finance</t>
+          <t>theoretical and empirical models of asset prices and returns, return predictability, empirical methodology, macro-finance, the study of financial institutions as related to asset prices, information and liquidity in asset markets, behavioural investment studies, asset market structure and microstructure, risk analysis, hedge funds, mutual funds, pension funds, ESG, and alternative investments</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Fischer-Shain Research Conference 2026</t>
+          <t>Johns Hopkins Carey Finance Conference</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>Johns Hopkins Carey Business School, 100 International Drive, Baltimore, MD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>50 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>financial intermediation, banking, financial services</t>
+          <t>All areas of finance, particularly early-stage papers</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ECB Money Market Conference 2026</t>
+          <t>5th Holden Conference in Finance and Real Estate</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>European Central Bank, Frankfurt am Main, Germany</t>
+          <t>Bloomington, IN</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$95 (USD)</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Money markets and monetary policy implementation, technological innovation in money markets (e.g., stable coins, CBDCs), functioning of money markets, role of non-bank financial institutions, funding strategies, central clearing effects, macroeconomic implications of volatile short-term rates</t>
+          <t>Empirical and theoretical papers in all finance and real estate areas</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Finance in the Digital Age (FiDA) Workshop</t>
+          <t>12th P2P Financial Systems International Workshop (P2PFISY 2026)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Calgary, Canada</t>
+          <t>Astana, Kazakhstan</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4519,14 +4519,14 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>AI, DeFi, robo-advisors, neurofinance</t>
+          <t>Regulation &amp; Compliance in Digital Asset Markets, Fraud, Financial Crime &amp; Forensics in Crypto Markets, CBDCs and Digital Public Infrastructure, Stablecoins and Digital Payment Systems, Artificial Intelligence in Financial Systems, Consumer Protection, Data Governance, and Trust in Digital Finance, Tokenisation of Real-World Assets (RWA)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>7th LTI@UniTO/Bank of Italy Workshop on Long-term investors’ trends: theory and practice</t>
+          <t>2026 Annual Community Bank Research Conference</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4536,17 +4536,17 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bank of Italy, Rome, Italy</t>
+          <t>Federal Reserve Bank of St. Louis, St. Louis, MO</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4556,145 +4556,145 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Long-term investors’ strategies and behavior in times of geopolitical fragmentation, rising protectionism and technological breakthroughs; Long-term investors’ role in the financing of the real economy and in fostering growth; Shifting equilibria in government bond markets driven by quantitative tightening, rising indebtedness and macroeconomic uncertainty; The evolution of sustainable investment strategies and green lash risks; Challenges for long-term investors stemming from increasing equity market concentration; The rising importance of non-bank investors in credit intermediation and its consequences for the transmission of monetary policy; The rise of cryptocurrencies, emerging financial technologies (fintech) and their impact on investment strategies; Emerging trends in asset allocation and risk management for long-term investors, including insurance companies, pension funds, and mutual funds; Shock transmission mechanisms from the real economy to financial institutions and the amplification of shocks through credit chains, fire sales, and other procyclical processes; The use of big data and artificial intelligence to assess in the investment processes and in the management of the exposure to risk factors; Innovations in financial markets and opportunities for financial institutions; Geopolitical risks and their effect on banks vs. non-bank intermediaries; The effects of the demographic transitions on financial markets and the role of long-term investors in tackling them.</t>
+          <t>Community banking, financial services to households and small businesses, impact of community banks on local/state economic activity, community banks’ response to economic shocks, effects of regulatory policy, challenges and opportunities for community banks, advantages and disadvantages of the community bank business model</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>7th Annual RCF-ECGI Corporate Finance and Governance Conference</t>
+          <t>Stigler Center-CEPR Political Economy of Finance Conference 2026: Crony Capitalism in 21st Century America</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Madrid, Spain, and virtually</t>
+          <t>Gleacher Center - Chicago</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>€350 in person / €50 online</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>capital structure, corporate and securities law, corporate culture, corporate failure, corporate finance and public policy, corporate governance, corporate restructuring, corporate social responsibility, crowdfunding, dividends, payout policy, repurchases, entrepreneurial finance, family business, financial contracting, financial intermediation, financial literacy, fintech, fraud, innovation, IPOs and SEOs, mergers and acquisitions, misconduct, private debt, private equity, trade credit, socially responsible investments, sustainable finance, real options, venture capital</t>
+          <t>Crony capitalism in 21st century America, political economy, intersections of finance, economics, political science, and law</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Fintech and Financial Institutions Research Conference</t>
+          <t>15th Fixed Income and Financial Institutions (FIFI) Conference</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Philadelphia, Philadelphia, PA</t>
+          <t>University of South Carolina in Columbia, SC</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>75 USD</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Economic consequences and impacts of the fintech sector, regulatory implications of the fintech sector</t>
+          <t>fixed income, commercial and investment banks, asset management and mutual fund companies, short sellers, hedge funds, broker-dealers, insurance companies</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Aarhus Finance Forum 2026</t>
+          <t>Higher Education Finance Research Conference</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Aarhus, Denmark</t>
+          <t>Federal Reserve Bank of Philadelphia</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>375 DKK</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Financial Decisions under Uncertainty and Ambiguity, Household Finance, Real Estate Finance, Corporate Finance, Climate Finance, Digital Finance, Asset Pricing</t>
+          <t>financial aid, student debt, higher education finance, household balance sheets, labor market outcomes, consumption, wealth accumulation</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>15th CDI Conference on Derivatives</t>
+          <t>2026 Wharton–Chicago–Harvard Insolvency and Restructuring Conference (WCHIRC)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Montreal, Canada</t>
+          <t>University of Pennsylvania, Philadelphia, PA</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4704,145 +4704,145 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Corporate financial distress and bankruptcy, Liability management and out-of-court restructurings, Chapter 11 and formal reorganization processes, Consumer bankruptcy, Leveraged lending and private credit, Creditor governance and capital structure dynamics, Distressed debt markets and asset pricing, Financial contracting and covenant design, Bankruptcy law, courts, and institutional design, Operational restructuring and firm performance</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Conference on CSR, the Economy and Financial Markets</t>
+          <t>Financial Decision-Making Conference 2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Düsseldorf, Germany</t>
+          <t>Bozeman, MT</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>€ 150 for regular participants and € 100 for PhD students</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Climate risk and pricing, Role of financial markets, banks, institutional investors in CSR, Effects of CSR on valuation, performance, cost of capital, funding and capital structure, Socio-economic aspects and their implications for companies and financial markets, Corporate governance and CSR, Risk management and CSR, CSR reporting and disclosure, ESG backlash and politicization, Sustainability strategy under new constraints, Measurement: information content and reliability of ESG indices, CSR activities and the economy</t>
+          <t>household finance, financial literacy and education, consumer financial behavior, retirement and savings decisions, financial education interventions, fintech and digital finance, financial advice and delegation, debt and credit decisions, insurance decisions, behavioral finance, financial inclusion</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026 Vietnam Symposium on Global Economy (VSGE2026)</t>
+          <t>Finance and Real Estate Conference 2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City, Vietnam</t>
+          <t>Miami University, Oxford, OH</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$50 USD</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Geopolitical, macroeconomic policy and development; Trade, foreign direct investment, and global value chain; Climate change, green transition, and public finance; Finance, stability, and sustainable investment; Digitalization, labor markets, and social protection; Urbanization, regional development and resilience; AI, growth, economic impacts, and government policies; Global governance, institutions, and international cooperation.</t>
+          <t>Asset pricing and valuation, Corporate finance, Real estate markets and investment, Risk management and financial regulation, Urban economics and housing policy, Sustainable and green finance, Behavioral finance</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>India Finance Conference (IFC) 2026</t>
+          <t>UGA Fall Finance Conference 2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Indian Institute of Management Bangalore</t>
+          <t>Athens, GA</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>70 USD</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Theoretical and empirical asset pricing, Corporate finance, capital structure and dividend policy, Asset allocation and investment management, Financial crises, systemic risk and macro-finance, Quality of financial reporting and adoption of IFRS, Corporate governance, executive compensation and ownership structure, Computational finance and financial econometrics, Financial risk analytics and management, Market microstructure and algorithmic trading, Financial policy choice, institutions and regulation, Financial Analytics, ESG, Climate Finance, Blended Finance, Insurance / Reinsurance / Pension Funds, Enhancing liquidity in commodity derivatives markets, Financial Literacy and Financial Education</t>
+          <t>All areas of finance</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Edinburgh Financial Technology Conference</t>
+          <t>Inquire Europe Autumn Conference: “Expectations and Asset Prices”</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Prague, Czech Republic</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4852,34 +4852,34 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>The application of AI and Machine Learning in finance, The application of distributed ledger technologies in finance, Cryptofinance, Cyber risk in finance, The microstructure of modern financial markets: algorithmic/high frequency trading, dark trading, blockchain settlements etc., Behavioural economics in financial technology, Alternative data (structured and unstructured datasets), Crowdsourcing and investment strategy, New exchange traded financial derivatives, Financial stability risks from the development of FinTech, RegTech, Open banking</t>
+          <t>Expectations and Asset Prices, deviations from rational expectations and their implications, optimism and pessimism in asset valuations and market dynamics, investment strategies and anomalies, factor investing, strategic and tactical asset allocation, portfolio choice under model and parameter uncertainty, short selling</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>5th Conference in Sustainable Finance</t>
+          <t>The WFE’s Sustainability Conference 2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>University of Luxembourg</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4889,71 +4889,71 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Any topic in sustainable finance</t>
+          <t>Transition finance and market design, Regulatory fragmentation and divergence, Sustainability reporting, Nature and biodiversity in capital markets, Just transition, social and gender finance, Proportionality for SMEs and emerging markets, Carbon market architecture</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>7th CEAR-RSI Household Finance Workshop</t>
+          <t>2026 FMA Annual Meeting</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>HEC Montréal</t>
+          <t>Tampa, FL</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$75 (current FMA members); $85 (non-members)</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Consumption-saving decisions and investment choices, Financial literacy and education, Pensions and retirement, Financial planning and advice, Financial delinquency and bankruptcy, Household insurance and risk management</t>
+          <t>Financial decision-making, financial management and related topics</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Next-Gen AI and Autonomous Finance (NGAI) workshop</t>
+          <t>3rd AI in Finance Conference</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Rennes School of Business, Rennes, France</t>
+          <t>Montréal, QC, Canada</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4963,34 +4963,34 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Autonomous agents &amp; decision-making in finance, AI-driven trading, portfolio optimization &amp; market microstructure, Risk, robustness, and model governance, Ethics, fairness, transparency &amp; societal impacts of financial AI, Financial decision making and AI, Bias and stereotyping in relation to AI driven finance, AI, money and financial value formation.</t>
+          <t>Machine learning and artificial intelligence in asset pricing and financial econometrics, Portfolio management, trading strategies, and risk management using AI, Large language models (LLMs), NLP, and textual analysis in finance, Corporate finance applications including M&amp;A and investment decisions, Banking, credit markets, and financial intermediation, Cryptocurrency, digital assets, and decentralized finance, ESG, sustainability, and climate finance, Financial regulation, policy analysis, and central bank communication, Real estate finance and urban economics, Alternative data and high-dimensional financial datasets, Investor behavior, sentiment, and attention, Macroeconomic and financial risk forecasting</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>12th Annual ICGS Conference</t>
+          <t>2026 Summer Research Conference</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>HEC Montréal, Quebec, Canada</t>
+          <t>Indian School of Business, Hyderabad Campus</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5000,71 +5000,71 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Behavioral perspectives on governance, institutional and political approaches, implications of AI adoption, evolving forms of activism, reconfiguration of governance under geopolitical crises, governance mechanisms for managing state-firm relations</t>
+          <t>Recent Advances in Finance, corporate finance and its interface with asset pricing, behavioral finance, financial intermediation, household finance, market microstructure</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Vienna Festival of Finance Theory 2026</t>
+          <t>International Risk Management Conference 2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Vienna, Austria</t>
+          <t>Warsaw, Poland</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>65 EUR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Corporate finance theory, financial intermediation theory</t>
+          <t>Asset pricing; Banking; Financial econometrics; Capital markets; Financial intermediation; Corporate finance; Financial crises; Corporate governance; Market microstructure; Financial regulation; International corporate finance; Risk management; Emerging market; Corporate investment decision; Global risk markets; Macro-financial linkages; Financial policy securitization; Behavioural finance; Financial integration; Mathematical &amp; computational finance; Stochastic optimization approaches in finance; Mergers &amp; acquisitions; Modelling, money and liquidity; Sustainable finance; Climate change risk; AI innovation; crypto and related assets and technology.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>The 11th (2026) Cross Country Perspectives in Finance (CCPF) Conference</t>
+          <t>The Second USTC Frontiers in Finance Conference</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Nanjing, China (online and on-site)</t>
+          <t>International Finance Institute, University of Science and Technology of China, No. 1789 Guangxi Road, Binhu New District, Hefei City, Anhui Province, P.R.China</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -5074,71 +5074,71 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>cross-country factors, credit, banking, asset pricing, market liquidity, corporate finance, corporate governance, entrepreneurial finance</t>
+          <t>All topics of finance</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>6th Annual Bristol Financial Markets Conference</t>
+          <t>Fischer-Shain Research Conference 2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bristol, UK</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>50 USD</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Skill, performance, and evaluation in delegated portfolio management; The rise of passive investment and its effects on financial markets; New developments and trends in delegation: ESG / thematic/private markets; Machine learning and AI in asset management; Textual analysis and news coverage in delegated investment decisions; The role of index providers in delegated portfolio management</t>
+          <t>financial intermediation, banking, financial services</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Inaugural CEIBS-APS Centre for Financial Markets (CAC) Academic Conference</t>
+          <t>ECB Money Market Conference 2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>China Europe International Business School (CEIBS), Shanghai, China</t>
+          <t>European Central Bank, Frankfurt am Main, Germany</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -5148,34 +5148,34 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>asset pricing, macro-finance, impact of institutional features on capital market dynamics</t>
+          <t>Money markets and monetary policy implementation, technological innovation in money markets, functioning of money markets</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Dauphine Finance PhD Workshop</t>
+          <t>Finance in the Digital Age (FiDA) Workshop</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Paris, France</t>
+          <t>Calgary, Canada</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -5185,34 +5185,34 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Papers in all areas of Finance and Financial Economics</t>
+          <t>AI, DeFi, robo-advisors, neurofinance</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>14th Helsinki Finance Summit on Investor Behavior</t>
+          <t>7th LTI@UniTO/Bank of Italy Workshop on Long-term investors’ trends: theory and practice</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Helsinki/Espoo, Finland</t>
+          <t>Bank of Italy, Rome, Italy</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -5222,219 +5222,219 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Investor behavior, behavior of different investor types, market microstructure, behavioral biases, household consumption, investor education, finance professionals, biological and psychological foundations of investor behavior, influence of analysts and media, social influence and networks, impact of investor behavior on corporate policies</t>
+          <t>Long-term investors’ strategies and behavior, Long-term investors’ role in financing the economy, Shifting equilibria in government bond markets, Evolution of sustainable investment strategies, Challenges for long-term investors, Importance of non-bank investors, Rising of cryptocurrencies and fintech, Emerging trends in asset allocation and risk management, Shock transmission mechanisms, Use of big data and AI in investment processes, Innovations in financial markets, Geopolitical risks effects, Effects of demographic transitions on financial markets</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026 Clemson Finance Research Conference</t>
+          <t>7th Annual RCF-ECGI Corporate Finance and Governance Conference</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Clemson, SC</t>
+          <t>Madrid, Spain, and virtually</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>75 USD</t>
+          <t>€350 in person, €50 online option</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>corporate finance, asset pricing, investment, banking, asset management, household finance, labor economics, behavioral finance, Fintech, real estate</t>
+          <t>capital structure, corporate and securities law, corporate culture, corporate failure, corporate finance and public policy, corporate governance, corporate restructuring, corporate social responsibility, crowdfunding, dividends, payout policy, and repurchases, entrepreneurial finance, family business, financial contracting, financial intermediation, financial literacy, fintech, fraud, innovation, IPOs and SEOs, mergers and acquisitions, misconduct, private debt, private equity, trade credit, socially responsible investments, sustainable finance, real options, and venture capital</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Politics in Finance 2026 Conference</t>
+          <t>Fintech and Financial Institutions Research Conference</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>McDonough School of Business, Rafik B. Hariri Building 37th and O Streets, N.W Washington, D.C. 20057 USA</t>
+          <t>Federal Reserve Bank of Philadelphia, Philadelphia, PA</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>$75 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>The role of political connections and political ideologies in shaping capital market forces, How political ideologies affect the decision making by firms and workers, Political connections and corruption in developing economies, The political economy of financial development, The interaction between government and financial institutions, Implications of political uncertainty and political connections for asset prices and corporate policies, Political economy of financial regulation and financial crises</t>
+          <t>Interlinkages of the fintech sector and the broader financial system, economic consequences of fintech, regulatory implications of fintech</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>11th SDU Finance Workshop on Corporate Finance -- Dynamics, Uncertainty, and Strategic Decisions</t>
+          <t>Aarhus Finance Forum 2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>University of Southern Denmark (SDU), Odense, Denmark</t>
+          <t>Aarhus, Denmark</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>300 DKK (approx. 40 EUR)</t>
+          <t>375 DKK (approx. 50 Euros)</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Corporate Finance, Dynamics, Uncertainty, Strategic Decisions</t>
+          <t>Financial Decisions under Uncertainty and Ambiguity, Household Finance, Real Estate Finance, Corporate Finance, Climate Finance, Digital Finance, Asset Pricing</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Northern Finance Association 2026 Annual Meeting</t>
+          <t>15th CDI Conference on Derivatives</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Quebec City, Canada</t>
+          <t>Montreal, Canada</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>CAD 75</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Papers on any topic related to finance, including asset pricing, corporate finance, financial intermediation, investments, Canadian financial markets, insurance, household finance, sustainable finance, fintech, and AI.</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>London Business School 2026 Summer Finance Symposium</t>
+          <t>Conference on CSR, the Economy and Financial Markets</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>London Business School</t>
+          <t>Düsseldorf, Germany</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>£50</t>
+          <t>€150 for regular participants, €100 for PhD students</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Papers from all areas of finance</t>
+          <t>Climate risk and pricing, Role of financial markets, banks, institutional investors in CSR, Effects of CSR on valuation, performance, cost of capital, funding and capital structure, Socio-economic aspects and their implications for companies and financial markets, Corporate governance and CSR, Risk management and CSR, CSR reporting and disclosure, ESG backlash and politicization, Sustainability strategy under new constraints, Measurement: information content and reliability of ESG indices, CSR activities and the economy</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Sustainability, Technology, and the Transformation of Accounting and Finance (STTAF26)</t>
+          <t>2026 Vietnam Symposium on Global Economy (VSGE2026)</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Bahrain</t>
+          <t>Ho Chi Minh City, Vietnam</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5444,599 +5444,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Climate Finance, Artificial Intelligence (AI) and Machine Learning in Finance and Accounting, Green Finance, Sustainable Finance, ESG Reporting, and Climate Risk, FinTech, Blockchain, and Digital Currencies, Corporate Governance and Technological Innovation, Big Data in Accounting and Finance, Green Accounting and Carbon Disclosure, RegTech and Financial Compliance, Data Analytics and Financial Decision-Making, Digital Transformation in Public Sector Accounting, Ethical Implications of AI and Automation in Financial Services, Evolving Accounting Standards in Response to Sustainability/Technology</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>11th International Conference on Accounting and Finance (ICOAF-2026)</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Danang, Vietnam</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>Accounting, Finance, and Banking, encompassing both theoretical and empirical studies</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Liechtenstein Workshop on AI in Finance 2026</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Vaduz, Liechtenstein</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>forecasting financial variables with AI, asset allocation and asset management with AI, AI-based factor models, natural language processing and large language models in finance, AI applications in corporate finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>3rd Modern Finance Conference (MFC 2026)</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Krakow, Poland</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>Asset pricing and valuation, Banking and financial services, Behavioral finance and decision making, Capital structure, Corporate finance, Corporate governance, Cryptocurrencies, Derivatives, Economic development, Exchange rates and currency markets, Finance and accounting standards, Financial econometrics and quantitative methods, Financial markets and instruments, Financial, management, and tax accounting, Financial regulation and supervision, Financial stability, Fintech and financial innovation, Green finance, Investment and portfolio management, Insurance, Market microstructure, Mergers and acquisitions, Microfinance, Monetary policy and central banking, Risk management, Sustainable finance and responsible investment</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>First University of Maryland/Singapore Management University/UBS Quant Investment Forum: AI and Finance</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>95 SGD</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>AI for Investments &amp; Asset Pricing, Alternative Data and Investment Insights, Portfolio &amp; Risk Management, Algorithmic Trading &amp; Market Impact</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>2026 City University of Hong Kong International Finance Conference</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>City University of Hong Kong</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>Corporate Finance, Asset Pricing</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>2026 Research Summer Workshop on Regulated Funds and Retail-oriented Investment Products</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Washington, DC, USA</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>50 USD</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>Regulated funds, retail-oriented investment products, mutual fund industry</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>2026 Vietnam Symposium in Entrepreneurship, Finance, and Innovation</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Hanoi, Vietnam</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>AI, Big Data, and Machine Learning Applications in Finance; Asset Pricing; Bankruptcy and Liquidation; Biodiversity Finance; Climate Finance; Corporate Finance and Governance; Corporate Responsibility and Sustainability; Crypto Assets, Blockchain, and Decentralized Finance; Electronic Markets, Trading Platforms, and Market Microstructure; ESG and Sustainable Finance; Financial Markets; Household Finance; Information Disclosure, Market Efficiency, and Transparency; Portfolio and Investment Decisions; FinTech, Alternative Finance, and Digital Financial Infrastructure; Tokenomics, Digital Currencies, and Payment Systems; Business Model Innovation and Corporate Digital Transformation; Digital Innovation, Knowledge Management, and Innovation Systems; Digital Human Resources and the Future of Work; Innovation Management and Growth Strategies; Innovation and Industrial Policy; Institutions, Regulation, and Innovation Systems; Science, R&amp;D, and the Economics of Knowledge Creation; Sustainability in the Digital Economy; Crowdfunding, Peer-to-Peer Lending, and Platform-Based Finance; Entrepreneurship, Intrapreneurship, and Innovation; Entrepreneurship in Emerging and Transition Markets; Family-Owned Businesses and Governance; Governance and Financing of High-Tech Firms; New Venture Creation and Performance; Social and Sustainable Entrepreneurship; Startups, SMEs, and Resource Allocation; Venture Financing and Entrepreneurial Growth</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>12th IWH-FIN-FIRE Workshop on “Challenges to Financial Stability”</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Halle Institute for Economic Research (IWH), Halle/Saale Germany</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>regulation and financial intermediation, corporate finance, law, politics and finance, monetary policy, inflation and financial resilience, macroprudential policy and real estate, financial networks and systemic risk, pricing of climate risk in financial markets, ecological hazards and the behaviour of firms and households, governance of financial firms and markets, private credit and risk transfer</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Bridging Theory and Empirical Research in Finance</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Boston College</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>$50</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>corporate finance, corporate governance, financial intermediation, agency and delegation, information and securities, financial markets</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>11th Bank of Finland and European Systemic Risk Board Joint Conference on AI and Systemic Risk Analytics</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Bank of Finland, Helsinki</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>Use of Large Language Models (LLM) and trustworthy AI; AI and changing interdependencies in the financial markets; Cyber security and operational risks as sources of systemic risk; AI and Quantum Computing as potential source of new systemic risks; Use of AI with big data for systemic risk analytics; Risks and opportunities stemming from disruptive innovations in financial technology (FinTech); Analysing emerging risks from interconnectedness of the financial system; Identifying risks from market-based finance; Modelling geopolitical risks; Using systemic risk analytics to support macro-prudential policy and regulation; Evidence of macroprudential policy measures</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Bank of Finland and CEPR Joint conference on Navigating Monetary Policy by the Northern Lights</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>2026-12-17</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>2026-12-18</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Saariselkä, Lapland</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>Monetary Policy Transmission, Inflation Dynamics and Expectations; Heterogeneity in Macro and Monetary Economics Models; Monetary-Fiscal Interactions; Technological Advances, Financial Market Developments, and Central Banks; Geopolitical Shocks and Monetary Policy; Central bank credibility and independence</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>2026 FIRN/UQ Asset Management Meeting</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Brisbane, Australia</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>asset management, FinTech, mutual funds, hedge funds, pension funds, ETFs, alternative investments, data assets/markets, digital finance, platform finance, financial technology, artificial intelligence, big data in asset management</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>World Finance &amp; Banking Symposium</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>2026-12-14</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>2026-12-16</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>University of Latvia, Riga</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>All areas of finance, economics, and banking</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>Geopolitical, macroeconomic policy, and development; Trade, foreign direct investment, and global value chain; Climate change, green transition, and public finance; Finance, stability, and sustainable investment; Digitalization, labor markets, and social protection; Urbanization, regional development and resilience; AI, growth, economic impacts, and government policies; Global governance, institutions, and international cooperation</t>
         </is>
       </c>
     </row>

--- a/public/conference_list.xlsx
+++ b/public/conference_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G136"/>
+  <dimension ref="A1:G129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,249 +456,249 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>UWFC 2027</t>
+          <t>Eighth Edinburgh Corporate Finance Conference</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2027-02-04</t>
+          <t>2027-06-07</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2027-02-07</t>
+          <t>2027-06-08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>The Cliff Lodge at Snowbird, Utah</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>$105 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>financial economics</t>
+          <t>Corporate finance, both theoretical and empirical</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>European Winter Finance Summit</t>
+          <t>1st Arctic Finance Conference</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2027-03-14</t>
+          <t>2027-06-24</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2027-03-17</t>
+          <t>2027-06-27</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hotel Arlberghaus, Zürs, Austria</t>
+          <t>Svolvær, Lofoten, Norway</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>EUR 50</t>
+          <t>CHF 60</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Contributions from all areas of finance</t>
+          <t>Empirical and theoretical contributions from all areas of finance</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sustainability, Trade and Digital Finance (STDF)</t>
+          <t>ASU Sonoran Winter Finance Conference 2027</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2027-02-10</t>
+          <t>2027-02-04</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2027-02-11</t>
+          <t>2027-02-06</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Department of Banking &amp; Finance, University of Jos, Nigeria</t>
+          <t>Andaz Scottsdale Resort and Bungalows, Scottsdale, Arizona</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>USD 100</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Artificial Intelligence in Finance, Stock Market Trading &amp; Investment, FinTech &amp; Digital Finance, Quantitative Finance &amp; Financial Econometrics, AI, ESG &amp; Sustainable Investment, Emerging Markets</t>
+          <t>All areas of finance, both theoretical and empirical contributions</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>16th Workshop on Exchange Rates</t>
+          <t>14th Annual Conference on Financial Market Regulation (CFMR 2027)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2027-05-06</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2027-05-07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>SEC Headquarters, 100 F St NE, Washington, DC 20002</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>50 USD</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Drivers of exchange rates and related asset prices, exchange rates and the transmission of monetary policy, FX interventions and supply side shocks, exchange rates and macrofinancial stability frameworks, FX risk premia and their drivers, global linkages between capital flows, foreign exchange rates and risk appetite, international use of currencies and implications for exchange rates, implications of digital and tokenised assets for FX markets</t>
+          <t>Asset management, corporate finance, financial intermediation, market microstructure and trading</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026 NBS Conference on AI for Finance</t>
+          <t>Finance Down Under: Building on the Best from the Cellars of Finance</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2027-02-25</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2027-02-27</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Nanyang Technological University (Singapore)</t>
+          <t>Melbourne, Australia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>US$100</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Generative AI, Foundation Models, and Financial Decision-Making; AI-Driven Asset Pricing, Portfolio Management, and Investment Strategies; Machine Learning for Financial Forecasting and Market Prediction; Alternative Data, Natural Language Processing, and Financial Analytics; AI in Banking, Credit Risk Assessment, and Financial Intermediation; AI, FinTech Innovation, and the Future of Financial Services; Human-AI Collaboration in Financial Markets and Corporate Finance; AI for Climate Finance, ESG Analysis, and Sustainable Investing; AI Governance, Regulation, Ethics, and Responsible Innovation in Finance</t>
+          <t>asset pricing, corporate finance, data and AI in finance, economic measurement, financial valuations</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Risk Theory Society Meeting 2027</t>
+          <t>ASU Cactus Conference</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2027-05-28</t>
+          <t>2027-03-11</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2027-05-30</t>
+          <t>2027-03-13</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Munich, Germany</t>
+          <t>Tempe, Arizona</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>100 USD</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Insurance economics, financial economics related to insurance markets, actuarial science, economic analysis of risk and uncertainty</t>
+          <t>All areas of accounting and all research methods</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IIM Calcutta-NYU Stern India Research Conference</t>
+          <t>World Finance Conference 2027</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2027-03-01</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2027-07-28</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2027-07-31</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>WEBINAR</t>
+          <t>Athens University of Economics and Business, Athens, Greece</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -708,293 +708,293 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>finance, economics, accounting, challenges and implications of major policy initiatives in India, Indian financial markets, effect of AI on the economies of India, China, and the US</t>
+          <t>FinTech, economics, banking</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UNC Duke Corporate Finance Conference</t>
+          <t>European Financial Management Merton H. Miller Doctoral Student Seminar</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2027-04-02</t>
+          <t>2027-06-23</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2027-04-03</t>
+          <t>2027-06-26</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Chapel Hill</t>
+          <t>The University of Leeds, Leeds, UK</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>100 USD</t>
+          <t>500.00 USD</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Papers in all areas of corporate finance</t>
+          <t>corporate finance, asset pricing, market microstructure, international finance, financial institutions and intermediation, academic publishing, career development</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3rd LSU Finance Mardi Gras Conference</t>
+          <t>European Financial Management Association 2027 Annual Meeting</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2027-02-05</t>
+          <t>2027-06-23</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2027-02-06</t>
+          <t>2027-06-26</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA</t>
+          <t>The University of Leeds, Leeds, UK</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>75 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>All topics in finance</t>
+          <t>All areas of Finance</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Financial Research Association 2026 Annual Conference</t>
+          <t>Spring Finance Workshop</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2027-04-11</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2027-04-13</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, USA</t>
+          <t>Ischgl, Austria</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>72 EUR</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>New finance papers of general interest to the profession, early work, research by junior scholars</t>
+          <t>All fields of finance</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Winter Finance Summit in Asia 2027</t>
+          <t>2027 Currency Conference</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2027-03-01</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2027-03-01</t>
+          <t>2027-05-24</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2027-03-04</t>
+          <t>2027-05-26</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Iwate, Japan</t>
+          <t>Berlin, Germany</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JPY8,000</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>All areas of finance and real estate finance, particularly early-stage research not previously presented at major conferences</t>
+          <t>Cash Resilience, The Future of Central Bank Money, Access / Right to Cash, Currency Design, Cash Infrastructure: Who Shoulders the Burden?, AI in the Cash Cycle, Geopolitics / Reserve Currencies, Demand Forecasting</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Stern/Salomon Microstructure Conference</t>
+          <t>ASU Sonoran Winter Real Estate Conference 2027</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2027-02-04</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2027-02-04</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stern School, New York University</t>
+          <t>Andaz Scottsdale Resort and Bungalows, Scottsdale, Arizona</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>95 USD</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>The economics of securities markets, theoretical, empirical, and experimental analyses of the role of information in the price-discovery process, definition, measurement, and determinants of liquidity, costs and benefits of alternate trading mechanisms and market structures, measurement and control of transactions costs, role of regulation and the evolution of market design, domestic and international comparisons of trading costs, cross-border listing and trading securities, trading technology and information systems, practical implications of market design for risk management, financial engineering</t>
+          <t>Real estate research, finance, economics, urban research, environmental research, public policy, credit and risk, affordability and access, sustainability in residential and commercial markets</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3rd Annual Boca Finance and Real Estate Conference</t>
+          <t>SoFiE sponsored joint Financial Econometrics Conference</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2027-04-21</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2027-04-23</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Florida Atlantic University, Boca Raton, Florida, USA</t>
+          <t>Lancaster University, England</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>$50 USD</t>
+          <t>30 GBP</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Finance and real estate</t>
+          <t>High-frequency econometrics, Market microstructure, Forecasting, Asset Pricing and investments, Risk neutral density estimation, Fintech &amp; blockchain, Cryptocurrencies, Climate econometrics, Volatility modelling, Artificial intelligence &amp; machine learning, Factor models, Term structure models, Risk modelling, Real time detection of extreme market events, Options &amp; derivatives modelling, Multivariate &amp; high dimensional time series modelling</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1st Arctic Finance Conference</t>
+          <t>Central Bank Payments Conference (CBPC)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2027-01-11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2027-06-24</t>
+          <t>2027-03-15</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2027-06-27</t>
+          <t>2027-03-17</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Svolvær, Lofoten, Norway</t>
+          <t>Bangkok, Thailand</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CHF 60</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Empirical and theoretical contributions from all areas of finance</t>
+          <t>Cross-Border Payments, Digital Money: CBDCs, Stablecoins, and Tokenization, Payments Fraud and Scams, Agentic AI and Payments, Cyber Resilience and Quantum Preparedness, Payments Sovereignty, Payment System Interoperability</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>22nd International Behavioural Finance Conference (IBFC)</t>
+          <t>2026 Wellington Finance Summit</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>University of Chicago, Booth School of Business, Gleacher Center</t>
+          <t>Wellington, New Zealand</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1004,34 +1004,34 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Behavioural Asset Pricing, Behavioural Corporate Finance, Biases and Heuristics, Cryptocurrencies, Financial Analysts, Personal Financial Behavior, Financial Markets, Investment Decisions, Mergers and Acquisitions, Political Environment, Retail Investors, Sentiment, Climate Finance, CSR and ESG</t>
+          <t>All fields of finance</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026 Sydney Banking and Financial Stability Conference</t>
+          <t>University of Kentucky Finance Conference</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2027-04-22</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2027-04-24</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>The University of Sydney Business School, Sydney, Australia</t>
+          <t>Lexington, Kentucky, USA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1041,34 +1041,34 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Banking, financial stability, financial intermediation, financial institutions and markets, fintech, cryptocurrency, central bank digital currency, corporate finance, asset pricing, investment and funds management, macro finance</t>
+          <t>All areas of finance</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026 VINS Annual Conference</t>
+          <t>3rd Lapland Finance Summit</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2027-04-05</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2027-04-06</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>NYU Shanghai, Shanghai, China</t>
+          <t>Levi, Kittilä, Finland</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1078,182 +1078,182 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Applications in Asset Management &amp; Trading, Market Microstructure &amp; Liquidity, Emerging Financial &amp; Operational Risks, Governance &amp; Regulation</t>
+          <t>Household finance, investment funds, stock market participation, portfolio and security choice, personality and household finance, debt behavior, retirement savings, financial literacy, financial advice, climate change and finance, machine learning in finance, fund performance measurement, ESG in finance, macroeconomic issues, innovations in fund design</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Finance Down Under: Building on the Best from the Cellars of Finance</t>
+          <t>Columbia/BPI Bank Regulation Research Conference</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2027-02-25</t>
+          <t>2027-02-18</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2027-02-27</t>
+          <t>2027-02-18</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Melbourne, Australia</t>
+          <t>Columbia University, New York City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>US$100</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>asset pricing, corporate finance, data and AI in finance, and all other areas of finance</t>
+          <t>Bank capital and liquidity regulation, Payments and digital asset innovations, Bank regulation and central bank balance sheets, Bank resilience to financial or operational risks, Household finance, Bank Merger policy</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FMA Annual Meeting</t>
+          <t>16th ITAM Finance Conference</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2027-02-20</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tampa, FL</t>
+          <t>ITAM Santa Teresa Campus, Mexico City, Mexico</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$1,250 MXN (approximately $74 USD)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Corporate Finance, Asset Pricing / Investments, Fintech and AI, Financial Institutions, Household Finance, Sustainable Finance</t>
+          <t>Empirical or theoretical papers from all areas of finance and financial economics</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>34th Annual PBFEAM and 20th NYCU International conferences</t>
+          <t>11th Northeastern Finance Conference</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2027-05-05</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2027-05-07</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>National Yang Ming Chiao Tung University, Hsinchu, Taiwan</t>
+          <t>Boston, Massachusetts, United States</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>USD $250 for On-line Presenter &amp; USD $300 for On-site Presenter</t>
+          <t>90 USD</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>All areas of finance, theoretical and empirical</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>11th Annual Young Scholars Finance Consortium</t>
+          <t>2027 Baruch-JFQA Climate Finance and Sustainability Conference</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2027-03-04</t>
+          <t>2027-03-11</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2027-03-06</t>
+          <t>2027-03-12</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>The George Hotel, College Station, Texas</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>100 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>corporate finance and governance, financial markets and intermediation, household finance</t>
+          <t>Climate finance and sustainability, AI/data-center electricity demand, physical-risk insurance gaps</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5th Frankfurt/Mannheim Workshop on Digital Finance</t>
+          <t>Sustainable Finance Research Forum Paris 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Frankfurt am Main, Germany</t>
+          <t>Paris, France</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1263,71 +1263,71 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>digital assets, decentralized finance (DeFi), FinTech, AI</t>
+          <t>Sustainable finance, applied research from corporate, financial intermediary, and investor perspectives</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CBER-Tokenomics 2026</t>
+          <t>Friends of Women in Finance 5th Symposium in Greater New York (FWFS-GNY)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>New York City, USA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>FREE</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>token and protocol design, decentralized finance, stablecoins and digital payments, DAOs and decentralized governance, tokenized real-world assets, prediction markets, AI agents and decentralized AI, economic world models, applications of large language models to macroeconomic, financial, and economy-wide modelling</t>
+          <t>AI and digital finance, behavioral and social finance, corporate finance and governance, climate and sustainable finance, investment and asset pricing, financial markets and institutions, and other finance-related research</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>21st Annual Conference on Asia-Pacific Financial Markets (CAFM)</t>
+          <t>Emerging Markets Group - European Bank of Reconstruction and Development workshop on “The Drivers of growth in the 21st century”</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2027-02-07</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2027-06-09</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2027-06-10</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CONRAD Seoul</t>
+          <t>Bayes Business School, City St. George's, University of London - London</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1337,34 +1337,34 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>All areas of finance</t>
+          <t>Impact of globalization in the era of rising geopolitical tensions, Advances in artificial intelligence, Impact of financial development, Demographic trends, The growing role of China in the global financial system, Changes in economies’ comparative advantages, Public health, institutions, climate change, inequality</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026 Vietnam Symposium in Climate Transition (VSCT-2026)</t>
+          <t>WFEClear 2027</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2027-01-06</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2027-04-27</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2027-04-29</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>The University of Danang - University of Economics, Danang, Vietnam</t>
+          <t>Almaty, Kazakhstan</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1374,145 +1374,145 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Behavioral finance/economics and its implications for climate transition, Blue economy, Carbon market, Circular economy, Climate change: mitigation and adaptation, Climate change: policy and regulations, Climate finance, Climate risks: assessment and management, Climate transition and COVID-19 recovery, Climate transition and portfolio management, Corporate Social Responsibility (CSR), Energy and environmental issues, Energy markets and energy transition, Environmental, Social and Governance (ESG), Financial markets and climate transition, Geopolitical risk and climate change mitigation, Just climate transition, Low-carbon technologies and innovation, Artificial intelligence and climate transition, Management of extractive industries, Responsible behaviors and sustainability in family business, Responsible business conduct and SDG goals, Role of management, business strategies, and SDG goals, Sustainable business model innovation, Sustainable entrepreneurship, Sustainable infrastructure investment, Sustainable production and consumption, Sustainable key performance indicators</t>
+          <t>Clearing in emerging and developing markets, CCP design, governance and risk management, Margin, collateral and liquidity, Clearing, systemic risk and resilience, Regulation, incentives and the economics of clearing, Innovation, technology and the future of clearing, New products, markets and clearing arrangements</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026 Conference on Auditing and Capital Markets</t>
+          <t>2027 Loyola Wealth Management Conference</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2027-03-12</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2027-03-12</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Washington, DC</t>
+          <t>Loyola University Maryland | Baltimore, MD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Economic impact of auditing, audit regulation, audit oversight on capital markets</t>
+          <t>Mutual funds, ETFs, and index investing; Fixed income securities and credit markets; Real estate investment trusts (REITs) and alternative assets; Private equity, venture capital, and hedge funds; Digital assets, cryptocurrencies, and fintech; Retirement planning, household finance, and target-date strategies; Asset allocation and portfolio management</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3rd American Conference of the Academy of Sustainable Finance, Accounting, Accountability &amp; Governance (ASFAAG) 2027</t>
+          <t>16th Workshop on Exchange Rates</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2027-03-10</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2027-03-12</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bentley University, Waltham, Massachusetts</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>$400 (Full-time Academics/Practitioners), $300 (Full-time PhD Students), $250 (Online Presentations)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>AI, Digital Transformation, Green Innovation, Systemic Resilience, Climate Finance, Climate Change: Mitigation and Adaptation, Sustainable Business Practices, Policy and Regulation, ESG Disclosures, Artificial Intelligence in Sustainability, Managing the Triple Bottom Line, Corporate Social Responsibility, Financial Innovation and Climate Transition, Carbon Emissions, Biodiversity Finance, Green Banking, Governance and Corporate Accountability, Financing Gaps in Sustainability, Political Risk and Sustainability, Market Mechanisms for Natural Resource Resilience</t>
+          <t>drivers of exchange rates and related asset prices from a financial perspective, exchange rates and the transmission of monetary policy, FX interventions and supply side shocks, exchange rates and macrofinancial stability frameworks, FX risk premia and their drivers, global linkages between capital flows, foreign exchange rates and risk appetite, the international use of currencies and its implications for exchange rates, implications of digital and tokenised assets for FX markets</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Finance at a Time of Change and Uncertainty — Journal of Corporate Finance &amp; Renmin University of China Conference</t>
+          <t>3rd Annual Boca Finance and Real Estate Conference</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Renmin University of China, Beijing, China</t>
+          <t>Florida Atlantic University, Boca Raton, Florida, USA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$50 USD</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Finance and AI, Finance and politics, Finance and climate change</t>
+          <t>All topics related to finance and real estate</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Fifth Annual Junior Faculty Business &amp; Financial Law Workshop</t>
+          <t>Southwestern Finance Association 2027 Annual Meeting</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-02-17</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Philadelphia, University of Pennsylvania</t>
+          <t>Las Vegas, NV</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1522,145 +1522,145 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Corporations, securities, finance, accounting, banking, bankruptcy, tax, general business law</t>
+          <t>All aspects of finance and financial education</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SGF Conference 2027</t>
+          <t>2026 Global Summit of Finance in the Age of AI and Climate Change</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2027-04-09</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2027-04-09</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Zurich, Switzerland</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CHF 60</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>All topic areas of finance</t>
+          <t>AI, information production, disclosure, and market efficiency; AI, corporate policies, and innovation; Financing science and technology innovation; Climate risks, asset prices, and financial stability; Green financial products, transition finance, and sustainable investing; Climate policy, environmental externalities, and corporate responses; Interactions between artificial intelligence and climate finance</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HEC-HKUST-NUS Workshop on Sustainable Finance</t>
+          <t>UWFC 2027</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2027-02-04</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2027-02-07</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Paris and Hong Kong</t>
+          <t>The Cliff Lodge at Snowbird, Utah</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>105 USD</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sustainable Finance</t>
+          <t>financial economics</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>European Winter Finance Conference 2027</t>
+          <t>European Winter Finance Summit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2027-01-10</t>
+          <t>2027-03-14</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2027-03-17</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hotel Armancette, Saint-Gervais-les-Bains (near Megève), France</t>
+          <t>Hotel Arlberghaus, Zürs, Austria</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>EUR 50</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>All areas of finance</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>International Conference in Venice - Artificial Intelligence, Financial Innovation and Credit Risk</t>
+          <t>NBS Conference on AI for Finance</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Venice, Italy</t>
+          <t>Nanyang Technological University (Singapore)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1670,34 +1670,34 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Artificial Intelligence, Financial Innovation, Credit Risk, Sustainability, Stability, Responsibility in a Data-Driven Financial System</t>
+          <t>Generative AI, Foundation Models, and Financial Decision-Making; AI-Driven Asset Pricing, Portfolio Management, and Investment Strategies; Machine Learning for Financial Forecasting and Market Prediction; Alternative Data, Natural Language Processing, and Financial Analytics; AI in Banking, Credit Risk Assessment, and Financial Intermediation; AI, FinTech Innovation, and the Future of Financial Services; Human-AI Collaboration in Financial Markets and Corporate Finance; AI for Climate Finance, ESG Analysis, and Sustainable Investing; AI Governance, Regulation, Ethics, and Responsible Innovation in Finance</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Prediction Markets Conference</t>
+          <t>Risk Theory Society Meeting 2027</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2027-05-28</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2027-05-30</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Yale School of Management, New Haven, Connecticut</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1707,145 +1707,145 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Theoretical and empirical research on prediction markets</t>
+          <t>insurance economics, financial economics related to insurance markets, actuarial science, economic analysis of risk and uncertainty</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>63rd Annual Eastern Finance Association Meeting</t>
+          <t>IIM Calcutta-NYU Stern India Research Conference</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2027-04-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2027-04-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>WEBINAR</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>$75 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>All areas of finance</t>
+          <t>finance, economics, and accounting covering issues concerning India and emerging economies; challenges and implications of major policy initiatives in India; effects of AI on the economies of India, China, and the US</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Oklahoma Aerospace and Defense Finance Conference</t>
+          <t>UNC Duke Corporate Finance Conference</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2027-03-26</t>
+          <t>2027-04-02</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2027-03-27</t>
+          <t>2027-04-03</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Norman, Oklahoma</t>
+          <t>Chapel Hill</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>100 USD</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Surging venture capital and private equity financing of aerospace and defense companies; Has the Starlink satcom network become SpaceX’s unique financial and economic flywheel?; Fiscal and financial impacts of the Rearmament of the West and incorporation of Ukraine into the alliance; Capital structure determinants for aerospace and defense companies; Will M&amp;A consolidate the space industry as it has the aviation and defense industries?; Sustainability and energy transition in military aviation; Funding of and financial returns from GPS and satellite company investments; Risk management, insurance, and financial engineering in aerospace and defense companies; Can one million satellites really create an orbital data center network?; Asset pricing of and financial returns from aerospace and defense investments; Will SpaceX’s record $86 billion IPO change the financing opportunity set of space companies?; Financing and investment challenges in the evolving commercial aircraft manufacturing duopoly; Differential impacts of asset characteristics on bankruptcy risk in aerospace and defense companies; Behavioral characteristics and leadership styles of aerospace company founders and CEOs; Impacts of international ownership and transit restrictions in the global aviation industry; Obsolescence risk and the financing of space companies; Why are airports state-owned in the US, but privately owned in other developed countries?; Cybersecurity investment and risk management in defense systems; Does government ownership and subsidization help or hurt Chinese space development?; Why is asset leasing pervasive in aviation, modest in defense, and non-existent in the space industry?; The importance of government contracts in promoting aerospace and defense industrial development; How will Lunar Base Alpha and Mars Colony One be financed?; Financial and strategic implications of the rise of drone, missile, and hypersonic warfare; Contrasting payout policies (dividends and share repurchases) of aviation, space, and defense companies; Paying for talent when cash is scarce: executive compensation in aerospace and defense start-ups</t>
+          <t>corporate finance</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026 Massey Sustainable Finance Conference</t>
+          <t>3rd LSU Finance Mardi Gras Conference</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2027-02-05</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2027-02-06</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Queenstown, New Zealand</t>
+          <t>Baton Rouge, LA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>75 USD</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Artificial intelligence and machine learning applications in Sustainable Finance, Alternative data on firms' digital transformation, Behavioral Finance/Economics and its implications to climate transition, Blue economy, Carbon market and carbon credit, Carbon price forecasting techniques, Circular economy, Corporate Social Responsibility, Climate Finance, Climate risks: assessment and management, Climate transition and portfolio management, Cryptocurrency and digital finance interactions with Sustainable Finance, Diversity, equity and inclusion in Finance, Digital finance, Fintech, and sustainability, Environmental, Social and Governance, Financial markets and climate transition, Household Finance and sustainability, Green Finance, Green Finance and energy security, (Renewable) Energy Finance, Renewable Energy and Sustainability, Sustainable Finance and Accounting</t>
+          <t>All topics in finance</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>22nd Annual Olin Finance Conference at WashU</t>
+          <t>Financial Research Association 2026 Annual Conference</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Washington University in St. Louis</t>
+          <t>Las Vegas, NV, USA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1855,71 +1855,71 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>asset pricing, behavioral finance, corporate finance, financial intermediation, household finance, development finance, labor finance</t>
+          <t>New finance papers of general interest to the profession; early work; research by junior scholars</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Southwestern Finance Association 2027 Annual Meeting</t>
+          <t>Winter Finance Summit in Asia</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2027-02-17</t>
+          <t>2027-03-01</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-03-04</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Las Vegas, NV</t>
+          <t>Iwate, Japan</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>JPY8,000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>All aspects of finance and financial education, panel discussions, tutorials</t>
+          <t>All areas of finance and real estate finance, particularly early-stage research not presented at major conferences</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Fisher AI in Business Conference</t>
+          <t>Stern/Salomon Microstructure Conference</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ohio State University, Columbus</t>
+          <t>Stern School, New York University</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1929,34 +1929,34 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>AI’s impact on business functions and organizational transformation; multi-agent AI systems and human-AI collaboration; AI-driven customer and employee experiences; AI, sustainability, and ESG; building and scaling AI ventures; AI governance, ethics, and regulation; AI’s influence on strategy and competition; AI’s impact on work and society; measuring AI effectiveness; and AI applications in healthcare, education, and other high-stakes domains.</t>
+          <t>Economics of securities markets, role of information in price-discovery process, measurement and determinants of liquidity, costs and benefits of alternate trading mechanisms, measurement and control of transactions costs, role of regulation, market design, trading costs comparisons, cross-border listing and trading securities, trading technology and information systems, implications of market design for risk management, financial engineering</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026 Derivative Markets Conference</t>
+          <t>22nd International Behavioural Finance Conference (IBFC)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Auckland, New Zealand</t>
+          <t>University of Chicago, Booth School of Business, Gleacher Center</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1966,219 +1966,219 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>All topics related to derivative markets</t>
+          <t>Behavioural Asset Pricing, Behavioural Corporate, Biases and Heuristics, Cryptocurrencies, Financial Analysts, Personal Financial Behavior, Financial Markets, Investment Decisions, Mergers and Acquisitions, Political Environment, Retail Investors, Sentiment, Climate Finance, CSR and ESG</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2027 Midwest Finance Association Annual Meeting</t>
+          <t>2026 Sydney Banking and Financial Stability Conference</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2027-03-18</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2027-03-20</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>The University of Sydney Business School, Sydney, Australia</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>75 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>corporate finance, financial institutions, asset pricing, asset management</t>
+          <t>Banking, financial stability, financial intermediation, financial institutions and markets, fintech, cryptocurrency and central bank digital currency, financial system stability, corporate finance, asset pricing, investment and funds management, macro finance</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2027 Bretton Woods Accounting and Finance Ski Conference</t>
+          <t>2026 VINS Annual Conference</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2027-03-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2027-03-06</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bretton Woods, New Hampshire</t>
+          <t>NYU Shanghai, Shanghai, China</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>89 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>All areas of accounting and finance</t>
+          <t>Applications in Asset Management &amp; Trading, Market Microstructure &amp; Liquidity, Emerging Financial &amp; Operational Risks, Governance &amp; Regulation</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Financial Econometrics Conference</t>
+          <t>FMA Annual Meeting</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2027-04-21</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2027-04-23</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Lancaster University, England</t>
+          <t>Tampa, FL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>£30 GBP</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>High-frequency econometrics, Market microstructure, Forecasting, Asset Pricing and investments, Risk neutral density estimation, Fintech &amp; blockchain, Cryptocurrencies, Climate econometrics, Volatility modelling, Artificial intelligence &amp; machine learning, Factor models, Term structure models, Risk modelling, Real time detection of extreme market events, Options &amp; derivatives modelling, Multivariate &amp; high dimensional time series modelling</t>
+          <t>Corporate Finance, Asset Pricing / Investments, Fintech and AI, Financial Institutions, Household Finance, Sustainable Finance</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>IIMB-CCGS International Corporate Governance &amp; Sustainability Conference 2026</t>
+          <t>34th Annual PBFEAM and 20th NYCU International conferences</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Indian Institute of Management, Bangalore, India</t>
+          <t>National Yang Ming Chiao Tung University, Hsinchu, Taiwan</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>USD $250 for On-line Presenter &amp; USD $300 for On-site Presenter</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Corporate governance, sustainability, geo-political risks, supply chain risk, AI, data analytics, machine learning, bridging management and law, corporate governance and executive leadership, internal and external mechanisms of corporate governance, board diversity, governance for sustainable value creation, governance in startups, family business &amp; SMEs, shareholders and stakeholders balance, role of auditors and institutional investors, corporate disclosures, environment, social and governance, enterprise risk management, cyber security and governance.</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Conference on CSR, the Economy and Financial Markets</t>
+          <t>11th Annual Young Scholars Finance Consortium</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2027-03-04</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2027-03-06</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Düsseldorf, Germany</t>
+          <t>The George Hotel, College Station, Texas</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>€150 for regular participants; €100 for PhD students</t>
+          <t>100 USD</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Climate risk and pricing; Role of financial markets, banks, institutional investors in CSR; Effects of CSR on valuation, performance, cost of capital, funding and capital structure; Socio-economic aspects and their implications for companies and financial markets; Corporate governance and CSR; Risk management and CSR; CSR reporting and disclosure; ESG backlash and politicization; Sustainability strategy under new constraints; Measurement: information content and reliability of ESG indices; CSR activities and the economy</t>
+          <t>corporate finance and governance, financial markets and intermediation, household finance</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>International Conference in Banking and Financial Studies 2026 (ICBFS 2026)</t>
+          <t>5th Frankfurt/Mannheim Workshop on Digital Finance</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Parma, Italy</t>
+          <t>Frankfurt am Main, Germany</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2188,34 +2188,34 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Accounting, auditing, and taxation; Asset allocation and valuation; Banking regulation and financial services; Behavioral and experimental finance/economics; Big data in finance, artificial intelligence, and cybersecurity; Climate finance and sustainability; Corporate finance, IPOs, SEOs, M&amp;A, and crowdfunding; Corporate governance; Country funds, sovereign funds, and hedge funds; Debt markets and instruments; Digital finance, cryptocurrencies, and blockchain; Emerging markets finance; Energy finance and environmental issues; Entrepreneurial finance, venture capital, and private equity; Ethical finance, green finance, ESG, and CSR; Financial accounting and regulation; Financial crises, contagion, integration, and global risk interconnections; Financial engineering and derivatives; Foreign exchange markets and currency issues; Global imbalances and sustainability; Household finance, real estate finance, and microfinance; Market efficiency and behavior; Multinational financial management; Portfolio management and optimization; Risk management and compliance; Small business finance</t>
+          <t>digital assets, decentralized finance (DeFi), FinTech, AI</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Colorado Finance Summit 2026</t>
+          <t>CBER-Tokenomics 2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Vail, Colorado</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2225,34 +2225,34 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>All areas of finance, both theoretical and empirical contributions</t>
+          <t>token and protocol design, decentralized finance, stablecoins and digital payments, DAOs and decentralized governance, tokenized real-world assets, prediction markets, AI agents and decentralized AI, economic world models, applications of large language models to macroeconomic, financial, and economy-wide modelling</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>18th Annual Hedge Fund Research Conference</t>
+          <t>21st Annual Conference on Asia-Pacific Financial Markets (CAFM)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Université Paris Dauphine - PSL, Paris</t>
+          <t>CONRAD Seoul</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2262,34 +2262,34 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hedge funds, mutual funds, ETFs, private equity funds, institutional investors’ risks and performance, transparency and due diligence, financial intermediation activity, systemic risk and contagion, institutional investors’ incentives and activism, portfolio liquidation and liquidity, financial regulation</t>
+          <t>All areas of finance</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>15th LaBS International Banking Workshop</t>
+          <t>2026 Vietnam Symposium in Climate Transition (VSCT-2026)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>HSE University and online</t>
+          <t>The University of Danang - University of Economics, Danang, Vietnam</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2299,34 +2299,34 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Banking in Emerging Markets: Challenges and Opportunities, theoretical and empirical research in all fields of Banking, Household finance</t>
+          <t>Behavioral finance/economics and its implications for climate transition, Blue economy, Carbon market, Circular economy, Climate change: mitigation and adaptation, Climate change: policy and regulations, Climate finance, Climate risks: assessment and management, Climate transition and COVID-19 recovery, Climate transition and portfolio management, Corporate Social Responsibility (CSR), Energy and environmental issues, Energy markets and energy transition, Environmental, Social and Governance (ESG), Financial markets and climate transition, Geopolitical risk and climate change mitigation, Just climate transition, Low-carbon technologies and innovation, Artificial intelligence and climate transition, Management of extractive industries, Responsible behaviors and sustainability in family business, Responsible business conduct and SDG goals, Role of management, business strategies, and SDG goals, Sustainable business model innovation, Sustainable entrepreneurship, Sustainable infrastructure investment, Sustainable production and consumption, Sustainable key performance indicators</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Private Equity Research Consortium (PERC) Symposium</t>
+          <t>2026 Conference on Auditing and Capital Markets</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Chapel Hill, NC</t>
+          <t>Washington, DC</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2336,71 +2336,71 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Private equity, buyouts, distressed securities, mezzanine financing, special situations, private credit, venture capital, real estate, real assets</t>
+          <t>Economic impact of auditing, audit regulation, audit oversight on capital markets</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>IMRC 2026</t>
+          <t>3rd American Conference of the Academy of Sustainable Finance, Accounting, Accountability &amp; Governance (ASFAAG) 2027</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2027-03-10</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2027-03-12</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>IIM Ahmedabad</t>
+          <t>Bentley University, Waltham, Massachusetts</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$400 (Full-time Academic/Practitioners), $300 (Full-Time PhD Students), $250 (Online Presentations)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Theoretical and Empirical Asset Pricing, Quality of Financial Reporting and Adoption of IFRS, Market Microstructure and Algorithmic Trading, Insurance / Reinsurance / Pension Funds, Business Cycles, Corporate Finance, Capital Structure and Dividend Policy, Financial Policy Choice, Institutions and Regulation, Enhancing Liquidity in Commodity Derivatives Markets, Public Economics, Asset Allocation and Investment Management, Computational Finance and Financial Econometrics, FDI and Portfolio Capital Flows, Household Finance, International Trade and Exchange Rates, Financial Crises, Systemic Risk and Macro-Finance, Financial Risk Analytics and Management, Financial Analytics, Monetary Policy and Banking, Global Value Chains and Firm Performance, Macroeconomics, Applied Microeconomics</t>
+          <t>Climate Finance, Climate Change: Mitigation and Adaptation, Sustainable Business Practices and Firms’ Profitability, Policy, Regulation, and Global Coordination, ESG Disclosures and Corporate Reporting Practices, Artificial Intelligence (AI), Data Analytics, and Machine Learning in the Context of Sustainability, Managing the Triple Bottom Line, Striking the balance between shareholders and other stakeholders' interests, Financial Reporting Quality and Accountability, Corporate Social Responsibility (CSR), Financial Innovation and Climate Transition, Carbon Emissions, Carbon pricing, Net-zero Commitments, Biodiversity Finance, Green Washing, Green Banking, Governance, Incentives, and Corporate Accountability, Financing Gaps: The Role of Pension Funds and Sovereign Wealth Management in Funding Sustainability Programs, Sustainability and Executive Compensation, Political Risk and Sustainability, Natural Resources Risk Mitigation, Market Mechanisms for Natural Resource Resilience, Risk, Disclosure, and Financial Stability, Emerging Markets, Adaptation, and Development Finance</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026 New Zealand Finance Meeting</t>
+          <t>Finance at a Time of Change and Uncertainty — Journal of Corporate Finance &amp; Renmin University of China Conference</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Auckland, New Zealand</t>
+          <t>Renmin University of China, Beijing, China</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2410,108 +2410,108 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>All topics related to the field of finance</t>
+          <t>Finance and AI, Finance and politics, Finance and climate change</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>6th Conference on Corporate Policies and Asset Prices (COAP)</t>
+          <t>Fifth Annual Junior Faculty Business &amp; Financial Law Workshop</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Nice, France, EDHEC Business School</t>
+          <t>Philadelphia, University of Pennsylvania</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>€50</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Asset pricing anomalies and their explanations, corporate finance models of asset pricing anomalies, dynamic corporate finance and contracting models and their asset pricing implications, asset pricing implications of sustainable finance, feedback effects from asset prices to corporate decisions, structural estimation of dynamic models using asset price data</t>
+          <t>corporations, securities, finance, accounting, banking, bankruptcy, tax, general business law</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5th Contemporary Issues in Financial Markets and Banking</t>
+          <t>SGF Conference 2027</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2027-02-10</t>
+          <t>2027-04-09</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2027-02-11</t>
+          <t>2027-04-09</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Online Conference</t>
+          <t>Zurich, Switzerland</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>USD 175</t>
+          <t>60 CHF</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Financial resilience; Green, climate and sustainable finance; Decentralised finance and disruptive financial technologies; Theoretical asset pricing; Empirical asset pricing, liquidity and behavioural economics and finance; Risk management; Financial inclusion; Alternative investments; Crowd-funding; Islamic banking; Banking and financial sector stability and regulation; Financial (dis)integration and Brexit; Artificial intelligence, machine and deep learning applications in finance; Corporate finance and sustainable energy financing; Crisis investment and portfolio management; Corporate governance; International financial management and investment; Market microstructure; Household finance; Real estate and property markets; Metaverse and Blockchain technologies in finance; Intersection between finance and economic theory, especially financial applications of game theory, decision theory, and computational financial economics; experimental economics with implications for financial theory and practice.</t>
+          <t>All topic areas of finance</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>International Conference on Trade Wars, Geopolitical Fragmentation and Repercussions for Financial and Monetary Stability</t>
+          <t>HEC-HKUST-NUS Workshop on Sustainable Finance</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Brunel University of London (UK)</t>
+          <t>Paris and Hong Kong</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2521,34 +2521,34 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Art of the (trade) deal and financial costs; Asymmetric impacts on regions, commodity exporters, service-oriented economies and manufacturing centres; Capital flows and sudden stops due to trade wars; Central Banking in the age of trade wars and geopolitical conflicts; Central bank digital currencies (CBDCs), trade wars and geopolitical tensions; Currency weaponisation, competitive devaluation and financial instability; Digitisation, financial decoupling and financial stability during trade conflicts; Emerging markets and international financial flows under trade tensions; Empirical and theoretical analyses of strategic financial policies under trade restrictions; Exorbitant privilege of the US$ in the 21st century and the rise of alternative currencies; European Economic and Monetary Union’s financial integration with the US and the Global South; Financialization in the context of trade wars; Global financial imbalances, causes and financial consequences in the context of trade wars; International financial and monetary architecture and stress management in the age of trade conflict; Inflation targeting, trade wars and geopolitical conflicts; Productivity, innovation and efficiency related to technological spillovers and protectionism; Reallocation of global capital, safe havens and asset price bubbles during trade conflicts; Regional financial and monetary integration and the positive role of regions during trade conflicts; Role of central banks and macroprudential policy during trade conflicts; Sustainable financial development of the Global South and trade wars; Tariffs and non-tariff barriers and their negative financial impact on markets and firms</t>
+          <t>Sustainable Finance</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Labor &amp; Finance Group Fall 2026 Conference</t>
+          <t>European Winter Finance Conference 2027</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2027-01-10</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2027-01-13</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Penn State University – Smeal College of Business, State College, PA</t>
+          <t>Hotel Armancette, Saint-Gervais-les-Bains (near Megève), France</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2558,34 +2558,34 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Human capital, compensation, and incentives; Labor market power, monopsony/oligopsony, and wage setting; Unions, collective bargaining, and worker representation; Organizational design, internal labor markets, and corporate governance; Labor mobility, non-compete agreements, and talent flows; Labor-related disclosure, regulation, and policy; Labor and financial markets, asset pricing, and corporate policies; Entrepreneurship and innovation</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CUHK-RAPS-RCFS Conference on Asset Pricing and Corporate Finance</t>
+          <t>C.R.E.D.I.T. 2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Venice, Italy</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2595,34 +2595,34 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Asset Pricing, Corporate Finance</t>
+          <t>Artificial Intelligence, Financial Innovation, Credit Risk, Financial Stability, Sustainability, Market Integrity, Machine Learning, ESG</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026 ABFER-JFDS Conference on AI for Finance</t>
+          <t>Prediction Markets Conference</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>International Institute of Finance, No. 1789 Guangxi Road, Hefei, Anhui, China</t>
+          <t>Yale School of Management, New Haven, Connecticut</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2632,14 +2632,14 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Applications of artificial intelligence, machine learning, natural language processing, large language models, AI agents, high-performance computing, and other novel analytical methods in finance and financial economics; Use of unstructured and alternative data in investment, auditing, assurance, and related fields; Social and economic impacts of AI adoption; Ethical, governance, and regulatory considerations of AI in finance; Quantitative investment strategies, portfolio optimization, digital assets, DeFi, and platform finance using machine learning technologies or other AI models.</t>
+          <t>Theoretical and empirical research on prediction markets</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Financial Economic Meeting</t>
+          <t>63rd Annual Eastern Finance Association Meeting</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2649,54 +2649,54 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2027-04-07</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2027-04-10</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$75 USD</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Financial markets &amp; asset pricing, Banking, credit &amp; financial stability, Macroeconomics &amp; international finance, Sustainable finance &amp; climate risk, Quantitative methods &amp; emerging approaches</t>
+          <t>All areas of finance</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>39th Australasian Finance and Banking Conference</t>
+          <t>Oklahoma Aerospace and Defense Finance Conference</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2027-03-26</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2027-03-27</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sydney, Australia</t>
+          <t>Norman, Oklahoma</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2706,34 +2706,34 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Opportunities and Risks of AI Technology in Finance, CBDCs, Fintech, and Digital Finance, Sustainable Investment</t>
+          <t>Theoretical and empirical papers on aviation, space, or defense finance, including but not limited to venture capital and private equity financing, fiscal impacts of rearmament, capital structure determinants, mergers and acquisitions in the space industry, sustainability in military aviation, funding of satellite investments, risk management in aerospace companies, and implications of drone and hypersonic warfare.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MIT GCFP 13th Annual Conference</t>
+          <t>2026 Massey Sustainable Finance Conference</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Cambridge, MA</t>
+          <t>Queenstown, New Zealand</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2743,71 +2743,71 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>financial regulation in an era of innovation and disruption, AI’s impact on financial markets, labor markets and the economy, investor protection and fair lending, new risks to financial stability, changing market structure for equities, bonds, and derivatives, growth of event contracts and prediction markets, growth of non-bank credit, developments in stablecoins, digital currencies and payment systems, risks in “safe” assets such as sovereign debt, international coordination and comparisons, innovations in market architecture and infrastructure</t>
+          <t>Artificial intelligence and machine learning applications in Sustainable Finance, Alternative data on firms' digital transformation, Behavioral Finance/Economics and its implications to climate transition, Blue economy, Carbon market and carbon credit, Carbon price forecasting techniques, Circular economy, Corporate Social Responsibility, Climate Finance, Climate risks: assessment and management, Climate transition and portfolio management, Cryptocurrency and digital finance interactions with Sustainable Finance, Diversity, equity and inclusion in Finance, Digital finance, Fintech, and sustainability, Environmental, Social and Governance, Financial markets and climate transition, Household Finance and sustainability, Green Finance, Green Finance and energy security, (Renewable) Energy Finance, Renewable Energy and Sustainability, Sustainable Finance and Accounting</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>EUROFIDAI-ESSEC Paris December Finance Meeting</t>
+          <t>22nd Annual Olin Finance Conference at WashU</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Pullman Paris Montparnasse Hotel</t>
+          <t>Washington University in St. Louis</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>75€</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Latest research in all areas of finance</t>
+          <t>asset pricing, behavioral finance, corporate finance, financial intermediation, household finance, development finance, labor finance</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Chicago Fed/University of Chicago Conference on Municipal Bond Markets</t>
+          <t>Fisher AI in Business Conference</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Chicago</t>
+          <t>Ohio State University, Columbus</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2817,256 +2817,256 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Unpublished and highly policy-relevant research papers on municipal bond markets, including primary market frictions, secondary market frictions, the role of retail investors, and the effect of state and federal policies on state and local government access to external finance.</t>
+          <t>AI’s impact on business functions and organizational transformation; multi-agent AI systems and human-AI collaboration; AI-driven customer and employee experiences; AI, sustainability, and ESG; building and scaling AI ventures; AI governance, ethics, and regulation; AI’s influence on strategy and competition; AI’s impact on work and society; measuring AI effectiveness; AI applications in healthcare, education, and other high-stakes domains.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SFS Cavalcade Asia-Pacific 2026</t>
+          <t>2026 Derivative Markets Conference</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>City University of Hong Kong</t>
+          <t>Auckland, New Zealand</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>$75 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fixed Income, Asset Pricing, Corporate Finance</t>
+          <t>All topics related to derivative markets</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sustainable Accounting, Finance and Economics International Conference 2026 (SAFE2026)</t>
+          <t>Midwest Finance Association Annual Meeting</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2027-03-18</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2027-03-20</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bandar Sunway, Malaysia</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>75 USD</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sustainability-oriented research in accounting, finance, and economics</t>
+          <t>corporate finance, financial institutions, asset pricing, asset management</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026 CLIMATE FINANCE &amp; POLICY (CFP-2026)</t>
+          <t>Bretton Woods Accounting and Finance Ski Conference</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2027-03-03</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2027-03-06</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bari, Italy</t>
+          <t>Bretton Woods, New Hampshire</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$89 USD</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>AI-driven Climate Risk Assessment and Prediction, Big Data and ESG Decision-making, Carbon Border Adjustment Mechanisms, Carbon Finance and Pricing, Climate Change and Corporate Behavior, Climate Finance for Energy Efficiency, Carbon Taxes, Climate Agreements and Frameworks, Climate Funds and Public Finance, Climate Risk Assessment and Disclosure, ESG Measurement, Ratings &amp; Data Quality, Financing Climate Adaptation and Resilience, Green Finance, Green Bonds and Socially Responsible Bonds, Just Transition, Nature, Biodiversity &amp; Finance, Role of Technology in Climate Finance, Sustainable Investing, Sustainability Regulation &amp; Political Economy</t>
+          <t>All areas of accounting and finance</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026 Global AI Finance Research Conference</t>
+          <t>IIMB-CCGS International Corporate Governance &amp; Sustainability Conference 2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Taipei, Taiwan</t>
+          <t>Indian Institute of Management, Bangalore, India</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Waived for selected Paper Presenters</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Artificial Intelligence (AI), Big Data and Machine Learning, Blockchain and Cryptocurrencies, Security Token Offerings (STOs) and Initial Coin Offerings (ICOs), Decentralized Finance (DeFi), Peer-to-peer lending, FinTech regulation, High-frequency trading and market liquidity, Green FinTech</t>
+          <t>Corporate governance and sustainability, Geo-political, economy, supply chain risk and corporate governance, AI, Data Analytics, and Machine Learning: Technology &amp; Governance, Bridging Management and Law for a Responsible Corporation, Corporate Governance and Executive Leadership, Internal &amp; External Mechanisms of Corporate Governance, Corporate Governance in Today’s Business Environment, Board Diversity, Governance for sustainable value creation, Governance in Startups, family business &amp; SMEs, Managing the right balance: Shareholders and Stakeholders, Role of Auditors and Institutional Investors, Corporate Disclosures &amp; Reporting Practices, Environment, Social and Governance, Enterprise Risk Management, Cyber Security &amp; Governance</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>37th Annual Conference of the Academy of Behavioral Finance &amp; Economics</t>
+          <t>Conference on CSR, the Economy and Financial Markets</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Santa Monica, California, USA</t>
+          <t>Düsseldorf, Germany</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>$99.00 USD</t>
+          <t>€150 for regular participants; €100 for PhD students</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Behavioral/Cognitive Finance &amp; Economics, Neuroscience/Neuromorphic Computing, Political Economy, Biological Anthropology, Brain-Computer Interfaces</t>
+          <t>Effects of CSR on valuation, performance, cost of capital, funding and capital structure; Role of financial markets, banks, institutional investors in CSR; Climate risk and pricing; Socio-economic aspects and their implications for companies and financial markets; Corporate governance and CSR; Risk management and CSR; CSR reporting and disclosure; ESG backlash and politicization; Sustainability strategy under new constraints; Measurement and reliability of ESG indices; CSR activities and the economy at macro and micro levels.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026 UNSW Asset Pricing Workshop</t>
+          <t>International Conference in Banking and Financial Studies 2026 (ICBFS 2026)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sydney (NSW, Australia)</t>
+          <t>Parma, Italy</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>0 AUD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>All areas of Finance with a special focus on Asset Pricing</t>
+          <t>Accounting, auditing, and taxation; Asset allocation and valuation; Banking regulation and financial services; Behavioral and experimental finance/economics; Big data in finance, artificial intelligence, and cybersecurity; Climate finance and sustainability; Corporate finance, IPOs, SEOs, M&amp;A, and crowdfunding; Corporate governance; Country funds, sovereign funds, and hedge funds; Debt markets and instruments; Digital finance, cryptocurrencies, and blockchain; Emerging markets finance; Energy finance and environmental issues; Entrepreneurial finance, venture capital, and private equity; Ethical finance, green finance, ESG, and CSR; Financial accounting and regulation; Financial crises, contagion, integration, and global risk interconnections; Financial engineering and derivatives; Foreign exchange markets and currency issues; Global imbalances and sustainability; Household finance, real estate finance, and microfinance; Market efficiency and behavior; Multinational financial management; Portfolio management and optimization; Risk management and compliance; Small business finance</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>International Conference in Venice - Artificial Intelligence, Financial Innovation and Credit Risk</t>
+          <t>Colorado Finance Summit 2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Venice, Italy</t>
+          <t>Vail, Colorado</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3076,71 +3076,71 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Credit risk, financial innovation, artificial intelligence, sustainability, stability, responsibility, risk management, digital transformation, regulation, ethical risk, and systemic risk.</t>
+          <t>All areas of finance, theoretical contributions, empirical contributions</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>36th Annual Conference on Financial Economics and Accounting (CFEA)</t>
+          <t>18th Annual Hedge Fund Research Conference</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Toronto, Ontario (Canada)</t>
+          <t>Université Paris Dauphine - PSL, Paris</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>100 CAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Financial economics and accounting</t>
+          <t>hedge funds, mutual funds, ETFs, private equity funds, institutional investors’ risks and performance, transparency and due diligence, financial intermediation activity, systemic risk and contagion, institutional investors’ incentives and activism, portfolio liquidation and liquidity, financial regulation</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026 Lugano Real Estate and Urban Economics Conference</t>
+          <t>15th LaBS International Banking Workshop</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Lugano, Switzerland</t>
+          <t>HSE University and online</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3150,34 +3150,34 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>real estate finance, urban economics, real estate economics, regional economics</t>
+          <t>Banking in Emerging Markets, Household finance, theoretical and empirical research in Banking</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Santiago Finance Workshop 2026</t>
+          <t>Private Equity Research Consortium (PERC) Symposium</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Universidad de Chile, Diag. Paraguay 257, Santiago, Chile</t>
+          <t>Chapel Hill, NC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3187,34 +3187,34 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Any topic in finance or financial economics</t>
+          <t>Theoretical and empirical papers in the broad field of private equity, including research on buyouts, distressed securities, mezzanine financing, special situations, private credit, venture capital, real estate, and real assets</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>4th International Conference on Circular Economy, Business Strategy &amp; Management</t>
+          <t>IMRC 2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>EM Normandie Business School, Caen campus, France</t>
+          <t>IIM Ahmedabad</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3224,34 +3224,34 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>sustainability, ESG, innovation, resilience, circular business models, future of management research</t>
+          <t>Theoretical and Empirical Asset Pricing, Quality of Financial Reporting and Adoption of IFRS, Market Microstructure and Algorithmic Trading, Insurance/Reinsurance/Pension Funds, Business Cycles, Corporate Finance, Capital Structure and Dividend Policy, Financial Policy Choice, Institutions and Regulation, Enhancing Liquidity in Commodity Derivatives Markets, Public Economics, Asset Allocation and Investment Management, Computational Finance and Financial Econometrics, FDI and Portfolio Capital Flows, Household Finance, International Trade and Exchange Rates, Financial Crises, Systemic Risk and Macro-Finance, Financial Risk Analytics and Management, Financial Analytics, Monetary Policy and Banking, Global Value Chains and Firm Performance, Macroeconomics, Applied Microeconomics</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Climate Finance &amp; Sustainability Conference</t>
+          <t>2026 New Zealand Finance Meeting</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Montréal, QC, Canada</t>
+          <t>Auckland, New Zealand</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3261,108 +3261,108 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sustainability in business across various disciplines including strategy and management, accounting and finance, entrepreneurship and innovation, marketing and responsible consumption, supply chain and operations management</t>
+          <t>all topics related to the field of finance</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>China Accounting and Finance Review (CAFR) Special Issue Conference 2026</t>
+          <t>6th Conference on Corporate Policies and Asset Prices (COAP)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Zhongnan University of Economics and Law, Wuhan, China</t>
+          <t>Nice, France</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>€50</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>ESG in the AI Era: Challenges and Opportunities; AI-Driven ESG Reporting and Assurance; Algorithmic Bias, Ethics, and Fairness in ESG Analytics; Regulatory Responses to AI-Enabled ESG Practices; AI, Greenwashing, and Corporate Accountability; AI for Sustainable Finance and Investment Decision-Making</t>
+          <t>asset pricing anomalies and their explanations, corporate finance models of asset pricing anomalies, dynamic corporate finance and contracting models and their asset pricing implications, the asset pricing implications of sustainable finance, feedback effects from asset prices to corporate decisions, structural estimation of dynamic models using asset price data</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026 FMA Asia/Pacific Conference</t>
+          <t>5th Contemporary Issues in Financial Markets and Banking</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2027-02-10</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2027-02-11</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Massey University, Auckland, New Zealand</t>
+          <t>Online Conference</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>$50 USD (FMA-members), $60 USD (non-members)</t>
+          <t>USD 175</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Financial decision-making, financial management, related topics</t>
+          <t>Financial resilience; Green, climate and sustainable finance; Decentralised finance and disruptive financial technologies; Theoretical asset pricing; Empirical asset pricing, liquidity and behavioural economics and finance; Risk management; Financial inclusion; Alternative investments; Crowd-funding; Islamic banking; Banking and financial sector stability and regulation; Financial (dis)integration and Brexit; Artificial intelligence, machine and deep learning applications in finance; Corporate finance and sustainable energy financing; Crisis investment and portfolio management; Corporate governance; International financial management and investment; Market microstructure; Household finance; Real estate and property markets; Metaverse and Blockchain technologies in finance; Intersection between finance and economic theory, especially financial applications of game theory, decision theory, and computational financial economics; experimental economics with implications for financial theory and practice.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sixth Biennial Conference on Auto Lending</t>
+          <t>International Conference on Trade Wars, Geopolitical Fragmentation and Repercussions for Financial and Monetary Stability</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Philadelphia</t>
+          <t>Brunel University of London (UK)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3372,34 +3372,34 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>auto lending, consumer finance, consumer demand and vehicle choice, loan pricing and contract design, underwriting and credit risk modeling, dealer intermediation and markups, borrower outcomes and delinquency dynamics, fraud and identity risk, fair lending and consumer compliance, subprime and near-prime market structure, repossession and loss mitigation, servicing and collections, alternative data and automated decisioning, electric vehicles and evolving collateral risk, used vehicle prices and depreciation, auto insurance interactions, fintech and market structure, auto asset-backed securities, spillovers from monetary policy and macroeconomic shocks</t>
+          <t>Art of the (trade) deal and financial costs; Asymmetric impacts on regions, commodity exporters, service-oriented economies and manufacturing centres; Capital flows and sudden stops due to trade wars; Central Banking in the age of trade wars and geopolitical conflicts; Central bank digital currencies (CBDCs), trade wars and geopolitical tensions; Currency weaponisation, competitive devaluation and financial instability; Digitisation, financial decoupling and financial stability during trade conflicts; Emerging markets and international financial flows under trade tensions; Empirical and theoretical analyses of strategic financial policies under trade restrictions; Exorbitant privilege of the US$ in the 21st century and the rise of alternative currencies; European Economic and Monetary Union’s financial integration with the US and the Global South; Financialization in the context of trade wars; Global financial imbalances, causes and financial consequences in the context of trade wars; International financial and monetary architecture and stress management in the age of trade conflict; Inflation targeting, trade wars and geopolitical conflicts; Productivity, innovation and efficiency related to technological spillovers and protectionism; Reallocation of global capital, safe havens and asset price bubbles during trade conflicts; Regional financial and monetary integration and the positive role of regions during trade conflicts; Role of central banks and macroprudential policy during trade conflicts; Sustainable financial development of the Global South and trade wars; Tariffs and non-tariff barriers and their negative financial impact on markets and firms</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Frontiers in Machine Learning and Economics: Methods and Applications</t>
+          <t>Labor &amp; Finance Group Fall 2026 Conference</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2023-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
           <t>2026-11-06</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Philadelphia</t>
+          <t>Penn State University – Smeal College of Business, State College, PA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3409,34 +3409,34 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Methodological advances in analyzing complex and high-dimensional data sets, Methodological advances in natural language processing (particularly with respect to causal inference), Innovative applications of generative AI, The societal impacts of AI and algorithmic decision-making</t>
+          <t>Human capital, compensation, and incentives; Labor market power, monopsony/oligopsony, and wage setting; Unions, collective bargaining, and worker representation; Organizational design, internal labor markets, and corporate governance; Labor mobility, non-compete agreements, and talent flows; Labor-related disclosure, regulation, and policy; Labor and financial markets, asset pricing, and corporate policies; Entrepreneurship and innovation</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Workshop on Innovations in Credit Scoring</t>
+          <t>CUHK-RAPS-RCFS Conference on Asset Pricing and Corporate Finance</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Virtual</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3446,71 +3446,71 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Innovations in credit scoring, alternative data, artificial intelligence, machine learning, risk management, credit access</t>
+          <t>Asset Pricing, Corporate Finance</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026 Conference on Real-Time Data Analysis, Methods, and Applications</t>
+          <t>2026 ABFER-JFDS Conference on AI for Finance</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Philadelphia</t>
+          <t>International Institute of Finance, No. 1789 Guangxi Road, Hefei, Anhui, China</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0 USD</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>monitoring and forecasting of economic and financial developments, high-frequency data, survey data, text as data, transactions data, granular data, using preliminary and revised data in economic policy formulation and analysis, machine learning applications in real-time macroeconomics, probabilistic forecasts and assessments of crisis risks, related innovative data sets and toolboxes, seasonal and cyclical adjustment for real-time monitoring and forecasting</t>
+          <t>Applications of artificial intelligence, machine learning, natural language processing, large language models, AI agents, high-performance computing, and other novel analytical methods in finance and financial economics; Use of unstructured and alternative data in investment, auditing, assurance, and related fields; Social and economic impacts of AI adoption; Ethical, governance, and regulatory considerations of AI in finance; Quantitative investment strategies, portfolio optimization, digital assets, DeFi, and platform finance using machine learning technologies or other AI models.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026 Jacobs Levy Center Frontiers in Quantitative Finance Conference</t>
+          <t>Financial Economics Meeting</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3520,71 +3520,71 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Quantitative methods and asset pricing</t>
+          <t>Financial markets &amp; asset pricing, banking, credit &amp; financial stability, macroeconomics &amp; international finance, sustainable finance &amp; climate risk, quantitative methods &amp; emerging approaches</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026 AIM Investment Conference</t>
+          <t>39th Australasian Finance and Banking Conference</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Austin, Texas</t>
+          <t>Sydney, Australia</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>75 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>mutual funds, hedge funds, pension funds, investment management</t>
+          <t>Opportunities and Risks of AI Technology in Finance, CBDCs, Fintech, and Digital Finance, Sustainable Investment</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026 Wharton Conference on Liquidity and Financial Fragility</t>
+          <t>MIT GCFP 13th Annual Conference</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>University of Pennsylvania, Philadelphia, PA</t>
+          <t>Cambridge, MA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3594,71 +3594,71 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Coordination failures, self-fulfilling beliefs, and runs; Fragility in banks and non-bank institutions; Liquidity and frictions in financial markets and macroeconomy; Systemic risk and financial regulation; Monetary policy and financial stability; Artificial intelligence (AI) and its implications for financial macroeconomic stability; The rise and potential risks in private credit markets; New payment technologies, stablecoins, tokenization, and their financial stability implications; Geopolitical tensions, trade conflicts, currency competition, and financial fragility; Inflation, interest rate risks, and implications on financial fragility; The real impact of crises and fragility on firms’ financing and investment policies</t>
+          <t>Financial regulation, AI’s impact on financial markets, labor markets, investor protection, fair lending, risks to financial stability, changing market structure for equities, bonds, derivatives, event contracts and prediction markets, non-bank credit, stablecoins, digital currencies, payment systems, risks in sovereign debt, international coordination, innovations in market architecture and infrastructure.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Towards a New Synthesis in Islamic Finance: Law, Economics and Shari’ah</t>
+          <t>EUROFIDAI-ESSEC Paris December Finance Meeting</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Online Conference from Durham University, England, UK</t>
+          <t>Pullman Paris Montparnasse Hotel</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>75€</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Islamic finance, financial innovation, regulatory oversight, governance mechanisms, economic development, sustainability, social equity, inclusive economic development</t>
+          <t>All areas of finance</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>74th Meeting of the EURO Working Group for Commodities and Financial Modelling (EWGCFM)</t>
+          <t>Chicago Fed/University of Chicago Conference on Municipal Bond Markets</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Casa de Campo, La Romana, Dominican Republic</t>
+          <t>Federal Reserve Bank of Chicago</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3668,71 +3668,71 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Asset Pricing, Corporate Finance, Banking and Financial Institutions, Commodities and Energy Markets, Financial Modelling and Econometrics, Blockchain and Cryptocurrencies, Derivatives and Risk Management, Market Microstructure, and Sustainable Finance</t>
+          <t>Unpublished and highly policy-relevant research papers on municipal bond markets, primary and secondary market frictions, role of retail investors in bond price formation, effects of state and federal policies on local government access to finance</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>FIRN 2026 ANU Money, Credit, and Financial Stability Meeting</t>
+          <t>SFS Cavalcade Asia-Pacific 2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Australian National University (ANU), Canberra, Australia</t>
+          <t>City University of Hong Kong</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$75 USD</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Monetary policy and transmission mechanisms, Credit markets and financial intermediation, Banking, liquidity, and regulation, Financial crises and systemic risk, Macro-finance</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Inaugural Annual Conference on Insurance</t>
+          <t>Sustainable Accounting, Finance and Economics International Conference 2026 (SAFE2026)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Chicago</t>
+          <t>Bandar Sunway, Malaysia</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3742,34 +3742,34 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>life insurance, Property &amp; Casualty insurance, Reinsurance and risk transfer, Mergers and other ownership changes, Private equity ownership and impact on industry, Indexed, variable annuities, and other savings products, Household insurance choices, Insurances’ investment and funding strategies, Catastrophe risk, Impact of insurance regulation</t>
+          <t>Sustainability-oriented research in accounting, finance, and economics</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Payments, Digital Assets, AI and the Future of Financial Markets</t>
+          <t>2026 Climate Finance &amp; Policy (CFP-2026)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Imperial Business School, London</t>
+          <t>Bari, Italy</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3779,34 +3779,34 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Digital platforms, banking, and financial intermediation; Artificial intelligence, machine learning, and financial decision-making; Blockchain, tokenization, digital assets, and decentralized finance; Payment systems, central bank digital currencies, and stablecoins; FinTech regulation, supervision, market design, and financial stability; Data, privacy, cybersecurity, and consumer protection in finance; Entrepreneurial finance, venture capital, and innovation in financial services; Household finance, inclusion, and welfare effects of financial technology; Market microstructure, trading technologies, and liquidity; Competition between banks, platforms, and non-bank financial institutions</t>
+          <t>AI-driven Climate Risk Assessment and Prediction, Big Data and ESG Decision-making, Carbon Border Adjustment Mechanisms, Carbon Finance and Pricing, Climate Change and Corporate Behavior, Climate Finance for Energy Efficiency, Carbon Taxes, Climate Agreements and Frameworks, Climate Funds and Public Finance, Climate Risk Assessment and Disclosure, ESG Measurement, Ratings &amp; Data Quality, Financing Climate Adaptation and Resilience, Green Finance, Green Bonds and Socially Responsible Bonds, Just Transition, Nature, Biodiversity &amp; Finance, Role of Technology in Climate Finance, Sustainable Investing, Sustainability Regulation &amp; Political Economy</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Future Scholars in Finance Forum</t>
+          <t>2026 Global AI Finance Research Conference</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Beijing, China</t>
+          <t>Taipei, Taiwan</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3816,71 +3816,71 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>All areas of finance</t>
+          <t>Artificial Intelligence (AI), Big Data and Machine Learning, Blockchain and Cryptocurrencies, Security Token Offerings (STOs) and Initial Coin Offerings (ICOs), Decentralized Finance (DeFi), Peer-to-peer lending, FinTech regulation, High-frequency trading and market liquidity, Green FinTech</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Prototypes for Humanity 2026 Short Papers Platform</t>
+          <t>37th Annual Conference of the Academy of Behavioral Finance &amp; Economics</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Dubai, UAE</t>
+          <t>Santa Monica, California, USA</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>99.00 USD</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Wellbeing and Human Performance, Infrastructures and Cities, Autonomous Systems and Advanced Manufacturing, Environment, Sustainability and Energy, Mobility and Logistics, Socio-Economic Empowerment, Digital Economies and Future Markets, Open and Speculative</t>
+          <t>Behavioral/Cognitive Finance &amp; Economics, Neuroscience/Neuromorphic Computing, Political Economy, Biological Anthropology, Brain-Computer Interfaces, Development of New Financial &amp; Economic Models, Decision Making, Venture Startups &amp; Exits, Markets &amp; Capital, Investment &amp; Management, Development, Personal Finance, Pedagogy, Empirical Works, Planning, Strategies, Regulation, Valuation</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026 Federal Reserve Stress Testing Research Conference</t>
+          <t>2026 UNSW Asset Pricing Workshop</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Boston, Massachusetts</t>
+          <t>Sydney (NSW, Australia)</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3890,34 +3890,34 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>The economic and macroprudential effects of stress tests and bank regulation, Novel approaches to modeling bank profitability, financial risks, and operational risks, Design and applications of stress scenarios and reverse stress testing, Nonbank credit intermediation, Financial instruments for risk transfer, Recent developments in bank regulation, The impact of emerging technologies on banks and their regulators</t>
+          <t>All areas of Finance, with a special focus on Asset Pricing</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EBA's 15th Policy Research Workshop</t>
+          <t>International Conference in Venice - Artificial Intelligence, Financial Innovation and Credit Risk</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>EBA premises (Paris, France) and remotely</t>
+          <t>Venice, Italy</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3927,71 +3927,71 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Competitiveness and efficiency in the prudential rulebook without undermining resilience; Impacts of efficiency and proportionality; Competition, innovation, market entry, cross border growth and new areas under financial supervision; Proportionate integration of ESG risks in governance, strategy, and remuneration frameworks</t>
+          <t>Credit Risk and Advanced Analytics, Financial Innovation and Digital Transformation, Artificial Intelligence, Data Governance and Ethical Risk, Sustainability and Long-Term Value Creation, Systemic Risk, Resilience and Policy</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>3rd Financial Fraud, Misconduct and Market Manipulation Conference</t>
+          <t>36th Annual Conference on Financial Economics and Accounting (CFEA)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Lancaster University, England</t>
+          <t>Toronto, Ontario (Canada)</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>100 CAD</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Theoretical and empirical analysis of financial fraud, Case studies of recent instances of market misconduct, Insider trading, Implication of financial fraud/market manipulation for market efficiency, stability, and asset pricing, Market manipulation at a high-frequency (intraday) level, Fraudulent activities and crypto currency markets, Social networks, fake news, and their effect on financial markets, Money laundering and banking, Conflicts of interests and their implications for various stakeholders and financial markets, Hedge funds/Mutual funds and their involvement in market misconduct, Statistical/Machine Learning methods for fraud detection, Cyber security and cyber risk management, Regulatory response to financial misconduct, Unintended consequences of politics and regulations</t>
+          <t>Financial economics and accounting</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>22nd Annual Haskell &amp; White Corporate Reporting and Governance Conference</t>
+          <t>2026 Lugano Real Estate and Urban Economics Conference</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>California State University, Fullerton</t>
+          <t>Lugano, Switzerland</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4001,34 +4001,34 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>All areas of accounting and finance, including interdisciplinary research related to corporate reporting, governance, and financial markets</t>
+          <t>real estate economics, real estate finance, regional economics, urban economics</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>25th Annual Bank Research Conference</t>
+          <t>Santiago Finance Workshop 2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Arlington, VA</t>
+          <t>Universidad de Chile, Diag. Paraguay 257, Santiago, Chile</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4038,71 +4038,71 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Regulatory reform options and considerations, Risk and resiliency in the financial system, Real effects of financial turmoil, Innovations in financial intermediation, Deposit insurance and stability, Emerging competitive threats to traditional banking, AI and technology in finance, Banks’ role in the 21st Century</t>
+          <t>Any topic in finance or financial economics</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>The Future of Decision-Making and Risk-Taking: Bridging Finance, Economics, Brain, and Behavior</t>
+          <t>4th International Conference on Circular Economy, Business Strategy &amp; Management</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Santa Monica, California, USA</t>
+          <t>EM Normandie Business School, Caen campus, France</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>$99.00 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Behavioral/Cognitive Finance &amp; Economics, Neuroscience/Neuromorphic Computing, Political Economy, Biological Anthropology, Brain-Computer Interfaces, Development of New Financial &amp; Economic Models, Decision Making under risk and uncertainty, Venture Startups &amp; Exits, Trust in Financial/Capital Markets, Financial Management of Companies, Entrepreneurship and Innovation, Personal Finance, Behavioral Finance applications, Empirical Works in AI generated databases, Evidence-Based Financial Planning, Neuromorphic-based Strategies, Regulation and Valuation.</t>
+          <t>sustainability, ESG, innovation, resilience, circular business models, future of management research</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>17th Emerging Markets Conference</t>
+          <t>Climate Finance &amp; Sustainability Conference</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Mumbai, India</t>
+          <t>Montréal, QC, Canada</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4112,34 +4112,34 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>The sources of economic success or failure in EMs; Finance in EMs; Political economy, law, public administration, regulation in EMs; The impact of populism upon the possibility of sustained growth; Insights into large EMs; Insights from narrow research projects; The new phase of globalisation; Features of a society enabling or disabling convergence; The puzzles faced by decision makers; Grand challenges such as climate change; State capability in EMs; The interplay of military affairs, foreign policy and economics for EMs</t>
+          <t>Sustainability challenges in business, multi-stakeholder governance, ESG factors, sustainability reporting, climate finance, artificial intelligence in sustainability, sustainable business models, responsible consumption, supply chain management, among others.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026 International Forum on Financial Regulation and RegTech</t>
+          <t>China Accounting and Finance Review (CAFR) Special Issue Conference 2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Beihang University, Beijing, China</t>
+          <t>Zhongnan University of Economics and Law, Wuhan, China</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4149,108 +4149,108 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Financial Regulation &amp; RegTech Innovation, Risk Assessment &amp; Management, AI, LLMs &amp; Financial Infrastructure</t>
+          <t>ESG in the AI Era: Challenges and Opportunities; AI-Driven ESG Reporting and Assurance; Algorithmic Bias, Ethics, and Fairness in ESG Analytics; Regulatory Responses to AI-Enabled ESG Practices; AI, Greenwashing, and Corporate Accountability; AI for Sustainable Finance and Investment Decision-Making</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026 International Symposium on Climate, Finance, and Sustainability (ISCFS-2026)</t>
+          <t>2026 FMA Asia/Pacific Conference</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>House of Management Science, Paris Pantheon-Assas University, 1 rue Guy-de-la-Brosse 75005 Paris, France</t>
+          <t>Massey University, Auckland, New Zealand</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$50 USD (FMA-members), $60 USD (non-members)</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbon Finance and Taxes, Climate and Economic Modeling in Policy Making, Climate Finance, Climate Negotiations and Scenarios, Climate Risk and Disclosures, Climate-resilient Economies, Energy Derivatives: Pricing and Hedging, Energy Markets: Modeling and Forecasting, Energy, Environment, and Climate Models, Financial and Economic Analysis of Energy Markets, Financial Regulation of Energy and Environmental Markets, Green Finance and Sustainable Investment, Just Energy Transition, Macroeconomic Implications of Net-Zero Carbon Emissions, Nature-based Financial Instruments for Climate Change Mitigation, Natural Resources, Risk, Welfare, and Social Preferences, Renewable Energy, Regulation and Energy Governance, Role of Financial Institutions in Sustainability</t>
+          <t>Financial decision-making, financial management, current issues in finance</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>5th Annual Academic - 2026 DeFi &amp; Digital Currencies Conference</t>
+          <t>Sixth Biennial Conference on Auto Lending</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>The Shard, London, UK</t>
+          <t>Federal Reserve Bank of Philadelphia</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>£45</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>DeFi Protocols, Lending and Borrowing Protocols, Decentralized Exchanges, Blockchain Economics, Stablecoins and CBDCs, Digital Money and Payments, Tokenisation of real-world assets, Traditional and Decentralized Finance Interaction, Digital Finance and Inclusion</t>
+          <t>auto lending and auto finance topics including consumer demand and vehicle choice, loan pricing and contract design, underwriting and credit risk modeling, dealer intermediation and markups, borrower outcomes and delinquency dynamics, fraud and identity risk, fair lending and consumer compliance, subprime and near-prime market structure, repossession and loss mitigation, servicing and collections, the role of alternative data and automated decisioning, electric vehicles and evolving collateral risk, used vehicle prices and depreciation, auto insurance interactions, fintech and market structure, auto asset-backed securities, and spillovers from monetary policy and macroeconomic shocks.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3rd Arne Ryde Conference on Crypto, Fintech and Payments</t>
+          <t>Frontiers in Machine Learning and Economics: Methods and Applications</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Lund, Sweden</t>
+          <t>Federal Reserve Bank of Philadelphia</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4260,34 +4260,34 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Crypto and blockchain technology, Crypto markets and the real economy, Environmental and social impact of crypto markets, Interaction between traditional finance and decentralized finance, Stablecoins, Central Bank Digital Currencies (CBDCs), Financial technology (Fintech), Payment systems, Open banking and data sharing, Digital tools in financial services, Financial inclusion, development, and welfare in digital finance</t>
+          <t>Methodological advances in analyzing complex and high-dimensional data sets, Methodological advances in natural language processing with respect to causal inference, Innovative applications of generative AI, The societal impacts of AI and algorithmic decision-making</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Institute for Quantitative Investment Research Autumn Residential Seminar 2026</t>
+          <t>Workshop on Innovations in Credit Scoring</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Ashdown Park Hotel &amp; Country Club, Wych Cross, East Sussex, UK</t>
+          <t>Virtual</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4297,34 +4297,34 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>New risks in a changing political environment</t>
+          <t>Innovations in credit scoring, alternative data, artificial intelligence, machine learning, creditworthiness evaluation, risk management, data privacy</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>10th Shanghai-Edinburgh-London Finance Conference On Sustainable Finance in the Digital Era</t>
+          <t>2026 Conference on Real-Time Data Analysis, Methods, and Applications</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Shanghai and online</t>
+          <t>Federal Reserve Bank of Philadelphia</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4334,34 +4334,34 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Financial development, financial inclusion, policy frameworks for sustainable finance, cross-border sustainable finance, corporate governance, ESG backlash, AI applications in ESG investment, big data in ESG performance, blockchain applications in carbon markets, digital finance and low-carbon transition, fintech-enabled green lending</t>
+          <t>monitoring and forecasting of economic and financial developments, including the use of high-frequency data, survey data, text as data, transactions data, and granular data; using preliminary and revised data in economic policy formulation and analysis; machine learning applications in real-time macroeconomics; probabilistic forecasts and assessments of crisis risks (financial, macroeconomic, etc.); related innovative data sets and toolboxes; seasonal and cyclical adjustment for real-time monitoring and forecasting.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>22nd Annual Conference of the Asia-Pacific Association of Derivatives</t>
+          <t>2026 Jacobs Levy Center Frontiers in Quantitative Finance Conference</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Busan, Korea</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4371,71 +4371,71 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Derivatives; Volatility; Risk Management; Asset Pricing; Investments; Corporate Finance; Market Microstructure; Fintech; Regulation; Behavioral Finance</t>
+          <t>quantitative methods and asset pricing</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>FIRN Melbourne Asset Pricing Meeting</t>
+          <t>2026 AIM Investment Conference</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Melbourne, Australia</t>
+          <t>Austin, Texas</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$75 USD</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>theoretical and empirical models of asset prices and returns, return predictability, empirical methodology, macro-finance, the study of financial institutions as related to asset prices, information and liquidity in asset markets, behavioural investment studies, asset market structure and microstructure, risk analysis, hedge funds, mutual funds, pension funds, ESG, and alternative investments</t>
+          <t>mutual funds, hedge funds, pension funds, investment management</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Johns Hopkins Carey Finance Conference</t>
+          <t>2026 Wharton Conference on Liquidity and Financial Fragility</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Johns Hopkins Carey Business School, 100 International Drive, Baltimore, MD</t>
+          <t>University of Pennsylvania, Philadelphia, PA</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4445,71 +4445,71 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>All areas of finance, particularly early-stage papers</t>
+          <t>Coordination failures, self-fulfilling beliefs, and runs; Fragility in banks and non-bank institutions; Liquidity and frictions in financial markets and macroeconomy; Systemic risk and financial regulation; Monetary policy and financial stability; Artificial intelligence (AI) and its implications for financial macroeconomic stability; The rise and potential risks in private credit markets; New payment technologies, stablecoins, tokenization, and their financial stability implications; Geopolitical tensions, trade conflicts, currency competition, and financial fragility; Inflation, interest rate risks, and implications on financial fragility; The real impact of crises and fragility on firms’ financing and investment policies</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>5th Holden Conference in Finance and Real Estate</t>
+          <t>Towards a New Synthesis in Islamic Finance: Law, Economics and Shari’ah</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bloomington, IN</t>
+          <t>Online Conference from Durham University, England, UK</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>$95 (USD)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Empirical and theoretical papers in all finance and real estate areas</t>
+          <t>Islamic finance, financial innovation, regulatory oversight, governance mechanisms, economic development, sustainability, social equity, inclusive economic development</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>12th P2P Financial Systems International Workshop (P2PFISY 2026)</t>
+          <t>74th Meeting of the EURO Working Group for Commodities and Financial Modelling (EWGCFM)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Astana, Kazakhstan</t>
+          <t>Casa de Campo, La Romana, Dominican Republic</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4519,34 +4519,34 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Regulation &amp; Compliance in Digital Asset Markets, Fraud, Financial Crime &amp; Forensics in Crypto Markets, CBDCs and Digital Public Infrastructure, Stablecoins and Digital Payment Systems, Artificial Intelligence in Financial Systems, Consumer Protection, Data Governance, and Trust in Digital Finance, Tokenisation of Real-World Assets (RWA)</t>
+          <t>Asset Pricing, Corporate Finance, Banking and Financial Institutions, Commodities and Energy Markets, Financial Modelling and Econometrics, Blockchain and Cryptocurrencies, Derivatives and Risk Management, Market Microstructure, Sustainable Finance</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026 Annual Community Bank Research Conference</t>
+          <t>FIRN 2026 ANU Money, Credit, and Financial Stability Meeting</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of St. Louis, St. Louis, MO</t>
+          <t>Australian National University (ANU), Canberra, Australia</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4556,34 +4556,34 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Community banking, financial services to households and small businesses, impact of community banks on local/state economic activity, community banks’ response to economic shocks, effects of regulatory policy, challenges and opportunities for community banks, advantages and disadvantages of the community bank business model</t>
+          <t>Monetary policy and transmission mechanisms, Credit markets and financial intermediation, Banking, liquidity, and regulation, Financial crises and systemic risk, Macro-finance</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Stigler Center-CEPR Political Economy of Finance Conference 2026: Crony Capitalism in 21st Century America</t>
+          <t>Inaugural Annual Conference on Insurance</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Gleacher Center - Chicago</t>
+          <t>Federal Reserve Bank of Chicago</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4593,71 +4593,71 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Crony capitalism in 21st century America, political economy, intersections of finance, economics, political science, and law</t>
+          <t>life insurance, Property &amp; Casualty insurance, Reinsurance and risk transfer, Mergers and other ownership changes, Private equity ownership and impact on industry, Indexed, variable annuities, and other savings products, Household insurance choices, Insurances’ investment and funding strategies, Catastrophe risk, Impact of insurance regulation</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>15th Fixed Income and Financial Institutions (FIFI) Conference</t>
+          <t>Payments, Digital Assets, AI and the Future of Financial Markets</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>University of South Carolina in Columbia, SC</t>
+          <t>Imperial Business School, London</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>75 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>fixed income, commercial and investment banks, asset management and mutual fund companies, short sellers, hedge funds, broker-dealers, insurance companies</t>
+          <t>Digital platforms, banking, and financial intermediation; Artificial intelligence, machine learning, and financial decision-making; Blockchain, tokenization, digital assets, and decentralized finance; Payment systems, central bank digital currencies, and stablecoins; FinTech regulation, supervision, market design, and financial stability; Data, privacy, cybersecurity, and consumer protection in finance; Entrepreneurial finance, venture capital, and innovation in financial services; Household finance, inclusion, and welfare effects of financial technology; Market microstructure, trading technologies, and liquidity; Competition between banks, platforms, and non-bank financial institutions</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Higher Education Finance Research Conference</t>
+          <t>Future Scholars in Finance Forum</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Philadelphia</t>
+          <t>Beijing, China</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4667,34 +4667,34 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>financial aid, student debt, higher education finance, household balance sheets, labor market outcomes, consumption, wealth accumulation</t>
+          <t>All areas of finance</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026 Wharton–Chicago–Harvard Insolvency and Restructuring Conference (WCHIRC)</t>
+          <t>Prototypes for Humanity 2026 Short Papers Platform</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>University of Pennsylvania, Philadelphia, PA</t>
+          <t>Dubai, UAE</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4704,34 +4704,34 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Corporate financial distress and bankruptcy, Liability management and out-of-court restructurings, Chapter 11 and formal reorganization processes, Consumer bankruptcy, Leveraged lending and private credit, Creditor governance and capital structure dynamics, Distressed debt markets and asset pricing, Financial contracting and covenant design, Bankruptcy law, courts, and institutional design, Operational restructuring and firm performance</t>
+          <t>Wellbeing and Human Performance, Infrastructures and Cities, Autonomous Systems and Advanced Manufacturing, Environment, Sustainability and Energy, Mobility and Logistics, Socio-Economic Empowerment, Digital Economies and Future Markets, Open and Speculative</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Financial Decision-Making Conference 2026</t>
+          <t>2026 Federal Reserve Stress Testing Research Conference</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Bozeman, MT</t>
+          <t>Boston, Massachusetts</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4741,108 +4741,108 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>household finance, financial literacy and education, consumer financial behavior, retirement and savings decisions, financial education interventions, fintech and digital finance, financial advice and delegation, debt and credit decisions, insurance decisions, behavioral finance, financial inclusion</t>
+          <t>The economic and macroprudential effects of stress tests and bank regulation, Novel approaches to modeling bank profitability, financial risks, and operational risks, Design and applications of stress scenarios and reverse stress testing, Nonbank credit intermediation, Financial instruments for risk transfer, Recent developments in bank regulation, The impact of emerging technologies on banks and their regulators</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Finance and Real Estate Conference 2026</t>
+          <t>EBA's 15th Policy Research Workshop</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Miami University, Oxford, OH</t>
+          <t>EBA premises (Paris, France) and remotely</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>$50 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Asset pricing and valuation, Corporate finance, Real estate markets and investment, Risk management and financial regulation, Urban economics and housing policy, Sustainable and green finance, Behavioral finance</t>
+          <t>Competitiveness and efficiency in the prudential rulebook without undermining resilience; Impacts of efficiency and proportionality; Competition, innovation, market entry, cross border growth and new areas under financial supervision; Proportionate integration of ESG risks in governance, strategy, and remuneration frameworks</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>UGA Fall Finance Conference 2026</t>
+          <t>3rd Financial Fraud, Misconduct and Market Manipulation Conference</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Athens, GA</t>
+          <t>Lancaster University, England</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>70 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>All areas of finance</t>
+          <t>Theoretical and empirical analysis of financial fraud, case studies of recent instances of market misconduct, insider trading, implication of financial fraud/market manipulation for market efficiency, stability, and asset pricing, market manipulation at a high-frequency level, fraudulent activities and crypto currency markets, social networks, fake news and their effect on financial markets, money laundering and banking, conflicts of interests and their implications for various stakeholders and financial markets, hedge funds/mutual funds and their involvement in market misconduct, statistical/machine learning methods for fraud detection, cyber security and cyber risk management, regulatory response to financial misconduct, unintended consequences of politics and regulations</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Inquire Europe Autumn Conference: “Expectations and Asset Prices”</t>
+          <t>22nd Annual Haskell &amp; White Corporate Reporting and Governance Conference</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Prague, Czech Republic</t>
+          <t>California State University, Fullerton</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4852,34 +4852,34 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Expectations and Asset Prices, deviations from rational expectations and their implications, optimism and pessimism in asset valuations and market dynamics, investment strategies and anomalies, factor investing, strategic and tactical asset allocation, portfolio choice under model and parameter uncertainty, short selling</t>
+          <t>All areas of accounting and finance, including interdisciplinary research related to corporate reporting, governance, and financial markets</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>The WFE’s Sustainability Conference 2026</t>
+          <t>25th Annual Bank Research Conference</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Arlington, VA</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4889,71 +4889,71 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Transition finance and market design, Regulatory fragmentation and divergence, Sustainability reporting, Nature and biodiversity in capital markets, Just transition, social and gender finance, Proportionality for SMEs and emerging markets, Carbon market architecture</t>
+          <t>Regulatory reform options and considerations, Risk and resiliency in the financial system, Real effects of financial turmoil, Innovations in financial intermediation, Deposit insurance and stability, Emerging competitive threats to traditional banking, AI and technology in finance, Banks’ role in the 21st Century</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026 FMA Annual Meeting</t>
+          <t>The Future of Decision-Making and Risk-Taking: Bridging Finance, Economics, Brain, and Behavior</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Tampa, FL</t>
+          <t>Santa Monica, California, USA</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>$75 (current FMA members); $85 (non-members)</t>
+          <t>$99.00 USD</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Financial decision-making, financial management and related topics</t>
+          <t>Behavioral/Cognitive Finance &amp; Economics, Neuroscience/Neuromorphic Computing, Political Economy, Biological Anthropology, Brain-Computer Interfaces, Development of New Financial &amp; Economic Models, Decision Making under risk and uncertainty, Venture Startups &amp; Exits, Trust in Financial Markets, Investment &amp; Management, Personal Finance, Pedagogy using AI or AGI, Behavioral Finance in Practice</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>3rd AI in Finance Conference</t>
+          <t>17th Emerging Markets Conference</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Montréal, QC, Canada</t>
+          <t>Mumbai, India</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4963,34 +4963,34 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Machine learning and artificial intelligence in asset pricing and financial econometrics, Portfolio management, trading strategies, and risk management using AI, Large language models (LLMs), NLP, and textual analysis in finance, Corporate finance applications including M&amp;A and investment decisions, Banking, credit markets, and financial intermediation, Cryptocurrency, digital assets, and decentralized finance, ESG, sustainability, and climate finance, Financial regulation, policy analysis, and central bank communication, Real estate finance and urban economics, Alternative data and high-dimensional financial datasets, Investor behavior, sentiment, and attention, Macroeconomic and financial risk forecasting</t>
+          <t>The sources of economic success or failure in EMs, Finance in EMs (households, financial markets, financial intermediaries, firms and finance, finance and growth), Political economy, law, public administration, regulation in EMs, The impact of populism upon the possibility of sustained growth, Insights into large EMs that matter in and of themselves, Insights from narrow research projects that illuminate EMs in general, The new phase of globalisation and its consequences for international trade, international finance and the nature of the EM firm, Features of a society that enable or disable convergence into the “normal” package of high levels of freedom and prosperity, The puzzles faced by all kinds of decision makers: individuals, civil society actors, firms, all levels of government, Grand challenges such as climate change: implications for EMs and ramifications of choices made in EMs, State capability in EMs, The interplay of military affairs, foreign policy and economics for EMs</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026 Summer Research Conference</t>
+          <t>2026 International Forum on Financial Regulation and RegTech</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Indian School of Business, Hyderabad Campus</t>
+          <t>Beihang University, Beijing, China</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5000,34 +5000,34 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Recent Advances in Finance, corporate finance and its interface with asset pricing, behavioral finance, financial intermediation, household finance, market microstructure</t>
+          <t>Financial Regulation &amp; RegTech Innovation, Risk Assessment &amp; Management, AI, LLMs &amp; Financial Infrastructure</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>International Risk Management Conference 2026</t>
+          <t>2026 International Symposium on Climate, Finance, and Sustainability (ISCFS-2026)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Warsaw, Poland</t>
+          <t>House of Management Science, Paris Pantheon-Assas University, Paris, France</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -5037,108 +5037,108 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Asset pricing; Banking; Financial econometrics; Capital markets; Financial intermediation; Corporate finance; Financial crises; Corporate governance; Market microstructure; Financial regulation; International corporate finance; Risk management; Emerging market; Corporate investment decision; Global risk markets; Macro-financial linkages; Financial policy securitization; Behavioural finance; Financial integration; Mathematical &amp; computational finance; Stochastic optimization approaches in finance; Mergers &amp; acquisitions; Modelling, money and liquidity; Sustainable finance; Climate change risk; AI innovation; crypto and related assets and technology.</t>
+          <t>Energy transition, environmental sustainability, banking, climate finance, financial markets, macroeconomy, carbon finance, climate risk, green finance, renewable energy</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>The Second USTC Frontiers in Finance Conference</t>
+          <t>5th Annual Academic - 2026 DeFi &amp; Digital Currencies Conference</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>International Finance Institute, University of Science and Technology of China, No. 1789 Guangxi Road, Binhu New District, Hefei City, Anhui Province, P.R.China</t>
+          <t>The Shard, London, UK</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>£45</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>All topics of finance</t>
+          <t>DeFi Protocols, Lending and Borrowing Protocols, Decentralized Exchanges, Blockchain Economics, Stablecoins and CBDCs, Digital Money and Payments, Tokenisation of real-world assets, Traditional and Decentralized Finance Interaction, Digital Finance and Inclusion</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Fischer-Shain Research Conference 2026</t>
+          <t>3rd Arne Ryde Conference on Crypto, Fintech and Payments</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>Lund, Sweden</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>50 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>financial intermediation, banking, financial services</t>
+          <t>Crypto and blockchain technology, Crypto markets, households, and the real economy, Environmental and social impact of crypto markets, Interaction between traditional finance and decentralized finance, Stablecoins, Central Bank Digital Currencies (CBDCs), Financial technology (Fintech), Payment systems, Open banking and data sharing, Digital tools in financial services, Financial inclusion, development, and welfare in digital finance</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ECB Money Market Conference 2026</t>
+          <t>Institute for Quantitative Investment Research Autumn Residential Seminar 2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>European Central Bank, Frankfurt am Main, Germany</t>
+          <t>Ashdown Park Hotel &amp; Country Club, Wych Cross, East Sussex, UK</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -5148,34 +5148,34 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Money markets and monetary policy implementation, technological innovation in money markets, functioning of money markets</t>
+          <t>New risks in a changing political environment; innovative, high-quality research papers related to investment management</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Finance in the Digital Age (FiDA) Workshop</t>
+          <t>10th Shanghai-Edinburgh-London Finance Conference On Sustainable Finance in the Digital Era</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Calgary, Canada</t>
+          <t>Shanghai and online</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -5185,266 +5185,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>AI, DeFi, robo-advisors, neurofinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>7th LTI@UniTO/Bank of Italy Workshop on Long-term investors’ trends: theory and practice</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Bank of Italy, Rome, Italy</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>Long-term investors’ strategies and behavior, Long-term investors’ role in financing the economy, Shifting equilibria in government bond markets, Evolution of sustainable investment strategies, Challenges for long-term investors, Importance of non-bank investors, Rising of cryptocurrencies and fintech, Emerging trends in asset allocation and risk management, Shock transmission mechanisms, Use of big data and AI in investment processes, Innovations in financial markets, Geopolitical risks effects, Effects of demographic transitions on financial markets</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>7th Annual RCF-ECGI Corporate Finance and Governance Conference</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>Madrid, Spain, and virtually</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>€350 in person, €50 online option</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>capital structure, corporate and securities law, corporate culture, corporate failure, corporate finance and public policy, corporate governance, corporate restructuring, corporate social responsibility, crowdfunding, dividends, payout policy, and repurchases, entrepreneurial finance, family business, financial contracting, financial intermediation, financial literacy, fintech, fraud, innovation, IPOs and SEOs, mergers and acquisitions, misconduct, private debt, private equity, trade credit, socially responsible investments, sustainable finance, real options, and venture capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Fintech and Financial Institutions Research Conference</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Federal Reserve Bank of Philadelphia, Philadelphia, PA</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>Interlinkages of the fintech sector and the broader financial system, economic consequences of fintech, regulatory implications of fintech</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Aarhus Finance Forum 2026</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Aarhus, Denmark</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>375 DKK (approx. 50 Euros)</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>Financial Decisions under Uncertainty and Ambiguity, Household Finance, Real Estate Finance, Corporate Finance, Climate Finance, Digital Finance, Asset Pricing</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>15th CDI Conference on Derivatives</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Montreal, Canada</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Conference on CSR, the Economy and Financial Markets</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Düsseldorf, Germany</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>€150 for regular participants, €100 for PhD students</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>Climate risk and pricing, Role of financial markets, banks, institutional investors in CSR, Effects of CSR on valuation, performance, cost of capital, funding and capital structure, Socio-economic aspects and their implications for companies and financial markets, Corporate governance and CSR, Risk management and CSR, CSR reporting and disclosure, ESG backlash and politicization, Sustainability strategy under new constraints, Measurement: information content and reliability of ESG indices, CSR activities and the economy</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>2026 Vietnam Symposium on Global Economy (VSGE2026)</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Ho Chi Minh City, Vietnam</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>Geopolitical, macroeconomic policy, and development; Trade, foreign direct investment, and global value chain; Climate change, green transition, and public finance; Finance, stability, and sustainable investment; Digitalization, labor markets, and social protection; Urbanization, regional development and resilience; AI, growth, economic impacts, and government policies; Global governance, institutions, and international cooperation</t>
+          <t>Sustainable finance, AI, blockchain, ESG integration, financial development, financial inclusion, policy frameworks, corporate governance, AI applications in ESG, big data in ESG performance, blockchain in carbon markets, digital finance, fintech-enabled green lending</t>
         </is>
       </c>
     </row>
